--- a/artfynd/A 41794-2025 artfynd.xlsx
+++ b/artfynd/A 41794-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128991347</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128998779</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128997543</v>
+        <v>128993314</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492963</v>
+        <v>493165</v>
       </c>
       <c r="R4" t="n">
-        <v>6761283</v>
+        <v>6761309</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128994822</v>
+        <v>128997543</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493022</v>
+        <v>492963</v>
       </c>
       <c r="R5" t="n">
-        <v>6761226</v>
+        <v>6761283</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128993314</v>
+        <v>128999532</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,14 +1134,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493165</v>
+        <v>493157</v>
       </c>
       <c r="R6" t="n">
-        <v>6761309</v>
+        <v>6761137</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,7 +1218,7 @@
         <v>128992649</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128999532</v>
+        <v>128994822</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,14 +1353,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493157</v>
+        <v>493022</v>
       </c>
       <c r="R8" t="n">
-        <v>6761137</v>
+        <v>6761226</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,12 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128998367</v>
+        <v>128999351</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492928</v>
+        <v>493087</v>
       </c>
       <c r="R9" t="n">
-        <v>6761141</v>
+        <v>6761166</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,7 +1539,7 @@
         <v>128999256</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128999351</v>
+        <v>128998367</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493087</v>
+        <v>492928</v>
       </c>
       <c r="R11" t="n">
-        <v>6761166</v>
+        <v>6761141</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128998263</v>
+        <v>128998025</v>
       </c>
       <c r="B12" t="n">
-        <v>57717</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,39 +1761,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492885</v>
+        <v>492895</v>
       </c>
       <c r="R12" t="n">
-        <v>6761180</v>
+        <v>6761212</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1862,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128997799</v>
+        <v>128991923</v>
       </c>
       <c r="B13" t="n">
-        <v>57717</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,39 +1868,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492929</v>
+        <v>493277</v>
       </c>
       <c r="R13" t="n">
-        <v>6761272</v>
+        <v>6761265</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,7 +1927,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1937,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,10 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128998274</v>
+        <v>128998263</v>
       </c>
       <c r="B14" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,10 +2004,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492894</v>
+        <v>492885</v>
       </c>
       <c r="R14" t="n">
-        <v>6761171</v>
+        <v>6761180</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2086,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128998025</v>
+        <v>128999613</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,34 +2087,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492895</v>
+        <v>493205</v>
       </c>
       <c r="R15" t="n">
-        <v>6761212</v>
+        <v>6761180</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2161,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128991923</v>
+        <v>128997799</v>
       </c>
       <c r="B16" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2204,34 +2199,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493277</v>
+        <v>492929</v>
       </c>
       <c r="R16" t="n">
-        <v>6761265</v>
+        <v>6761272</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128991903</v>
+        <v>128998274</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,34 +2311,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493287</v>
+        <v>492894</v>
       </c>
       <c r="R17" t="n">
-        <v>6761277</v>
+        <v>6761171</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2375,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2385,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,32 +2412,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128990939</v>
+        <v>128991903</v>
       </c>
       <c r="B18" t="n">
-        <v>97507</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2442,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493487</v>
+        <v>493287</v>
       </c>
       <c r="R18" t="n">
-        <v>6761281</v>
+        <v>6761277</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2488,11 +2493,6 @@
       <c r="AB18" t="inlineStr">
         <is>
           <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2519,50 +2519,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128999613</v>
+        <v>128990939</v>
       </c>
       <c r="B19" t="n">
-        <v>57717</v>
+        <v>97514</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493205</v>
+        <v>493487</v>
       </c>
       <c r="R19" t="n">
-        <v>6761180</v>
+        <v>6761281</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2594,7 +2589,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2604,7 +2599,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2631,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128994202</v>
+        <v>128991027</v>
       </c>
       <c r="B20" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2662,14 +2662,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493144</v>
+        <v>493464</v>
       </c>
       <c r="R20" t="n">
-        <v>6761263</v>
+        <v>6761291</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2741,7 +2741,7 @@
         <v>128998438</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2845,10 +2845,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128991027</v>
+        <v>128994202</v>
       </c>
       <c r="B22" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2876,14 +2876,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493464</v>
+        <v>493144</v>
       </c>
       <c r="R22" t="n">
-        <v>6761291</v>
+        <v>6761263</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2955,7 +2955,7 @@
         <v>128998223</v>
       </c>
       <c r="B23" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>128998201</v>
       </c>
       <c r="B24" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>128991711</v>
       </c>
       <c r="B25" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>128995392</v>
       </c>
       <c r="B26" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3389,45 +3389,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128994100</v>
+        <v>128990886</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493167</v>
+        <v>493487</v>
       </c>
       <c r="R27" t="n">
-        <v>6761257</v>
+        <v>6761281</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3469,7 +3469,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Sumpskogskaraktär i området här.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3496,45 +3501,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128990886</v>
+        <v>128994100</v>
       </c>
       <c r="B28" t="n">
-        <v>79124</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493487</v>
+        <v>493167</v>
       </c>
       <c r="R28" t="n">
-        <v>6761281</v>
+        <v>6761257</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3566,7 +3571,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3576,12 +3581,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Sumpskogskaraktär i området här.</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3611,7 +3611,7 @@
         <v>128994343</v>
       </c>
       <c r="B29" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3715,32 +3715,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128998878</v>
+        <v>128995396</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492993</v>
+        <v>492992</v>
       </c>
       <c r="R30" t="n">
-        <v>6761002</v>
+        <v>6761309</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3822,32 +3822,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128995396</v>
+        <v>128998878</v>
       </c>
       <c r="B31" t="n">
-        <v>79124</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492992</v>
+        <v>492993</v>
       </c>
       <c r="R31" t="n">
-        <v>6761309</v>
+        <v>6761002</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3929,45 +3929,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128994846</v>
+        <v>128991481</v>
       </c>
       <c r="B32" t="n">
-        <v>79124</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493013</v>
+        <v>493300</v>
       </c>
       <c r="R32" t="n">
-        <v>6761220</v>
+        <v>6761215</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4036,45 +4036,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128991481</v>
+        <v>128994846</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493300</v>
+        <v>493013</v>
       </c>
       <c r="R33" t="n">
-        <v>6761215</v>
+        <v>6761220</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4146,7 +4146,7 @@
         <v>128994977</v>
       </c>
       <c r="B34" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>128997967</v>
       </c>
       <c r="B35" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128993887</v>
+        <v>128991491</v>
       </c>
       <c r="B36" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4373,34 +4373,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493167</v>
+        <v>493290</v>
       </c>
       <c r="R36" t="n">
-        <v>6761257</v>
+        <v>6761213</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4432,7 +4437,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4442,7 +4447,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4469,10 +4474,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128994367</v>
+        <v>128993887</v>
       </c>
       <c r="B37" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4504,10 +4509,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493118</v>
+        <v>493167</v>
       </c>
       <c r="R37" t="n">
-        <v>6761310</v>
+        <v>6761257</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4576,10 +4581,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128994864</v>
+        <v>128994367</v>
       </c>
       <c r="B38" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4611,10 +4616,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493021</v>
+        <v>493118</v>
       </c>
       <c r="R38" t="n">
-        <v>6761214</v>
+        <v>6761310</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4683,10 +4688,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128991964</v>
+        <v>128994864</v>
       </c>
       <c r="B39" t="n">
-        <v>58150</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4694,42 +4699,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493252</v>
+        <v>493021</v>
       </c>
       <c r="R39" t="n">
-        <v>6761277</v>
+        <v>6761214</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4795,10 +4795,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128991491</v>
+        <v>128991964</v>
       </c>
       <c r="B40" t="n">
-        <v>57717</v>
+        <v>58153</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4806,27 +4806,27 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4835,13 +4835,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493290</v>
+        <v>493252</v>
       </c>
       <c r="R40" t="n">
-        <v>6761213</v>
+        <v>6761277</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>128999032</v>
       </c>
       <c r="B41" t="n">
-        <v>58150</v>
+        <v>58153</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5019,10 +5019,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128999732</v>
+        <v>128995173</v>
       </c>
       <c r="B42" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5050,14 +5050,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493327</v>
+        <v>493010</v>
       </c>
       <c r="R42" t="n">
-        <v>6761155</v>
+        <v>6761236</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5126,10 +5126,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128995173</v>
+        <v>128994946</v>
       </c>
       <c r="B43" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5161,10 +5161,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493010</v>
+        <v>492986</v>
       </c>
       <c r="R43" t="n">
-        <v>6761236</v>
+        <v>6761194</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5233,10 +5233,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128994294</v>
+        <v>128991661</v>
       </c>
       <c r="B44" t="n">
-        <v>79743</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5244,34 +5244,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>493144</v>
+        <v>493295</v>
       </c>
       <c r="R44" t="n">
-        <v>6761263</v>
+        <v>6761257</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5340,10 +5340,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128991661</v>
+        <v>128999732</v>
       </c>
       <c r="B45" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5375,10 +5375,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>493295</v>
+        <v>493327</v>
       </c>
       <c r="R45" t="n">
-        <v>6761257</v>
+        <v>6761155</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5447,10 +5447,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128994946</v>
+        <v>128994294</v>
       </c>
       <c r="B46" t="n">
-        <v>79124</v>
+        <v>79648</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5458,21 +5458,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5482,10 +5482,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492986</v>
+        <v>493144</v>
       </c>
       <c r="R46" t="n">
-        <v>6761194</v>
+        <v>6761263</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5554,10 +5554,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128994503</v>
+        <v>128998610</v>
       </c>
       <c r="B47" t="n">
-        <v>57717</v>
+        <v>79029</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5565,39 +5565,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493047</v>
+        <v>492993</v>
       </c>
       <c r="R47" t="n">
-        <v>6761263</v>
+        <v>6761086</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5629,7 +5624,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5639,7 +5634,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5669,7 +5664,7 @@
         <v>128991653</v>
       </c>
       <c r="B48" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5778,10 +5773,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128998610</v>
+        <v>128994503</v>
       </c>
       <c r="B49" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5789,34 +5784,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492993</v>
+        <v>493047</v>
       </c>
       <c r="R49" t="n">
-        <v>6761086</v>
+        <v>6761263</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5992,10 +5992,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128994661</v>
+        <v>128999627</v>
       </c>
       <c r="B51" t="n">
-        <v>57717</v>
+        <v>79029</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6003,39 +6003,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493048</v>
+        <v>493222</v>
       </c>
       <c r="R51" t="n">
-        <v>6761242</v>
+        <v>6761162</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6067,7 +6062,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6077,7 +6072,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6104,10 +6099,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128999627</v>
+        <v>128994661</v>
       </c>
       <c r="B52" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6115,34 +6110,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493222</v>
+        <v>493048</v>
       </c>
       <c r="R52" t="n">
-        <v>6761162</v>
+        <v>6761242</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6211,10 +6211,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128991818</v>
+        <v>128998999</v>
       </c>
       <c r="B53" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6242,14 +6242,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>493312</v>
+        <v>493048</v>
       </c>
       <c r="R53" t="n">
-        <v>6761262</v>
+        <v>6761092</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6318,10 +6318,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128998638</v>
+        <v>128991818</v>
       </c>
       <c r="B54" t="n">
-        <v>57717</v>
+        <v>79029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6329,39 +6329,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>492971</v>
+        <v>493312</v>
       </c>
       <c r="R54" t="n">
-        <v>6761075</v>
+        <v>6761262</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6393,7 +6388,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6403,7 +6398,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6430,10 +6425,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128998999</v>
+        <v>128998638</v>
       </c>
       <c r="B55" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6441,34 +6436,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>493048</v>
+        <v>492971</v>
       </c>
       <c r="R55" t="n">
-        <v>6761092</v>
+        <v>6761075</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6540,7 +6540,7 @@
         <v>128991463</v>
       </c>
       <c r="B56" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>128995292</v>
       </c>
       <c r="B57" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>128990627</v>
       </c>
       <c r="B58" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>128994922</v>
       </c>
       <c r="B59" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6972,6 +6972,111 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>129015883</v>
+      </c>
+      <c r="B60" t="n">
+        <v>92841</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Stikå-Persänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>493474</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6761277</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41794-2025 artfynd.xlsx
+++ b/artfynd/A 41794-2025 artfynd.xlsx
@@ -1750,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128991903</v>
+        <v>128998263</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,34 +1761,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493287</v>
+        <v>492885</v>
       </c>
       <c r="R12" t="n">
-        <v>6761277</v>
+        <v>6761180</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1830,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1857,45 +1862,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128990939</v>
+        <v>128999613</v>
       </c>
       <c r="B13" t="n">
-        <v>97522</v>
+        <v>57720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493487</v>
+        <v>493205</v>
       </c>
       <c r="R13" t="n">
-        <v>6761281</v>
+        <v>6761180</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1937,12 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,7 +1974,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128998263</v>
+        <v>128997799</v>
       </c>
       <c r="B14" t="n">
         <v>57720</v>
@@ -2009,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492885</v>
+        <v>492929</v>
       </c>
       <c r="R14" t="n">
-        <v>6761180</v>
+        <v>6761272</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2081,7 +2086,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128999613</v>
+        <v>128998274</v>
       </c>
       <c r="B15" t="n">
         <v>57720</v>
@@ -2121,10 +2126,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493205</v>
+        <v>492894</v>
       </c>
       <c r="R15" t="n">
-        <v>6761180</v>
+        <v>6761171</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2161,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2171,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128997799</v>
+        <v>128998025</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2204,39 +2209,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492929</v>
+        <v>492895</v>
       </c>
       <c r="R16" t="n">
-        <v>6761272</v>
+        <v>6761212</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2305,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128998274</v>
+        <v>128991923</v>
       </c>
       <c r="B17" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2316,39 +2316,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492894</v>
+        <v>493277</v>
       </c>
       <c r="R17" t="n">
-        <v>6761171</v>
+        <v>6761265</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,7 +2375,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2390,7 +2385,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2417,7 +2412,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128998025</v>
+        <v>128991903</v>
       </c>
       <c r="B18" t="n">
         <v>79034</v>
@@ -2448,14 +2443,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492895</v>
+        <v>493287</v>
       </c>
       <c r="R18" t="n">
-        <v>6761212</v>
+        <v>6761277</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2487,7 +2482,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2497,7 +2492,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2524,32 +2519,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128991923</v>
+        <v>128990939</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>97522</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2559,10 +2554,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493277</v>
+        <v>493487</v>
       </c>
       <c r="R19" t="n">
-        <v>6761265</v>
+        <v>6761281</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2605,6 +2600,11 @@
       <c r="AB19" t="inlineStr">
         <is>
           <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3929,45 +3929,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128994846</v>
+        <v>128991481</v>
       </c>
       <c r="B32" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493013</v>
+        <v>493300</v>
       </c>
       <c r="R32" t="n">
-        <v>6761220</v>
+        <v>6761215</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4036,45 +4036,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128991481</v>
+        <v>128994846</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493300</v>
+        <v>493013</v>
       </c>
       <c r="R33" t="n">
-        <v>6761215</v>
+        <v>6761220</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4250,10 +4250,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128994864</v>
+        <v>128991964</v>
       </c>
       <c r="B35" t="n">
-        <v>79034</v>
+        <v>58153</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4261,37 +4261,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493021</v>
+        <v>493252</v>
       </c>
       <c r="R35" t="n">
-        <v>6761214</v>
+        <v>6761277</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4320,7 +4325,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4330,7 +4335,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4357,10 +4362,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128997967</v>
+        <v>128999032</v>
       </c>
       <c r="B36" t="n">
-        <v>79034</v>
+        <v>58153</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4368,34 +4373,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492949</v>
+        <v>493048</v>
       </c>
       <c r="R36" t="n">
-        <v>6761266</v>
+        <v>6761092</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4427,7 +4437,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4437,12 +4447,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4469,10 +4474,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128993887</v>
+        <v>128991491</v>
       </c>
       <c r="B37" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4480,34 +4485,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493167</v>
+        <v>493290</v>
       </c>
       <c r="R37" t="n">
-        <v>6761257</v>
+        <v>6761213</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4539,7 +4549,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4549,7 +4559,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4576,7 +4586,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128994367</v>
+        <v>128994864</v>
       </c>
       <c r="B38" t="n">
         <v>79034</v>
@@ -4611,10 +4621,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493118</v>
+        <v>493021</v>
       </c>
       <c r="R38" t="n">
-        <v>6761310</v>
+        <v>6761214</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4683,10 +4693,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128991491</v>
+        <v>128993887</v>
       </c>
       <c r="B39" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4694,39 +4704,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493290</v>
+        <v>493167</v>
       </c>
       <c r="R39" t="n">
-        <v>6761213</v>
+        <v>6761257</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4758,7 +4763,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4768,7 +4773,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4795,10 +4800,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128991964</v>
+        <v>128994367</v>
       </c>
       <c r="B40" t="n">
-        <v>58153</v>
+        <v>79034</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4806,42 +4811,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493252</v>
+        <v>493118</v>
       </c>
       <c r="R40" t="n">
-        <v>6761277</v>
+        <v>6761310</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4907,10 +4907,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128999032</v>
+        <v>128997967</v>
       </c>
       <c r="B41" t="n">
-        <v>58153</v>
+        <v>79034</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4918,39 +4918,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493048</v>
+        <v>492949</v>
       </c>
       <c r="R41" t="n">
-        <v>6761092</v>
+        <v>6761266</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4982,7 +4977,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4992,7 +4987,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5019,10 +5019,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128994294</v>
+        <v>128995173</v>
       </c>
       <c r="B42" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493144</v>
+        <v>493010</v>
       </c>
       <c r="R42" t="n">
-        <v>6761263</v>
+        <v>6761236</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5447,10 +5447,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128995173</v>
+        <v>128994294</v>
       </c>
       <c r="B46" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5458,21 +5458,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5482,10 +5482,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493010</v>
+        <v>493144</v>
       </c>
       <c r="R46" t="n">
-        <v>6761236</v>
+        <v>6761263</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>

--- a/artfynd/A 41794-2025 artfynd.xlsx
+++ b/artfynd/A 41794-2025 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128999532</v>
+        <v>128993314</v>
       </c>
       <c r="B4" t="n">
         <v>79034</v>
@@ -920,14 +920,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493157</v>
+        <v>493165</v>
       </c>
       <c r="R4" t="n">
-        <v>6761137</v>
+        <v>6761309</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128993314</v>
+        <v>128997543</v>
       </c>
       <c r="B5" t="n">
         <v>79034</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493165</v>
+        <v>492963</v>
       </c>
       <c r="R5" t="n">
-        <v>6761309</v>
+        <v>6761283</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128997543</v>
+        <v>128992649</v>
       </c>
       <c r="B6" t="n">
         <v>79034</v>
@@ -1139,14 +1134,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492963</v>
+        <v>493247</v>
       </c>
       <c r="R6" t="n">
-        <v>6761283</v>
+        <v>6761309</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128992649</v>
+        <v>128994822</v>
       </c>
       <c r="B7" t="n">
         <v>79034</v>
@@ -1246,14 +1241,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493247</v>
+        <v>493022</v>
       </c>
       <c r="R7" t="n">
-        <v>6761309</v>
+        <v>6761226</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128994822</v>
+        <v>128999532</v>
       </c>
       <c r="B8" t="n">
         <v>79034</v>
@@ -1353,14 +1348,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493022</v>
+        <v>493157</v>
       </c>
       <c r="R8" t="n">
-        <v>6761226</v>
+        <v>6761137</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,7 +1397,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,7 +1429,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128999256</v>
+        <v>128998367</v>
       </c>
       <c r="B9" t="n">
         <v>79034</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493048</v>
+        <v>492928</v>
       </c>
       <c r="R9" t="n">
-        <v>6761242</v>
+        <v>6761141</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128998367</v>
+        <v>128999256</v>
       </c>
       <c r="B10" t="n">
         <v>79034</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492928</v>
+        <v>493048</v>
       </c>
       <c r="R10" t="n">
-        <v>6761141</v>
+        <v>6761242</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1750,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128998263</v>
+        <v>128991903</v>
       </c>
       <c r="B12" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,39 +1761,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492885</v>
+        <v>493287</v>
       </c>
       <c r="R12" t="n">
-        <v>6761180</v>
+        <v>6761277</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1820,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1830,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128999613</v>
+        <v>128998025</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,39 +1868,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493205</v>
+        <v>492895</v>
       </c>
       <c r="R13" t="n">
-        <v>6761180</v>
+        <v>6761212</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,7 +1927,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1937,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,10 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128997799</v>
+        <v>128991923</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,39 +1975,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492929</v>
+        <v>493277</v>
       </c>
       <c r="R14" t="n">
-        <v>6761272</v>
+        <v>6761265</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,7 +2034,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2059,7 +2044,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,7 +2071,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128998274</v>
+        <v>128998263</v>
       </c>
       <c r="B15" t="n">
         <v>57720</v>
@@ -2126,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492894</v>
+        <v>492885</v>
       </c>
       <c r="R15" t="n">
-        <v>6761171</v>
+        <v>6761180</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2198,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128998025</v>
+        <v>128999613</v>
       </c>
       <c r="B16" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,34 +2194,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492895</v>
+        <v>493205</v>
       </c>
       <c r="R16" t="n">
-        <v>6761212</v>
+        <v>6761180</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2278,7 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2305,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128991923</v>
+        <v>128997799</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2316,34 +2306,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493277</v>
+        <v>492929</v>
       </c>
       <c r="R17" t="n">
-        <v>6761265</v>
+        <v>6761272</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2375,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2385,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2412,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128991903</v>
+        <v>128998274</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,34 +2418,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493287</v>
+        <v>492894</v>
       </c>
       <c r="R18" t="n">
-        <v>6761277</v>
+        <v>6761171</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2522,7 +2522,7 @@
         <v>128990939</v>
       </c>
       <c r="B19" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128994202</v>
+        <v>128991027</v>
       </c>
       <c r="B20" t="n">
         <v>79034</v>
@@ -2662,14 +2662,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493144</v>
+        <v>493464</v>
       </c>
       <c r="R20" t="n">
-        <v>6761263</v>
+        <v>6761291</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2845,7 +2845,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128991027</v>
+        <v>128994202</v>
       </c>
       <c r="B22" t="n">
         <v>79034</v>
@@ -2876,14 +2876,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493464</v>
+        <v>493144</v>
       </c>
       <c r="R22" t="n">
-        <v>6761291</v>
+        <v>6761263</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2952,10 +2952,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128998223</v>
+        <v>128991711</v>
       </c>
       <c r="B23" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2963,34 +2963,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492885</v>
+        <v>493310</v>
       </c>
       <c r="R23" t="n">
-        <v>6761180</v>
+        <v>6761241</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3022,7 +3027,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3032,7 +3037,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3059,7 +3064,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128998201</v>
+        <v>128998223</v>
       </c>
       <c r="B24" t="n">
         <v>79034</v>
@@ -3094,10 +3099,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492877</v>
+        <v>492885</v>
       </c>
       <c r="R24" t="n">
-        <v>6761211</v>
+        <v>6761180</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3166,10 +3171,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128991711</v>
+        <v>128998201</v>
       </c>
       <c r="B25" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3177,39 +3182,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493310</v>
+        <v>492877</v>
       </c>
       <c r="R25" t="n">
-        <v>6761241</v>
+        <v>6761211</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3278,10 +3278,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128995392</v>
+        <v>128990886</v>
       </c>
       <c r="B26" t="n">
-        <v>91540</v>
+        <v>79034</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3289,38 +3289,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492992</v>
+        <v>493487</v>
       </c>
       <c r="R26" t="n">
-        <v>6761309</v>
+        <v>6761281</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3352,7 +3348,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3362,7 +3358,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Sumpskogskaraktär i området här.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3389,45 +3390,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128994100</v>
+        <v>128995392</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>91543</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493167</v>
+        <v>492992</v>
       </c>
       <c r="R27" t="n">
-        <v>6761257</v>
+        <v>6761309</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3496,45 +3501,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128990886</v>
+        <v>128994100</v>
       </c>
       <c r="B28" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493487</v>
+        <v>493167</v>
       </c>
       <c r="R28" t="n">
-        <v>6761281</v>
+        <v>6761257</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3566,7 +3571,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3576,12 +3581,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Sumpskogskaraktär i området här.</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3608,32 +3608,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128995396</v>
+        <v>128998878</v>
       </c>
       <c r="B29" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492992</v>
+        <v>492993</v>
       </c>
       <c r="R29" t="n">
-        <v>6761309</v>
+        <v>6761002</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3822,32 +3822,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128998878</v>
+        <v>128995396</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492993</v>
+        <v>492992</v>
       </c>
       <c r="R31" t="n">
-        <v>6761002</v>
+        <v>6761309</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3929,45 +3929,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128991481</v>
+        <v>128994846</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493300</v>
+        <v>493013</v>
       </c>
       <c r="R32" t="n">
-        <v>6761215</v>
+        <v>6761220</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4036,45 +4036,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128994846</v>
+        <v>128991481</v>
       </c>
       <c r="B33" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493013</v>
+        <v>493300</v>
       </c>
       <c r="R33" t="n">
-        <v>6761220</v>
+        <v>6761215</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4250,10 +4250,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128991964</v>
+        <v>128993887</v>
       </c>
       <c r="B35" t="n">
-        <v>58153</v>
+        <v>79034</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4261,42 +4261,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493252</v>
+        <v>493167</v>
       </c>
       <c r="R35" t="n">
-        <v>6761277</v>
+        <v>6761257</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4325,7 +4320,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4335,7 +4330,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4362,10 +4357,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128999032</v>
+        <v>128997967</v>
       </c>
       <c r="B36" t="n">
-        <v>58153</v>
+        <v>79034</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4373,39 +4368,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493048</v>
+        <v>492949</v>
       </c>
       <c r="R36" t="n">
-        <v>6761092</v>
+        <v>6761266</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4437,7 +4427,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4447,7 +4437,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4474,10 +4469,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128991491</v>
+        <v>128994367</v>
       </c>
       <c r="B37" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4485,39 +4480,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493290</v>
+        <v>493118</v>
       </c>
       <c r="R37" t="n">
-        <v>6761213</v>
+        <v>6761310</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4549,7 +4539,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4559,7 +4549,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4693,10 +4683,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128993887</v>
+        <v>128991491</v>
       </c>
       <c r="B39" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4704,34 +4694,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493167</v>
+        <v>493290</v>
       </c>
       <c r="R39" t="n">
-        <v>6761257</v>
+        <v>6761213</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4763,7 +4758,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4773,7 +4768,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4800,10 +4795,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128994367</v>
+        <v>128991964</v>
       </c>
       <c r="B40" t="n">
-        <v>79034</v>
+        <v>58153</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4811,37 +4806,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493118</v>
+        <v>493252</v>
       </c>
       <c r="R40" t="n">
-        <v>6761310</v>
+        <v>6761277</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4907,10 +4907,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128997967</v>
+        <v>128999032</v>
       </c>
       <c r="B41" t="n">
-        <v>79034</v>
+        <v>58153</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4918,34 +4918,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492949</v>
+        <v>493048</v>
       </c>
       <c r="R41" t="n">
-        <v>6761266</v>
+        <v>6761092</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4977,7 +4982,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4987,12 +4992,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5126,7 +5126,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128999732</v>
+        <v>128994946</v>
       </c>
       <c r="B43" t="n">
         <v>79034</v>
@@ -5157,14 +5157,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493327</v>
+        <v>492986</v>
       </c>
       <c r="R43" t="n">
-        <v>6761155</v>
+        <v>6761194</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5340,7 +5340,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128994946</v>
+        <v>128999732</v>
       </c>
       <c r="B45" t="n">
         <v>79034</v>
@@ -5371,14 +5371,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>492986</v>
+        <v>493327</v>
       </c>
       <c r="R45" t="n">
-        <v>6761194</v>
+        <v>6761155</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5554,50 +5554,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128991653</v>
+        <v>128999673</v>
       </c>
       <c r="B47" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493295</v>
+        <v>493255</v>
       </c>
       <c r="R47" t="n">
-        <v>6761257</v>
+        <v>6761127</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5629,7 +5624,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5639,7 +5634,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5666,10 +5661,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128994503</v>
+        <v>128998610</v>
       </c>
       <c r="B48" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5677,39 +5672,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493047</v>
+        <v>492993</v>
       </c>
       <c r="R48" t="n">
-        <v>6761263</v>
+        <v>6761086</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5741,7 +5731,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5751,7 +5741,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5778,10 +5768,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128998610</v>
+        <v>128991653</v>
       </c>
       <c r="B49" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5789,34 +5779,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492993</v>
+        <v>493295</v>
       </c>
       <c r="R49" t="n">
-        <v>6761086</v>
+        <v>6761257</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5848,7 +5843,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5858,7 +5853,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5885,45 +5880,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128999673</v>
+        <v>128994503</v>
       </c>
       <c r="B50" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493255</v>
+        <v>493047</v>
       </c>
       <c r="R50" t="n">
-        <v>6761127</v>
+        <v>6761263</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5992,10 +5992,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128994661</v>
+        <v>128999627</v>
       </c>
       <c r="B51" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6003,39 +6003,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493048</v>
+        <v>493222</v>
       </c>
       <c r="R51" t="n">
-        <v>6761242</v>
+        <v>6761162</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6067,7 +6062,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6077,7 +6072,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6104,10 +6099,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128999627</v>
+        <v>128994661</v>
       </c>
       <c r="B52" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6115,34 +6110,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493222</v>
+        <v>493048</v>
       </c>
       <c r="R52" t="n">
-        <v>6761162</v>
+        <v>6761242</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6211,10 +6211,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128998638</v>
+        <v>128998999</v>
       </c>
       <c r="B53" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6222,39 +6222,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>492971</v>
+        <v>493048</v>
       </c>
       <c r="R53" t="n">
-        <v>6761075</v>
+        <v>6761092</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6430,10 +6425,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128998999</v>
+        <v>128998638</v>
       </c>
       <c r="B55" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6441,34 +6436,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>493048</v>
+        <v>492971</v>
       </c>
       <c r="R55" t="n">
-        <v>6761092</v>
+        <v>6761075</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6978,7 +6978,7 @@
         <v>129015883</v>
       </c>
       <c r="B60" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 41794-2025 artfynd.xlsx
+++ b/artfynd/A 41794-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128991347</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128998779</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128993314</v>
+        <v>128999532</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,14 +920,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493165</v>
+        <v>493157</v>
       </c>
       <c r="R4" t="n">
-        <v>6761309</v>
+        <v>6761137</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128997543</v>
+        <v>128993314</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492963</v>
+        <v>493165</v>
       </c>
       <c r="R5" t="n">
-        <v>6761283</v>
+        <v>6761309</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128992649</v>
+        <v>128997543</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,14 +1139,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493247</v>
+        <v>492963</v>
       </c>
       <c r="R6" t="n">
-        <v>6761309</v>
+        <v>6761283</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128994822</v>
+        <v>128992649</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,14 +1246,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493022</v>
+        <v>493247</v>
       </c>
       <c r="R7" t="n">
-        <v>6761226</v>
+        <v>6761309</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128999532</v>
+        <v>128994822</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,14 +1353,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493157</v>
+        <v>493022</v>
       </c>
       <c r="R8" t="n">
-        <v>6761137</v>
+        <v>6761226</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,12 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128998367</v>
+        <v>128999256</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492928</v>
+        <v>493048</v>
       </c>
       <c r="R9" t="n">
-        <v>6761141</v>
+        <v>6761242</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128999256</v>
+        <v>128998367</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493048</v>
+        <v>492928</v>
       </c>
       <c r="R10" t="n">
-        <v>6761242</v>
+        <v>6761141</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,7 +1646,7 @@
         <v>128999351</v>
       </c>
       <c r="B11" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1750,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128991903</v>
+        <v>128998263</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,34 +1761,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493287</v>
+        <v>492885</v>
       </c>
       <c r="R12" t="n">
-        <v>6761277</v>
+        <v>6761180</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1830,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1857,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128998025</v>
+        <v>128999613</v>
       </c>
       <c r="B13" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,34 +1873,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492895</v>
+        <v>493205</v>
       </c>
       <c r="R13" t="n">
-        <v>6761212</v>
+        <v>6761180</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1937,7 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1964,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128991923</v>
+        <v>128997799</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1975,34 +1985,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493277</v>
+        <v>492929</v>
       </c>
       <c r="R14" t="n">
-        <v>6761265</v>
+        <v>6761272</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +2049,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2044,7 +2059,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,7 +2086,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128998263</v>
+        <v>128998274</v>
       </c>
       <c r="B15" t="n">
         <v>57720</v>
@@ -2111,10 +2126,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492885</v>
+        <v>492894</v>
       </c>
       <c r="R15" t="n">
-        <v>6761180</v>
+        <v>6761171</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128999613</v>
+        <v>128998025</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,39 +2209,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493205</v>
+        <v>492895</v>
       </c>
       <c r="R16" t="n">
-        <v>6761180</v>
+        <v>6761212</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,7 +2268,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2268,7 +2278,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128997799</v>
+        <v>128991923</v>
       </c>
       <c r="B17" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2306,39 +2316,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492929</v>
+        <v>493277</v>
       </c>
       <c r="R17" t="n">
-        <v>6761272</v>
+        <v>6761265</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2375,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2385,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,10 +2412,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128998274</v>
+        <v>128991903</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2418,39 +2423,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492894</v>
+        <v>493287</v>
       </c>
       <c r="R18" t="n">
-        <v>6761171</v>
+        <v>6761277</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2522,7 +2522,7 @@
         <v>128990939</v>
       </c>
       <c r="B19" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2631,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128991027</v>
+        <v>128994202</v>
       </c>
       <c r="B20" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2662,14 +2662,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493464</v>
+        <v>493144</v>
       </c>
       <c r="R20" t="n">
-        <v>6761291</v>
+        <v>6761263</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2741,7 +2741,7 @@
         <v>128998438</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2845,10 +2845,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128994202</v>
+        <v>128991027</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2876,14 +2876,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493144</v>
+        <v>493464</v>
       </c>
       <c r="R22" t="n">
-        <v>6761263</v>
+        <v>6761291</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3067,7 +3067,7 @@
         <v>128998223</v>
       </c>
       <c r="B24" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>128998201</v>
       </c>
       <c r="B25" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3278,10 +3278,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128990886</v>
+        <v>128995392</v>
       </c>
       <c r="B26" t="n">
-        <v>79034</v>
+        <v>91546</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3289,34 +3289,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493487</v>
+        <v>492992</v>
       </c>
       <c r="R26" t="n">
-        <v>6761281</v>
+        <v>6761309</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3348,7 +3352,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3358,12 +3362,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Sumpskogskaraktär i området här.</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3390,10 +3389,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128995392</v>
+        <v>128990886</v>
       </c>
       <c r="B27" t="n">
-        <v>91543</v>
+        <v>79035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3401,38 +3400,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492992</v>
+        <v>493487</v>
       </c>
       <c r="R27" t="n">
-        <v>6761309</v>
+        <v>6761281</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3464,7 +3459,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3474,7 +3469,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Sumpskogskaraktär i området här.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3608,32 +3608,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128998878</v>
+        <v>128995396</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492993</v>
+        <v>492992</v>
       </c>
       <c r="R29" t="n">
-        <v>6761002</v>
+        <v>6761309</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3718,7 +3718,7 @@
         <v>128994343</v>
       </c>
       <c r="B30" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3822,32 +3822,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128995396</v>
+        <v>128998878</v>
       </c>
       <c r="B31" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492992</v>
+        <v>492993</v>
       </c>
       <c r="R31" t="n">
-        <v>6761309</v>
+        <v>6761002</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3929,45 +3929,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128994846</v>
+        <v>128991481</v>
       </c>
       <c r="B32" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493013</v>
+        <v>493300</v>
       </c>
       <c r="R32" t="n">
-        <v>6761220</v>
+        <v>6761215</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4036,45 +4036,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128991481</v>
+        <v>128994846</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493300</v>
+        <v>493013</v>
       </c>
       <c r="R33" t="n">
-        <v>6761215</v>
+        <v>6761220</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4146,7 +4146,7 @@
         <v>128994977</v>
       </c>
       <c r="B34" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4250,10 +4250,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128993887</v>
+        <v>128991491</v>
       </c>
       <c r="B35" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4261,34 +4261,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493167</v>
+        <v>493290</v>
       </c>
       <c r="R35" t="n">
-        <v>6761257</v>
+        <v>6761213</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4320,7 +4325,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4330,7 +4335,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4357,10 +4362,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128997967</v>
+        <v>128994864</v>
       </c>
       <c r="B36" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4392,10 +4397,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492949</v>
+        <v>493021</v>
       </c>
       <c r="R36" t="n">
-        <v>6761266</v>
+        <v>6761214</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4438,11 +4443,6 @@
       <c r="AB36" t="inlineStr">
         <is>
           <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4469,10 +4469,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128994367</v>
+        <v>128993887</v>
       </c>
       <c r="B37" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493118</v>
+        <v>493167</v>
       </c>
       <c r="R37" t="n">
-        <v>6761310</v>
+        <v>6761257</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4576,10 +4576,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128994864</v>
+        <v>128994367</v>
       </c>
       <c r="B38" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493021</v>
+        <v>493118</v>
       </c>
       <c r="R38" t="n">
-        <v>6761214</v>
+        <v>6761310</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4683,10 +4683,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128991491</v>
+        <v>128997967</v>
       </c>
       <c r="B39" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4694,39 +4694,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493290</v>
+        <v>492949</v>
       </c>
       <c r="R39" t="n">
-        <v>6761213</v>
+        <v>6761266</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4758,7 +4753,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4768,7 +4763,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5022,7 +5022,7 @@
         <v>128995173</v>
       </c>
       <c r="B42" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5126,10 +5126,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128994946</v>
+        <v>128994294</v>
       </c>
       <c r="B43" t="n">
-        <v>79034</v>
+        <v>79654</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5137,21 +5137,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5161,10 +5161,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492986</v>
+        <v>493144</v>
       </c>
       <c r="R43" t="n">
-        <v>6761194</v>
+        <v>6761263</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5233,10 +5233,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128991661</v>
+        <v>128999732</v>
       </c>
       <c r="B44" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5268,10 +5268,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>493295</v>
+        <v>493327</v>
       </c>
       <c r="R44" t="n">
-        <v>6761257</v>
+        <v>6761155</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5340,10 +5340,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128999732</v>
+        <v>128991661</v>
       </c>
       <c r="B45" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5375,10 +5375,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>493327</v>
+        <v>493295</v>
       </c>
       <c r="R45" t="n">
-        <v>6761155</v>
+        <v>6761257</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5447,10 +5447,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128994294</v>
+        <v>128994946</v>
       </c>
       <c r="B46" t="n">
-        <v>79653</v>
+        <v>79035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5458,21 +5458,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5482,10 +5482,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493144</v>
+        <v>492986</v>
       </c>
       <c r="R46" t="n">
-        <v>6761263</v>
+        <v>6761194</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5554,45 +5554,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128999673</v>
+        <v>128991653</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493255</v>
+        <v>493295</v>
       </c>
       <c r="R47" t="n">
-        <v>6761127</v>
+        <v>6761257</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5624,7 +5629,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5634,7 +5639,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5661,10 +5666,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128998610</v>
+        <v>128994503</v>
       </c>
       <c r="B48" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5672,34 +5677,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492993</v>
+        <v>493047</v>
       </c>
       <c r="R48" t="n">
-        <v>6761086</v>
+        <v>6761263</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5731,7 +5741,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5741,7 +5751,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5768,10 +5778,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128991653</v>
+        <v>128998610</v>
       </c>
       <c r="B49" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5779,39 +5789,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493295</v>
+        <v>492993</v>
       </c>
       <c r="R49" t="n">
-        <v>6761257</v>
+        <v>6761086</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5843,7 +5848,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5853,7 +5858,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5880,50 +5885,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128994503</v>
+        <v>128999673</v>
       </c>
       <c r="B50" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493047</v>
+        <v>493255</v>
       </c>
       <c r="R50" t="n">
-        <v>6761263</v>
+        <v>6761127</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5995,7 +5995,7 @@
         <v>128999627</v>
       </c>
       <c r="B51" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6211,10 +6211,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128998999</v>
+        <v>128998638</v>
       </c>
       <c r="B53" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6222,34 +6222,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>493048</v>
+        <v>492971</v>
       </c>
       <c r="R53" t="n">
-        <v>6761092</v>
+        <v>6761075</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6321,7 +6326,7 @@
         <v>128991818</v>
       </c>
       <c r="B54" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6425,10 +6430,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128998638</v>
+        <v>128998999</v>
       </c>
       <c r="B55" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6436,39 +6441,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>492971</v>
+        <v>493048</v>
       </c>
       <c r="R55" t="n">
-        <v>6761075</v>
+        <v>6761092</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6652,7 +6652,7 @@
         <v>128995292</v>
       </c>
       <c r="B57" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>128994922</v>
       </c>
       <c r="B59" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>129015883</v>
       </c>
       <c r="B60" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 41794-2025 artfynd.xlsx
+++ b/artfynd/A 41794-2025 artfynd.xlsx
@@ -1750,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128998263</v>
+        <v>128998025</v>
       </c>
       <c r="B12" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,39 +1761,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492885</v>
+        <v>492895</v>
       </c>
       <c r="R12" t="n">
-        <v>6761180</v>
+        <v>6761212</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1862,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128999613</v>
+        <v>128991923</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,39 +1868,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493205</v>
+        <v>493277</v>
       </c>
       <c r="R13" t="n">
-        <v>6761180</v>
+        <v>6761265</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,7 +1927,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1937,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,10 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128997799</v>
+        <v>128991903</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,39 +1975,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492929</v>
+        <v>493287</v>
       </c>
       <c r="R14" t="n">
-        <v>6761272</v>
+        <v>6761277</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,7 +2034,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2059,7 +2044,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,7 +2071,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128998274</v>
+        <v>128998263</v>
       </c>
       <c r="B15" t="n">
         <v>57720</v>
@@ -2126,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492894</v>
+        <v>492885</v>
       </c>
       <c r="R15" t="n">
-        <v>6761171</v>
+        <v>6761180</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2198,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128998025</v>
+        <v>128999613</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,34 +2194,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492895</v>
+        <v>493205</v>
       </c>
       <c r="R16" t="n">
-        <v>6761212</v>
+        <v>6761180</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2278,7 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2305,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128991923</v>
+        <v>128997799</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2316,34 +2306,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493277</v>
+        <v>492929</v>
       </c>
       <c r="R17" t="n">
-        <v>6761265</v>
+        <v>6761272</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2375,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2385,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2412,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128991903</v>
+        <v>128998274</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,34 +2418,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493287</v>
+        <v>492894</v>
       </c>
       <c r="R18" t="n">
-        <v>6761277</v>
+        <v>6761171</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2952,10 +2952,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128991711</v>
+        <v>128998223</v>
       </c>
       <c r="B23" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2963,39 +2963,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493310</v>
+        <v>492885</v>
       </c>
       <c r="R23" t="n">
-        <v>6761241</v>
+        <v>6761180</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3027,7 +3022,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3037,7 +3032,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3064,7 +3059,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128998223</v>
+        <v>128998201</v>
       </c>
       <c r="B24" t="n">
         <v>79035</v>
@@ -3099,10 +3094,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492885</v>
+        <v>492877</v>
       </c>
       <c r="R24" t="n">
-        <v>6761180</v>
+        <v>6761211</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3171,10 +3166,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128998201</v>
+        <v>128991711</v>
       </c>
       <c r="B25" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3182,34 +3177,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492877</v>
+        <v>493310</v>
       </c>
       <c r="R25" t="n">
-        <v>6761211</v>
+        <v>6761241</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3278,49 +3278,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128995392</v>
+        <v>128994100</v>
       </c>
       <c r="B26" t="n">
-        <v>91546</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492992</v>
+        <v>493167</v>
       </c>
       <c r="R26" t="n">
-        <v>6761309</v>
+        <v>6761257</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3389,10 +3385,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128990886</v>
+        <v>128995392</v>
       </c>
       <c r="B27" t="n">
-        <v>79035</v>
+        <v>91546</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3400,34 +3396,38 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493487</v>
+        <v>492992</v>
       </c>
       <c r="R27" t="n">
-        <v>6761281</v>
+        <v>6761309</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3469,12 +3469,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Sumpskogskaraktär i området här.</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3501,45 +3496,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128994100</v>
+        <v>128990886</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493167</v>
+        <v>493487</v>
       </c>
       <c r="R28" t="n">
-        <v>6761257</v>
+        <v>6761281</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3571,7 +3566,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3581,7 +3576,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Sumpskogskaraktär i området här.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3608,32 +3608,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128995396</v>
+        <v>128998878</v>
       </c>
       <c r="B29" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492992</v>
+        <v>492993</v>
       </c>
       <c r="R29" t="n">
-        <v>6761309</v>
+        <v>6761002</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3715,7 +3715,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128994343</v>
+        <v>128995396</v>
       </c>
       <c r="B30" t="n">
         <v>79035</v>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493103</v>
+        <v>492992</v>
       </c>
       <c r="R30" t="n">
-        <v>6761270</v>
+        <v>6761309</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3822,32 +3822,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128998878</v>
+        <v>128994343</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492993</v>
+        <v>493103</v>
       </c>
       <c r="R31" t="n">
-        <v>6761002</v>
+        <v>6761270</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3929,45 +3929,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128991481</v>
+        <v>128994846</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493300</v>
+        <v>493013</v>
       </c>
       <c r="R32" t="n">
-        <v>6761215</v>
+        <v>6761220</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4036,45 +4036,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128994846</v>
+        <v>128991481</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493013</v>
+        <v>493300</v>
       </c>
       <c r="R33" t="n">
-        <v>6761220</v>
+        <v>6761215</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4250,10 +4250,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128991491</v>
+        <v>128994864</v>
       </c>
       <c r="B35" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4261,39 +4261,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493290</v>
+        <v>493021</v>
       </c>
       <c r="R35" t="n">
-        <v>6761213</v>
+        <v>6761214</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4325,7 +4320,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4335,7 +4330,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4362,7 +4357,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128994864</v>
+        <v>128993887</v>
       </c>
       <c r="B36" t="n">
         <v>79035</v>
@@ -4397,10 +4392,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493021</v>
+        <v>493167</v>
       </c>
       <c r="R36" t="n">
-        <v>6761214</v>
+        <v>6761257</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4469,7 +4464,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128993887</v>
+        <v>128994367</v>
       </c>
       <c r="B37" t="n">
         <v>79035</v>
@@ -4504,10 +4499,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493167</v>
+        <v>493118</v>
       </c>
       <c r="R37" t="n">
-        <v>6761257</v>
+        <v>6761310</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4576,7 +4571,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128994367</v>
+        <v>128997967</v>
       </c>
       <c r="B38" t="n">
         <v>79035</v>
@@ -4611,10 +4606,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493118</v>
+        <v>492949</v>
       </c>
       <c r="R38" t="n">
-        <v>6761310</v>
+        <v>6761266</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4657,6 +4652,11 @@
       <c r="AB38" t="inlineStr">
         <is>
           <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4683,10 +4683,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128997967</v>
+        <v>128991491</v>
       </c>
       <c r="B39" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4694,34 +4694,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492949</v>
+        <v>493290</v>
       </c>
       <c r="R39" t="n">
-        <v>6761266</v>
+        <v>6761213</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4753,7 +4758,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4763,12 +4768,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4795,7 +4795,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128991964</v>
+        <v>128999032</v>
       </c>
       <c r="B40" t="n">
         <v>58153</v>
@@ -4831,17 +4831,17 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493252</v>
+        <v>493048</v>
       </c>
       <c r="R40" t="n">
-        <v>6761277</v>
+        <v>6761092</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4907,7 +4907,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128999032</v>
+        <v>128991964</v>
       </c>
       <c r="B41" t="n">
         <v>58153</v>
@@ -4943,17 +4943,17 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493048</v>
+        <v>493252</v>
       </c>
       <c r="R41" t="n">
-        <v>6761092</v>
+        <v>6761277</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5126,10 +5126,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128994294</v>
+        <v>128999732</v>
       </c>
       <c r="B43" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5137,34 +5137,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493144</v>
+        <v>493327</v>
       </c>
       <c r="R43" t="n">
-        <v>6761263</v>
+        <v>6761155</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5233,7 +5233,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128999732</v>
+        <v>128991661</v>
       </c>
       <c r="B44" t="n">
         <v>79035</v>
@@ -5268,10 +5268,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>493327</v>
+        <v>493295</v>
       </c>
       <c r="R44" t="n">
-        <v>6761155</v>
+        <v>6761257</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5340,7 +5340,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128991661</v>
+        <v>128994946</v>
       </c>
       <c r="B45" t="n">
         <v>79035</v>
@@ -5371,14 +5371,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>493295</v>
+        <v>492986</v>
       </c>
       <c r="R45" t="n">
-        <v>6761257</v>
+        <v>6761194</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5447,10 +5447,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128994946</v>
+        <v>128994294</v>
       </c>
       <c r="B46" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5458,21 +5458,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5482,10 +5482,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492986</v>
+        <v>493144</v>
       </c>
       <c r="R46" t="n">
-        <v>6761194</v>
+        <v>6761263</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5554,50 +5554,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128991653</v>
+        <v>128999673</v>
       </c>
       <c r="B47" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493295</v>
+        <v>493255</v>
       </c>
       <c r="R47" t="n">
-        <v>6761257</v>
+        <v>6761127</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5629,7 +5624,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5639,7 +5634,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5666,10 +5661,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128994503</v>
+        <v>128998610</v>
       </c>
       <c r="B48" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5677,39 +5672,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493047</v>
+        <v>492993</v>
       </c>
       <c r="R48" t="n">
-        <v>6761263</v>
+        <v>6761086</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5741,7 +5731,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5751,7 +5741,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5778,10 +5768,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128998610</v>
+        <v>128991653</v>
       </c>
       <c r="B49" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5789,34 +5779,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492993</v>
+        <v>493295</v>
       </c>
       <c r="R49" t="n">
-        <v>6761086</v>
+        <v>6761257</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5848,7 +5843,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5858,7 +5853,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5885,45 +5880,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128999673</v>
+        <v>128994503</v>
       </c>
       <c r="B50" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493255</v>
+        <v>493047</v>
       </c>
       <c r="R50" t="n">
-        <v>6761127</v>
+        <v>6761263</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6211,10 +6211,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128998638</v>
+        <v>128991818</v>
       </c>
       <c r="B53" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6222,39 +6222,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>492971</v>
+        <v>493312</v>
       </c>
       <c r="R53" t="n">
-        <v>6761075</v>
+        <v>6761262</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6286,7 +6281,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6296,7 +6291,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6323,7 +6318,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128991818</v>
+        <v>128998999</v>
       </c>
       <c r="B54" t="n">
         <v>79035</v>
@@ -6354,14 +6349,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493312</v>
+        <v>493048</v>
       </c>
       <c r="R54" t="n">
-        <v>6761262</v>
+        <v>6761092</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6393,7 +6388,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6403,7 +6398,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6430,10 +6425,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128998999</v>
+        <v>128998638</v>
       </c>
       <c r="B55" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6441,34 +6436,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>493048</v>
+        <v>492971</v>
       </c>
       <c r="R55" t="n">
-        <v>6761092</v>
+        <v>6761075</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6649,48 +6649,53 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128995292</v>
+        <v>128990627</v>
       </c>
       <c r="B57" t="n">
-        <v>79035</v>
+        <v>58093</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>492996</v>
+        <v>493483</v>
       </c>
       <c r="R57" t="n">
-        <v>6761284</v>
+        <v>6761261</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6719,7 +6724,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6729,7 +6734,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6756,53 +6761,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128990627</v>
+        <v>128995292</v>
       </c>
       <c r="B58" t="n">
-        <v>58093</v>
+        <v>79035</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>493483</v>
+        <v>492996</v>
       </c>
       <c r="R58" t="n">
-        <v>6761261</v>
+        <v>6761284</v>
       </c>
       <c r="S58" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 41794-2025 artfynd.xlsx
+++ b/artfynd/A 41794-2025 artfynd.xlsx
@@ -3278,45 +3278,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128994100</v>
+        <v>128995392</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>91546</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493167</v>
+        <v>492992</v>
       </c>
       <c r="R26" t="n">
-        <v>6761257</v>
+        <v>6761309</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3385,10 +3389,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128995392</v>
+        <v>128990886</v>
       </c>
       <c r="B27" t="n">
-        <v>91546</v>
+        <v>79035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3396,38 +3400,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492992</v>
+        <v>493487</v>
       </c>
       <c r="R27" t="n">
-        <v>6761309</v>
+        <v>6761281</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3469,7 +3469,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Sumpskogskaraktär i området här.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3496,45 +3501,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128990886</v>
+        <v>128994100</v>
       </c>
       <c r="B28" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493487</v>
+        <v>493167</v>
       </c>
       <c r="R28" t="n">
-        <v>6761281</v>
+        <v>6761257</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3566,7 +3571,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3576,12 +3581,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Sumpskogskaraktär i området här.</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3608,32 +3608,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128998878</v>
+        <v>128995396</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492993</v>
+        <v>492992</v>
       </c>
       <c r="R29" t="n">
-        <v>6761002</v>
+        <v>6761309</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3715,7 +3715,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128995396</v>
+        <v>128994343</v>
       </c>
       <c r="B30" t="n">
         <v>79035</v>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492992</v>
+        <v>493103</v>
       </c>
       <c r="R30" t="n">
-        <v>6761309</v>
+        <v>6761270</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3822,32 +3822,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128994343</v>
+        <v>128998878</v>
       </c>
       <c r="B31" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493103</v>
+        <v>492993</v>
       </c>
       <c r="R31" t="n">
-        <v>6761270</v>
+        <v>6761002</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 41794-2025 artfynd.xlsx
+++ b/artfynd/A 41794-2025 artfynd.xlsx
@@ -1429,7 +1429,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128999256</v>
+        <v>128999351</v>
       </c>
       <c r="B9" t="n">
         <v>79035</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493048</v>
+        <v>493087</v>
       </c>
       <c r="R9" t="n">
-        <v>6761242</v>
+        <v>6761166</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128998367</v>
+        <v>128999256</v>
       </c>
       <c r="B10" t="n">
         <v>79035</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492928</v>
+        <v>493048</v>
       </c>
       <c r="R10" t="n">
-        <v>6761141</v>
+        <v>6761242</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128999351</v>
+        <v>128998367</v>
       </c>
       <c r="B11" t="n">
         <v>79035</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493087</v>
+        <v>492928</v>
       </c>
       <c r="R11" t="n">
-        <v>6761166</v>
+        <v>6761141</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,45 +1750,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128998025</v>
+        <v>128990939</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>97530</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492895</v>
+        <v>493487</v>
       </c>
       <c r="R12" t="n">
-        <v>6761212</v>
+        <v>6761281</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1830,7 +1830,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1857,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128991923</v>
+        <v>128998263</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,34 +1873,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493277</v>
+        <v>492885</v>
       </c>
       <c r="R13" t="n">
-        <v>6761265</v>
+        <v>6761180</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1937,7 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1964,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128991903</v>
+        <v>128999613</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1975,34 +1985,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493287</v>
+        <v>493205</v>
       </c>
       <c r="R14" t="n">
-        <v>6761277</v>
+        <v>6761180</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +2049,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2044,7 +2059,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128998263</v>
+        <v>128998025</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2082,39 +2097,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492885</v>
+        <v>492895</v>
       </c>
       <c r="R15" t="n">
-        <v>6761180</v>
+        <v>6761212</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128999613</v>
+        <v>128991923</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,39 +2204,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493205</v>
+        <v>493277</v>
       </c>
       <c r="R16" t="n">
-        <v>6761180</v>
+        <v>6761265</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,7 +2263,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2268,7 +2273,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128997799</v>
+        <v>128991903</v>
       </c>
       <c r="B17" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2306,39 +2311,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492929</v>
+        <v>493287</v>
       </c>
       <c r="R17" t="n">
-        <v>6761272</v>
+        <v>6761277</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,7 +2407,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128998274</v>
+        <v>128997799</v>
       </c>
       <c r="B18" t="n">
         <v>57720</v>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492894</v>
+        <v>492929</v>
       </c>
       <c r="R18" t="n">
-        <v>6761171</v>
+        <v>6761272</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2519,45 +2519,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128990939</v>
+        <v>128998274</v>
       </c>
       <c r="B19" t="n">
-        <v>97530</v>
+        <v>57720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493487</v>
+        <v>492894</v>
       </c>
       <c r="R19" t="n">
-        <v>6761281</v>
+        <v>6761171</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,7 +2594,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2599,12 +2604,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3278,10 +3278,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128995392</v>
+        <v>128990886</v>
       </c>
       <c r="B26" t="n">
-        <v>91546</v>
+        <v>79035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3289,38 +3289,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492992</v>
+        <v>493487</v>
       </c>
       <c r="R26" t="n">
-        <v>6761309</v>
+        <v>6761281</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3352,7 +3348,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3362,7 +3358,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Sumpskogskaraktär i området här.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3389,10 +3390,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128990886</v>
+        <v>128995392</v>
       </c>
       <c r="B27" t="n">
-        <v>79035</v>
+        <v>91546</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3400,34 +3401,38 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493487</v>
+        <v>492992</v>
       </c>
       <c r="R27" t="n">
-        <v>6761281</v>
+        <v>6761309</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3459,7 +3464,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3469,12 +3474,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Sumpskogskaraktär i området här.</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4250,10 +4250,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128994864</v>
+        <v>128999032</v>
       </c>
       <c r="B35" t="n">
-        <v>79035</v>
+        <v>58153</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4261,34 +4261,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493021</v>
+        <v>493048</v>
       </c>
       <c r="R35" t="n">
-        <v>6761214</v>
+        <v>6761092</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4320,7 +4325,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4330,7 +4335,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4357,10 +4362,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128993887</v>
+        <v>128991964</v>
       </c>
       <c r="B36" t="n">
-        <v>79035</v>
+        <v>58153</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4368,37 +4373,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493167</v>
+        <v>493252</v>
       </c>
       <c r="R36" t="n">
-        <v>6761257</v>
+        <v>6761277</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4427,7 +4437,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4437,7 +4447,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4464,10 +4474,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128994367</v>
+        <v>128991491</v>
       </c>
       <c r="B37" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4475,34 +4485,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493118</v>
+        <v>493290</v>
       </c>
       <c r="R37" t="n">
-        <v>6761310</v>
+        <v>6761213</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4534,7 +4549,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4544,7 +4559,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4571,7 +4586,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128997967</v>
+        <v>128994864</v>
       </c>
       <c r="B38" t="n">
         <v>79035</v>
@@ -4606,10 +4621,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>492949</v>
+        <v>493021</v>
       </c>
       <c r="R38" t="n">
-        <v>6761266</v>
+        <v>6761214</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4652,11 +4667,6 @@
       <c r="AB38" t="inlineStr">
         <is>
           <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4683,10 +4693,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128991491</v>
+        <v>128993887</v>
       </c>
       <c r="B39" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4694,39 +4704,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493290</v>
+        <v>493167</v>
       </c>
       <c r="R39" t="n">
-        <v>6761213</v>
+        <v>6761257</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4758,7 +4763,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4768,7 +4773,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4795,10 +4800,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128999032</v>
+        <v>128994367</v>
       </c>
       <c r="B40" t="n">
-        <v>58153</v>
+        <v>79035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4806,39 +4811,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493048</v>
+        <v>493118</v>
       </c>
       <c r="R40" t="n">
-        <v>6761092</v>
+        <v>6761310</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4907,10 +4907,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128991964</v>
+        <v>128997967</v>
       </c>
       <c r="B41" t="n">
-        <v>58153</v>
+        <v>79035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4918,42 +4918,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493252</v>
+        <v>492949</v>
       </c>
       <c r="R41" t="n">
-        <v>6761277</v>
+        <v>6761266</v>
       </c>
       <c r="S41" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4982,7 +4977,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4992,7 +4987,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5554,45 +5554,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128999673</v>
+        <v>128991653</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493255</v>
+        <v>493295</v>
       </c>
       <c r="R47" t="n">
-        <v>6761127</v>
+        <v>6761257</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5624,7 +5629,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5634,7 +5639,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5661,10 +5666,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128998610</v>
+        <v>128994503</v>
       </c>
       <c r="B48" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5672,34 +5677,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492993</v>
+        <v>493047</v>
       </c>
       <c r="R48" t="n">
-        <v>6761086</v>
+        <v>6761263</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5731,7 +5741,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5741,7 +5751,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5768,10 +5778,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128991653</v>
+        <v>128998610</v>
       </c>
       <c r="B49" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5779,39 +5789,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493295</v>
+        <v>492993</v>
       </c>
       <c r="R49" t="n">
-        <v>6761257</v>
+        <v>6761086</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5843,7 +5848,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5853,7 +5858,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5880,50 +5885,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128994503</v>
+        <v>128999673</v>
       </c>
       <c r="B50" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493047</v>
+        <v>493255</v>
       </c>
       <c r="R50" t="n">
-        <v>6761263</v>
+        <v>6761127</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 41794-2025 artfynd.xlsx
+++ b/artfynd/A 41794-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128991347</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128998779</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128999532</v>
+        <v>128993314</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,14 +920,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493157</v>
+        <v>493165</v>
       </c>
       <c r="R4" t="n">
-        <v>6761137</v>
+        <v>6761309</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128993314</v>
+        <v>128997543</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493165</v>
+        <v>492963</v>
       </c>
       <c r="R5" t="n">
-        <v>6761309</v>
+        <v>6761283</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128997543</v>
+        <v>128992649</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,14 +1134,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492963</v>
+        <v>493247</v>
       </c>
       <c r="R6" t="n">
-        <v>6761283</v>
+        <v>6761309</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128992649</v>
+        <v>128994822</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,14 +1241,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493247</v>
+        <v>493022</v>
       </c>
       <c r="R7" t="n">
-        <v>6761309</v>
+        <v>6761226</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128994822</v>
+        <v>128999532</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,14 +1348,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493022</v>
+        <v>493157</v>
       </c>
       <c r="R8" t="n">
-        <v>6761226</v>
+        <v>6761137</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,7 +1397,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128999351</v>
+        <v>128998367</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493087</v>
+        <v>492928</v>
       </c>
       <c r="R9" t="n">
-        <v>6761166</v>
+        <v>6761141</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,7 +1539,7 @@
         <v>128999256</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128998367</v>
+        <v>128999351</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492928</v>
+        <v>493087</v>
       </c>
       <c r="R11" t="n">
-        <v>6761141</v>
+        <v>6761166</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,45 +1750,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128990939</v>
+        <v>128998263</v>
       </c>
       <c r="B12" t="n">
-        <v>97530</v>
+        <v>57722</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493487</v>
+        <v>492885</v>
       </c>
       <c r="R12" t="n">
-        <v>6761281</v>
+        <v>6761180</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1830,12 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128998263</v>
+        <v>128999613</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492885</v>
+        <v>493205</v>
       </c>
       <c r="R13" t="n">
         <v>6761180</v>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128999613</v>
+        <v>128997799</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493205</v>
+        <v>492929</v>
       </c>
       <c r="R14" t="n">
-        <v>6761180</v>
+        <v>6761272</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128998025</v>
+        <v>128998274</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,34 +2097,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492895</v>
+        <v>492894</v>
       </c>
       <c r="R15" t="n">
-        <v>6761212</v>
+        <v>6761171</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2193,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128991923</v>
+        <v>128991903</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2228,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493277</v>
+        <v>493287</v>
       </c>
       <c r="R16" t="n">
-        <v>6761265</v>
+        <v>6761277</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2300,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128991903</v>
+        <v>128998025</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2331,14 +2336,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493287</v>
+        <v>492895</v>
       </c>
       <c r="R17" t="n">
-        <v>6761277</v>
+        <v>6761212</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2375,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2385,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,10 +2412,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128997799</v>
+        <v>128991923</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2418,39 +2423,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492929</v>
+        <v>493277</v>
       </c>
       <c r="R18" t="n">
-        <v>6761272</v>
+        <v>6761265</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2519,50 +2519,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128998274</v>
+        <v>128990939</v>
       </c>
       <c r="B19" t="n">
-        <v>57720</v>
+        <v>97540</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492894</v>
+        <v>493487</v>
       </c>
       <c r="R19" t="n">
-        <v>6761171</v>
+        <v>6761281</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2594,7 +2589,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2604,7 +2599,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2631,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128994202</v>
+        <v>128991027</v>
       </c>
       <c r="B20" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2662,14 +2662,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493144</v>
+        <v>493464</v>
       </c>
       <c r="R20" t="n">
-        <v>6761263</v>
+        <v>6761291</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2741,7 +2741,7 @@
         <v>128998438</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2845,10 +2845,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128991027</v>
+        <v>128994202</v>
       </c>
       <c r="B22" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2876,14 +2876,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493464</v>
+        <v>493144</v>
       </c>
       <c r="R22" t="n">
-        <v>6761291</v>
+        <v>6761263</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2955,7 +2955,7 @@
         <v>128998223</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>128998201</v>
       </c>
       <c r="B24" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>128991711</v>
       </c>
       <c r="B25" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>128990886</v>
       </c>
       <c r="B26" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3390,49 +3390,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128995392</v>
+        <v>128994100</v>
       </c>
       <c r="B27" t="n">
-        <v>91546</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492992</v>
+        <v>493167</v>
       </c>
       <c r="R27" t="n">
-        <v>6761309</v>
+        <v>6761257</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3501,45 +3497,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128994100</v>
+        <v>128995392</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>91553</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493167</v>
+        <v>492992</v>
       </c>
       <c r="R28" t="n">
-        <v>6761257</v>
+        <v>6761309</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3608,32 +3608,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128995396</v>
+        <v>128998878</v>
       </c>
       <c r="B29" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492992</v>
+        <v>492993</v>
       </c>
       <c r="R29" t="n">
-        <v>6761309</v>
+        <v>6761002</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3718,7 +3718,7 @@
         <v>128994343</v>
       </c>
       <c r="B30" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3822,32 +3822,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128998878</v>
+        <v>128995396</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492993</v>
+        <v>492992</v>
       </c>
       <c r="R31" t="n">
-        <v>6761002</v>
+        <v>6761309</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3932,7 +3932,7 @@
         <v>128994846</v>
       </c>
       <c r="B32" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>128994977</v>
       </c>
       <c r="B34" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4250,10 +4250,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128999032</v>
+        <v>128991491</v>
       </c>
       <c r="B35" t="n">
-        <v>58153</v>
+        <v>57722</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4261,39 +4261,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103001</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493048</v>
+        <v>493290</v>
       </c>
       <c r="R35" t="n">
-        <v>6761092</v>
+        <v>6761213</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4365,7 +4365,7 @@
         <v>128991964</v>
       </c>
       <c r="B36" t="n">
-        <v>58153</v>
+        <v>58155</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4474,10 +4474,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128991491</v>
+        <v>128999032</v>
       </c>
       <c r="B37" t="n">
-        <v>57720</v>
+        <v>58155</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4485,39 +4485,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493290</v>
+        <v>493048</v>
       </c>
       <c r="R37" t="n">
-        <v>6761213</v>
+        <v>6761092</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4586,10 +4586,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128994864</v>
+        <v>128993887</v>
       </c>
       <c r="B38" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4621,10 +4621,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493021</v>
+        <v>493167</v>
       </c>
       <c r="R38" t="n">
-        <v>6761214</v>
+        <v>6761257</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4693,10 +4693,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128993887</v>
+        <v>128997967</v>
       </c>
       <c r="B39" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493167</v>
+        <v>492949</v>
       </c>
       <c r="R39" t="n">
-        <v>6761257</v>
+        <v>6761266</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4774,6 +4774,11 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4803,7 +4808,7 @@
         <v>128994367</v>
       </c>
       <c r="B40" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4907,10 +4912,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128997967</v>
+        <v>128994864</v>
       </c>
       <c r="B41" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4942,10 +4947,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492949</v>
+        <v>493021</v>
       </c>
       <c r="R41" t="n">
-        <v>6761266</v>
+        <v>6761214</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4988,11 +4993,6 @@
       <c r="AB41" t="inlineStr">
         <is>
           <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5022,7 +5022,7 @@
         <v>128995173</v>
       </c>
       <c r="B42" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5126,10 +5126,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128999732</v>
+        <v>128994294</v>
       </c>
       <c r="B43" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5137,34 +5137,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493327</v>
+        <v>493144</v>
       </c>
       <c r="R43" t="n">
-        <v>6761155</v>
+        <v>6761263</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5233,10 +5233,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128991661</v>
+        <v>128994946</v>
       </c>
       <c r="B44" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5264,14 +5264,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>493295</v>
+        <v>492986</v>
       </c>
       <c r="R44" t="n">
-        <v>6761257</v>
+        <v>6761194</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5340,10 +5340,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128994946</v>
+        <v>128991661</v>
       </c>
       <c r="B45" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5371,14 +5371,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>492986</v>
+        <v>493295</v>
       </c>
       <c r="R45" t="n">
-        <v>6761194</v>
+        <v>6761257</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5447,10 +5447,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128994294</v>
+        <v>128999732</v>
       </c>
       <c r="B46" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5458,34 +5458,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493144</v>
+        <v>493327</v>
       </c>
       <c r="R46" t="n">
-        <v>6761263</v>
+        <v>6761155</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5554,50 +5554,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128991653</v>
+        <v>128999673</v>
       </c>
       <c r="B47" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493295</v>
+        <v>493255</v>
       </c>
       <c r="R47" t="n">
-        <v>6761257</v>
+        <v>6761127</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5629,7 +5624,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5639,7 +5634,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5669,7 +5664,7 @@
         <v>128994503</v>
       </c>
       <c r="B48" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5781,7 +5776,7 @@
         <v>128998610</v>
       </c>
       <c r="B49" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5885,45 +5880,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128999673</v>
+        <v>128991653</v>
       </c>
       <c r="B50" t="n">
-        <v>8450</v>
+        <v>57722</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493255</v>
+        <v>493295</v>
       </c>
       <c r="R50" t="n">
-        <v>6761127</v>
+        <v>6761257</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5992,10 +5992,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128999627</v>
+        <v>128994661</v>
       </c>
       <c r="B51" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6003,34 +6003,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493222</v>
+        <v>493048</v>
       </c>
       <c r="R51" t="n">
-        <v>6761162</v>
+        <v>6761242</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6062,7 +6067,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6072,7 +6077,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6099,10 +6104,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128994661</v>
+        <v>128999627</v>
       </c>
       <c r="B52" t="n">
-        <v>57720</v>
+        <v>79039</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6110,39 +6115,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493048</v>
+        <v>493222</v>
       </c>
       <c r="R52" t="n">
-        <v>6761242</v>
+        <v>6761162</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6211,10 +6211,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128991818</v>
+        <v>128998638</v>
       </c>
       <c r="B53" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6222,34 +6222,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>493312</v>
+        <v>492971</v>
       </c>
       <c r="R53" t="n">
-        <v>6761262</v>
+        <v>6761075</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6281,7 +6286,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6291,7 +6296,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6321,7 +6326,7 @@
         <v>128998999</v>
       </c>
       <c r="B54" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6425,10 +6430,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128998638</v>
+        <v>128991818</v>
       </c>
       <c r="B55" t="n">
-        <v>57720</v>
+        <v>79039</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6436,39 +6441,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>492971</v>
+        <v>493312</v>
       </c>
       <c r="R55" t="n">
-        <v>6761075</v>
+        <v>6761262</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6540,7 +6540,7 @@
         <v>128991463</v>
       </c>
       <c r="B56" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>128990627</v>
       </c>
       <c r="B57" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>128995292</v>
       </c>
       <c r="B58" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>128994922</v>
       </c>
       <c r="B59" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>129015883</v>
       </c>
       <c r="B60" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 41794-2025 artfynd.xlsx
+++ b/artfynd/A 41794-2025 artfynd.xlsx
@@ -2952,10 +2952,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128998223</v>
+        <v>128991711</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2963,34 +2963,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492885</v>
+        <v>493310</v>
       </c>
       <c r="R23" t="n">
-        <v>6761180</v>
+        <v>6761241</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3022,7 +3027,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3032,7 +3037,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3059,7 +3064,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128998201</v>
+        <v>128998223</v>
       </c>
       <c r="B24" t="n">
         <v>79039</v>
@@ -3094,10 +3099,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492877</v>
+        <v>492885</v>
       </c>
       <c r="R24" t="n">
-        <v>6761211</v>
+        <v>6761180</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3166,10 +3171,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128991711</v>
+        <v>128998201</v>
       </c>
       <c r="B25" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3177,39 +3182,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493310</v>
+        <v>492877</v>
       </c>
       <c r="R25" t="n">
-        <v>6761241</v>
+        <v>6761211</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3278,10 +3278,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128990886</v>
+        <v>128995392</v>
       </c>
       <c r="B26" t="n">
-        <v>79039</v>
+        <v>91553</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3289,34 +3289,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493487</v>
+        <v>492992</v>
       </c>
       <c r="R26" t="n">
-        <v>6761281</v>
+        <v>6761309</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3348,7 +3352,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3358,12 +3362,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Sumpskogskaraktär i området här.</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3390,45 +3389,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128994100</v>
+        <v>128990886</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493167</v>
+        <v>493487</v>
       </c>
       <c r="R27" t="n">
-        <v>6761257</v>
+        <v>6761281</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3460,7 +3459,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3470,7 +3469,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Sumpskogskaraktär i området här.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3497,49 +3501,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128995392</v>
+        <v>128994100</v>
       </c>
       <c r="B28" t="n">
-        <v>91553</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492992</v>
+        <v>493167</v>
       </c>
       <c r="R28" t="n">
-        <v>6761309</v>
+        <v>6761257</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4362,10 +4362,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128991964</v>
+        <v>128993887</v>
       </c>
       <c r="B36" t="n">
-        <v>58155</v>
+        <v>79039</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4373,42 +4373,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493252</v>
+        <v>493167</v>
       </c>
       <c r="R36" t="n">
-        <v>6761277</v>
+        <v>6761257</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4437,7 +4432,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4447,7 +4442,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4474,10 +4469,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128999032</v>
+        <v>128997967</v>
       </c>
       <c r="B37" t="n">
-        <v>58155</v>
+        <v>79039</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4485,39 +4480,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493048</v>
+        <v>492949</v>
       </c>
       <c r="R37" t="n">
-        <v>6761092</v>
+        <v>6761266</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4549,7 +4539,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4559,7 +4549,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4586,7 +4581,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128993887</v>
+        <v>128994367</v>
       </c>
       <c r="B38" t="n">
         <v>79039</v>
@@ -4621,10 +4616,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493167</v>
+        <v>493118</v>
       </c>
       <c r="R38" t="n">
-        <v>6761257</v>
+        <v>6761310</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4693,7 +4688,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128997967</v>
+        <v>128994864</v>
       </c>
       <c r="B39" t="n">
         <v>79039</v>
@@ -4728,10 +4723,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492949</v>
+        <v>493021</v>
       </c>
       <c r="R39" t="n">
-        <v>6761266</v>
+        <v>6761214</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4774,11 +4769,6 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4805,10 +4795,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128994367</v>
+        <v>128991964</v>
       </c>
       <c r="B40" t="n">
-        <v>79039</v>
+        <v>58155</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4816,37 +4806,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493118</v>
+        <v>493252</v>
       </c>
       <c r="R40" t="n">
-        <v>6761310</v>
+        <v>6761277</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4875,7 +4870,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4885,7 +4880,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4912,10 +4907,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128994864</v>
+        <v>128999032</v>
       </c>
       <c r="B41" t="n">
-        <v>79039</v>
+        <v>58155</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4923,34 +4918,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493021</v>
+        <v>493048</v>
       </c>
       <c r="R41" t="n">
-        <v>6761214</v>
+        <v>6761092</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5554,45 +5554,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128999673</v>
+        <v>128994503</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>57722</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493255</v>
+        <v>493047</v>
       </c>
       <c r="R47" t="n">
-        <v>6761127</v>
+        <v>6761263</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5624,7 +5629,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5634,7 +5639,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5661,10 +5666,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128994503</v>
+        <v>128998610</v>
       </c>
       <c r="B48" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5672,39 +5677,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493047</v>
+        <v>492993</v>
       </c>
       <c r="R48" t="n">
-        <v>6761263</v>
+        <v>6761086</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5773,10 +5773,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128998610</v>
+        <v>128991653</v>
       </c>
       <c r="B49" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5784,34 +5784,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492993</v>
+        <v>493295</v>
       </c>
       <c r="R49" t="n">
-        <v>6761086</v>
+        <v>6761257</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5843,7 +5848,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5853,7 +5858,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5880,50 +5885,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128991653</v>
+        <v>128999673</v>
       </c>
       <c r="B50" t="n">
-        <v>57722</v>
+        <v>8450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493295</v>
+        <v>493255</v>
       </c>
       <c r="R50" t="n">
-        <v>6761257</v>
+        <v>6761127</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6211,10 +6211,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128998638</v>
+        <v>128998999</v>
       </c>
       <c r="B53" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6222,39 +6222,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>492971</v>
+        <v>493048</v>
       </c>
       <c r="R53" t="n">
-        <v>6761075</v>
+        <v>6761092</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6323,7 +6318,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128998999</v>
+        <v>128991818</v>
       </c>
       <c r="B54" t="n">
         <v>79039</v>
@@ -6354,14 +6349,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493048</v>
+        <v>493312</v>
       </c>
       <c r="R54" t="n">
-        <v>6761092</v>
+        <v>6761262</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6393,7 +6388,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6403,7 +6398,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6430,10 +6425,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128991818</v>
+        <v>128998638</v>
       </c>
       <c r="B55" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6441,34 +6436,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>493312</v>
+        <v>492971</v>
       </c>
       <c r="R55" t="n">
-        <v>6761262</v>
+        <v>6761075</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 41794-2025 artfynd.xlsx
+++ b/artfynd/A 41794-2025 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128993314</v>
+        <v>128999532</v>
       </c>
       <c r="B4" t="n">
         <v>79039</v>
@@ -920,14 +920,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493165</v>
+        <v>493157</v>
       </c>
       <c r="R4" t="n">
-        <v>6761309</v>
+        <v>6761137</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128997543</v>
+        <v>128993314</v>
       </c>
       <c r="B5" t="n">
         <v>79039</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492963</v>
+        <v>493165</v>
       </c>
       <c r="R5" t="n">
-        <v>6761283</v>
+        <v>6761309</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1108,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128992649</v>
+        <v>128997543</v>
       </c>
       <c r="B6" t="n">
         <v>79039</v>
@@ -1134,14 +1139,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493247</v>
+        <v>492963</v>
       </c>
       <c r="R6" t="n">
-        <v>6761309</v>
+        <v>6761283</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128994822</v>
+        <v>128992649</v>
       </c>
       <c r="B7" t="n">
         <v>79039</v>
@@ -1241,14 +1246,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493022</v>
+        <v>493247</v>
       </c>
       <c r="R7" t="n">
-        <v>6761226</v>
+        <v>6761309</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1322,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128999532</v>
+        <v>128994822</v>
       </c>
       <c r="B8" t="n">
         <v>79039</v>
@@ -1348,14 +1353,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493157</v>
+        <v>493022</v>
       </c>
       <c r="R8" t="n">
-        <v>6761137</v>
+        <v>6761226</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,12 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,7 +1429,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128998367</v>
+        <v>128999256</v>
       </c>
       <c r="B9" t="n">
         <v>79039</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492928</v>
+        <v>493048</v>
       </c>
       <c r="R9" t="n">
-        <v>6761141</v>
+        <v>6761242</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128999256</v>
+        <v>128998367</v>
       </c>
       <c r="B10" t="n">
         <v>79039</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493048</v>
+        <v>492928</v>
       </c>
       <c r="R10" t="n">
-        <v>6761242</v>
+        <v>6761141</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2198,32 +2198,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128991903</v>
+        <v>128990939</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>97547</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493287</v>
+        <v>493487</v>
       </c>
       <c r="R16" t="n">
-        <v>6761277</v>
+        <v>6761281</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2279,6 +2279,11 @@
       <c r="AB16" t="inlineStr">
         <is>
           <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2519,32 +2524,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128990939</v>
+        <v>128991903</v>
       </c>
       <c r="B19" t="n">
-        <v>97540</v>
+        <v>79039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2554,10 +2559,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493487</v>
+        <v>493287</v>
       </c>
       <c r="R19" t="n">
-        <v>6761281</v>
+        <v>6761277</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2600,11 +2605,6 @@
       <c r="AB19" t="inlineStr">
         <is>
           <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2631,7 +2631,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128991027</v>
+        <v>128994202</v>
       </c>
       <c r="B20" t="n">
         <v>79039</v>
@@ -2662,14 +2662,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493464</v>
+        <v>493144</v>
       </c>
       <c r="R20" t="n">
-        <v>6761291</v>
+        <v>6761263</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2845,7 +2845,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128994202</v>
+        <v>128991027</v>
       </c>
       <c r="B22" t="n">
         <v>79039</v>
@@ -2876,14 +2876,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493144</v>
+        <v>493464</v>
       </c>
       <c r="R22" t="n">
-        <v>6761263</v>
+        <v>6761291</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2952,10 +2952,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128991711</v>
+        <v>128998223</v>
       </c>
       <c r="B23" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2963,39 +2963,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493310</v>
+        <v>492885</v>
       </c>
       <c r="R23" t="n">
-        <v>6761241</v>
+        <v>6761180</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3027,7 +3022,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3037,7 +3032,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3064,10 +3059,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128998223</v>
+        <v>128991711</v>
       </c>
       <c r="B24" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3075,34 +3070,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492885</v>
+        <v>493310</v>
       </c>
       <c r="R24" t="n">
-        <v>6761180</v>
+        <v>6761241</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3281,7 +3281,7 @@
         <v>128995392</v>
       </c>
       <c r="B26" t="n">
-        <v>91553</v>
+        <v>91560</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3608,32 +3608,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128998878</v>
+        <v>128995396</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492993</v>
+        <v>492992</v>
       </c>
       <c r="R29" t="n">
-        <v>6761002</v>
+        <v>6761309</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3822,32 +3822,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128995396</v>
+        <v>128998878</v>
       </c>
       <c r="B31" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492992</v>
+        <v>492993</v>
       </c>
       <c r="R31" t="n">
-        <v>6761309</v>
+        <v>6761002</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4250,10 +4250,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128991491</v>
+        <v>128994864</v>
       </c>
       <c r="B35" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4261,39 +4261,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493290</v>
+        <v>493021</v>
       </c>
       <c r="R35" t="n">
-        <v>6761213</v>
+        <v>6761214</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4325,7 +4320,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4335,7 +4330,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4469,7 +4464,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128997967</v>
+        <v>128994367</v>
       </c>
       <c r="B37" t="n">
         <v>79039</v>
@@ -4504,10 +4499,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>492949</v>
+        <v>493118</v>
       </c>
       <c r="R37" t="n">
-        <v>6761266</v>
+        <v>6761310</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4550,11 +4545,6 @@
       <c r="AB37" t="inlineStr">
         <is>
           <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4581,7 +4571,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128994367</v>
+        <v>128997967</v>
       </c>
       <c r="B38" t="n">
         <v>79039</v>
@@ -4616,10 +4606,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493118</v>
+        <v>492949</v>
       </c>
       <c r="R38" t="n">
-        <v>6761310</v>
+        <v>6761266</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4662,6 +4652,11 @@
       <c r="AB38" t="inlineStr">
         <is>
           <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4688,10 +4683,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128994864</v>
+        <v>128991964</v>
       </c>
       <c r="B39" t="n">
-        <v>79039</v>
+        <v>58155</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4699,37 +4694,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493021</v>
+        <v>493252</v>
       </c>
       <c r="R39" t="n">
-        <v>6761214</v>
+        <v>6761277</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4795,7 +4795,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128991964</v>
+        <v>128999032</v>
       </c>
       <c r="B40" t="n">
         <v>58155</v>
@@ -4831,17 +4831,17 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493252</v>
+        <v>493048</v>
       </c>
       <c r="R40" t="n">
-        <v>6761277</v>
+        <v>6761092</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4907,10 +4907,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128999032</v>
+        <v>128991491</v>
       </c>
       <c r="B41" t="n">
-        <v>58155</v>
+        <v>57722</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4918,39 +4918,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103001</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493048</v>
+        <v>493290</v>
       </c>
       <c r="R41" t="n">
-        <v>6761092</v>
+        <v>6761213</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5233,7 +5233,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128994946</v>
+        <v>128999732</v>
       </c>
       <c r="B44" t="n">
         <v>79039</v>
@@ -5264,14 +5264,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492986</v>
+        <v>493327</v>
       </c>
       <c r="R44" t="n">
-        <v>6761194</v>
+        <v>6761155</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5447,7 +5447,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128999732</v>
+        <v>128994946</v>
       </c>
       <c r="B46" t="n">
         <v>79039</v>
@@ -5478,14 +5478,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493327</v>
+        <v>492986</v>
       </c>
       <c r="R46" t="n">
-        <v>6761155</v>
+        <v>6761194</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5554,7 +5554,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128994503</v>
+        <v>128991653</v>
       </c>
       <c r="B47" t="n">
         <v>57722</v>
@@ -5585,19 +5585,19 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493047</v>
+        <v>493295</v>
       </c>
       <c r="R47" t="n">
-        <v>6761263</v>
+        <v>6761257</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5666,10 +5666,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128998610</v>
+        <v>128994503</v>
       </c>
       <c r="B48" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5677,34 +5677,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492993</v>
+        <v>493047</v>
       </c>
       <c r="R48" t="n">
-        <v>6761086</v>
+        <v>6761263</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5736,7 +5741,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5746,7 +5751,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5773,50 +5778,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128991653</v>
+        <v>128999673</v>
       </c>
       <c r="B49" t="n">
-        <v>57722</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493295</v>
+        <v>493255</v>
       </c>
       <c r="R49" t="n">
-        <v>6761257</v>
+        <v>6761127</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5885,32 +5885,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128999673</v>
+        <v>128998610</v>
       </c>
       <c r="B50" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5920,10 +5920,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493255</v>
+        <v>492993</v>
       </c>
       <c r="R50" t="n">
-        <v>6761127</v>
+        <v>6761086</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5992,10 +5992,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128994661</v>
+        <v>128999627</v>
       </c>
       <c r="B51" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6003,39 +6003,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493048</v>
+        <v>493222</v>
       </c>
       <c r="R51" t="n">
-        <v>6761242</v>
+        <v>6761162</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6067,7 +6062,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6077,7 +6072,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6104,10 +6099,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128999627</v>
+        <v>128994661</v>
       </c>
       <c r="B52" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6115,34 +6110,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493222</v>
+        <v>493048</v>
       </c>
       <c r="R52" t="n">
-        <v>6761162</v>
+        <v>6761242</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6211,10 +6211,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128998999</v>
+        <v>128998638</v>
       </c>
       <c r="B53" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6222,34 +6222,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>493048</v>
+        <v>492971</v>
       </c>
       <c r="R53" t="n">
-        <v>6761092</v>
+        <v>6761075</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6425,10 +6430,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128998638</v>
+        <v>128998999</v>
       </c>
       <c r="B55" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6436,39 +6441,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>492971</v>
+        <v>493048</v>
       </c>
       <c r="R55" t="n">
-        <v>6761075</v>
+        <v>6761092</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6649,53 +6649,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128990627</v>
+        <v>128995292</v>
       </c>
       <c r="B57" t="n">
-        <v>58095</v>
+        <v>79039</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>493483</v>
+        <v>492996</v>
       </c>
       <c r="R57" t="n">
-        <v>6761261</v>
+        <v>6761284</v>
       </c>
       <c r="S57" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6724,7 +6719,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6734,7 +6729,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6761,48 +6756,53 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128995292</v>
+        <v>128990627</v>
       </c>
       <c r="B58" t="n">
-        <v>79039</v>
+        <v>58095</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>492996</v>
+        <v>493483</v>
       </c>
       <c r="R58" t="n">
-        <v>6761284</v>
+        <v>6761261</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6978,7 +6978,7 @@
         <v>129015883</v>
       </c>
       <c r="B60" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 41794-2025 artfynd.xlsx
+++ b/artfynd/A 41794-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128991347</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128998779</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128999532</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>128993314</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>128997543</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128992649</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128994822</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>128999256</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>128998367</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>128999351</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1750,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128998263</v>
+        <v>128998025</v>
       </c>
       <c r="B12" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,39 +1761,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492885</v>
+        <v>492895</v>
       </c>
       <c r="R12" t="n">
-        <v>6761180</v>
+        <v>6761212</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1862,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128999613</v>
+        <v>128991923</v>
       </c>
       <c r="B13" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,39 +1868,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493205</v>
+        <v>493277</v>
       </c>
       <c r="R13" t="n">
-        <v>6761180</v>
+        <v>6761265</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,7 +1927,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1937,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,10 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128997799</v>
+        <v>128991903</v>
       </c>
       <c r="B14" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,39 +1975,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492929</v>
+        <v>493287</v>
       </c>
       <c r="R14" t="n">
-        <v>6761272</v>
+        <v>6761277</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,7 +2034,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2059,7 +2044,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,10 +2071,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128998274</v>
+        <v>128999613</v>
       </c>
       <c r="B15" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2126,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492894</v>
+        <v>493205</v>
       </c>
       <c r="R15" t="n">
-        <v>6761171</v>
+        <v>6761180</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,7 +2146,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2171,7 +2156,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2201,7 +2186,7 @@
         <v>128990939</v>
       </c>
       <c r="B16" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2310,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128998025</v>
+        <v>128998263</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,34 +2306,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492895</v>
+        <v>492885</v>
       </c>
       <c r="R17" t="n">
-        <v>6761212</v>
+        <v>6761180</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2417,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128991923</v>
+        <v>128997799</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,34 +2418,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493277</v>
+        <v>492929</v>
       </c>
       <c r="R18" t="n">
-        <v>6761265</v>
+        <v>6761272</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2487,7 +2482,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2497,7 +2492,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2524,10 +2519,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128991903</v>
+        <v>128998274</v>
       </c>
       <c r="B19" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,34 +2530,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493287</v>
+        <v>492894</v>
       </c>
       <c r="R19" t="n">
-        <v>6761277</v>
+        <v>6761171</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2634,7 +2634,7 @@
         <v>128994202</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>128998438</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>128991027</v>
       </c>
       <c r="B22" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>128998223</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3059,10 +3059,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128991711</v>
+        <v>128998201</v>
       </c>
       <c r="B24" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3070,39 +3070,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493310</v>
+        <v>492877</v>
       </c>
       <c r="R24" t="n">
-        <v>6761241</v>
+        <v>6761211</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3134,7 +3129,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3144,7 +3139,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3171,10 +3166,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128998201</v>
+        <v>128991711</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3182,34 +3177,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492877</v>
+        <v>493310</v>
       </c>
       <c r="R25" t="n">
-        <v>6761211</v>
+        <v>6761241</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3281,7 +3281,7 @@
         <v>128995392</v>
       </c>
       <c r="B26" t="n">
-        <v>91560</v>
+        <v>91562</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3389,45 +3389,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128990886</v>
+        <v>128994100</v>
       </c>
       <c r="B27" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493487</v>
+        <v>493167</v>
       </c>
       <c r="R27" t="n">
-        <v>6761281</v>
+        <v>6761257</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3469,12 +3469,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Sumpskogskaraktär i området här.</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3501,45 +3496,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128994100</v>
+        <v>128990886</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493167</v>
+        <v>493487</v>
       </c>
       <c r="R28" t="n">
-        <v>6761257</v>
+        <v>6761281</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3571,7 +3566,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3581,7 +3576,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Sumpskogskaraktär i området här.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3611,7 +3611,7 @@
         <v>128995396</v>
       </c>
       <c r="B29" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>128994343</v>
       </c>
       <c r="B30" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>128994846</v>
       </c>
       <c r="B32" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>128994977</v>
       </c>
       <c r="B34" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>128994864</v>
       </c>
       <c r="B35" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>128993887</v>
       </c>
       <c r="B36" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>128994367</v>
       </c>
       <c r="B37" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>128997967</v>
       </c>
       <c r="B38" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4683,10 +4683,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128991964</v>
+        <v>128991491</v>
       </c>
       <c r="B39" t="n">
-        <v>58155</v>
+        <v>57724</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4694,27 +4694,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103001</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4723,13 +4723,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493252</v>
+        <v>493290</v>
       </c>
       <c r="R39" t="n">
-        <v>6761277</v>
+        <v>6761213</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4795,10 +4795,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128999032</v>
+        <v>128991964</v>
       </c>
       <c r="B40" t="n">
-        <v>58155</v>
+        <v>58157</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4831,17 +4831,17 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493048</v>
+        <v>493252</v>
       </c>
       <c r="R40" t="n">
-        <v>6761092</v>
+        <v>6761277</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4907,10 +4907,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128991491</v>
+        <v>128999032</v>
       </c>
       <c r="B41" t="n">
-        <v>57722</v>
+        <v>58157</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4918,39 +4918,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493290</v>
+        <v>493048</v>
       </c>
       <c r="R41" t="n">
-        <v>6761213</v>
+        <v>6761092</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5022,7 +5022,7 @@
         <v>128995173</v>
       </c>
       <c r="B42" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>128994294</v>
       </c>
       <c r="B43" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>128999732</v>
       </c>
       <c r="B44" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>128991661</v>
       </c>
       <c r="B45" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>128994946</v>
       </c>
       <c r="B46" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5554,10 +5554,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128991653</v>
+        <v>128998610</v>
       </c>
       <c r="B47" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5565,39 +5565,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493295</v>
+        <v>492993</v>
       </c>
       <c r="R47" t="n">
-        <v>6761257</v>
+        <v>6761086</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5629,7 +5624,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5639,7 +5634,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5669,7 +5664,7 @@
         <v>128994503</v>
       </c>
       <c r="B48" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5778,45 +5773,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128999673</v>
+        <v>128991653</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493255</v>
+        <v>493295</v>
       </c>
       <c r="R49" t="n">
-        <v>6761127</v>
+        <v>6761257</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5885,32 +5885,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128998610</v>
+        <v>128999673</v>
       </c>
       <c r="B50" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5920,10 +5920,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492993</v>
+        <v>493255</v>
       </c>
       <c r="R50" t="n">
-        <v>6761086</v>
+        <v>6761127</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5992,10 +5992,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128999627</v>
+        <v>128994661</v>
       </c>
       <c r="B51" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6003,34 +6003,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493222</v>
+        <v>493048</v>
       </c>
       <c r="R51" t="n">
-        <v>6761162</v>
+        <v>6761242</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6062,7 +6067,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6072,7 +6077,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6099,10 +6104,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128994661</v>
+        <v>128999627</v>
       </c>
       <c r="B52" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6110,39 +6115,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493048</v>
+        <v>493222</v>
       </c>
       <c r="R52" t="n">
-        <v>6761242</v>
+        <v>6761162</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6214,7 +6214,7 @@
         <v>128998638</v>
       </c>
       <c r="B53" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>128991818</v>
       </c>
       <c r="B54" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>128998999</v>
       </c>
       <c r="B55" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>128991463</v>
       </c>
       <c r="B56" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6649,48 +6649,53 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128995292</v>
+        <v>128990627</v>
       </c>
       <c r="B57" t="n">
-        <v>79039</v>
+        <v>58097</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>492996</v>
+        <v>493483</v>
       </c>
       <c r="R57" t="n">
-        <v>6761284</v>
+        <v>6761261</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6719,7 +6724,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6729,7 +6734,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6756,53 +6761,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128990627</v>
+        <v>128995292</v>
       </c>
       <c r="B58" t="n">
-        <v>58095</v>
+        <v>79041</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>493483</v>
+        <v>492996</v>
       </c>
       <c r="R58" t="n">
-        <v>6761261</v>
+        <v>6761284</v>
       </c>
       <c r="S58" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6871,7 +6871,7 @@
         <v>128994922</v>
       </c>
       <c r="B59" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>129015883</v>
       </c>
       <c r="B60" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 41794-2025 artfynd.xlsx
+++ b/artfynd/A 41794-2025 artfynd.xlsx
@@ -2071,50 +2071,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128999613</v>
+        <v>128990939</v>
       </c>
       <c r="B15" t="n">
-        <v>57724</v>
+        <v>97549</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493205</v>
+        <v>493487</v>
       </c>
       <c r="R15" t="n">
-        <v>6761180</v>
+        <v>6761281</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2141,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2156,7 +2151,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,45 +2183,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128990939</v>
+        <v>128998263</v>
       </c>
       <c r="B16" t="n">
-        <v>97549</v>
+        <v>57724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493487</v>
+        <v>492885</v>
       </c>
       <c r="R16" t="n">
-        <v>6761281</v>
+        <v>6761180</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2263,12 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,7 +2295,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128998263</v>
+        <v>128999613</v>
       </c>
       <c r="B17" t="n">
         <v>57724</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492885</v>
+        <v>493205</v>
       </c>
       <c r="R17" t="n">
         <v>6761180</v>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3278,10 +3278,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128995392</v>
+        <v>128990886</v>
       </c>
       <c r="B26" t="n">
-        <v>91562</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3289,38 +3289,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492992</v>
+        <v>493487</v>
       </c>
       <c r="R26" t="n">
-        <v>6761309</v>
+        <v>6761281</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3352,7 +3348,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3362,7 +3358,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Sumpskogskaraktär i området här.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3389,45 +3390,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128994100</v>
+        <v>128995392</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>91562</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493167</v>
+        <v>492992</v>
       </c>
       <c r="R27" t="n">
-        <v>6761257</v>
+        <v>6761309</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3496,45 +3501,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128990886</v>
+        <v>128994100</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493487</v>
+        <v>493167</v>
       </c>
       <c r="R28" t="n">
-        <v>6761281</v>
+        <v>6761257</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3566,7 +3571,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3576,12 +3581,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Sumpskogskaraktär i området här.</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3608,32 +3608,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128995396</v>
+        <v>128998878</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492992</v>
+        <v>492993</v>
       </c>
       <c r="R29" t="n">
-        <v>6761309</v>
+        <v>6761002</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3715,7 +3715,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128994343</v>
+        <v>128995396</v>
       </c>
       <c r="B30" t="n">
         <v>79041</v>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493103</v>
+        <v>492992</v>
       </c>
       <c r="R30" t="n">
-        <v>6761270</v>
+        <v>6761309</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3822,32 +3822,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128998878</v>
+        <v>128994343</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492993</v>
+        <v>493103</v>
       </c>
       <c r="R31" t="n">
-        <v>6761002</v>
+        <v>6761270</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4683,10 +4683,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128991491</v>
+        <v>128991964</v>
       </c>
       <c r="B39" t="n">
-        <v>57724</v>
+        <v>58157</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4694,27 +4694,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4723,13 +4723,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493290</v>
+        <v>493252</v>
       </c>
       <c r="R39" t="n">
-        <v>6761213</v>
+        <v>6761277</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128991964</v>
+        <v>128999032</v>
       </c>
       <c r="B40" t="n">
         <v>58157</v>
@@ -4831,17 +4831,17 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493252</v>
+        <v>493048</v>
       </c>
       <c r="R40" t="n">
-        <v>6761277</v>
+        <v>6761092</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4907,10 +4907,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128999032</v>
+        <v>128991491</v>
       </c>
       <c r="B41" t="n">
-        <v>58157</v>
+        <v>57724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4918,39 +4918,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103001</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493048</v>
+        <v>493290</v>
       </c>
       <c r="R41" t="n">
-        <v>6761092</v>
+        <v>6761213</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5019,10 +5019,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128995173</v>
+        <v>128994294</v>
       </c>
       <c r="B42" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493010</v>
+        <v>493144</v>
       </c>
       <c r="R42" t="n">
-        <v>6761236</v>
+        <v>6761263</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5126,10 +5126,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128994294</v>
+        <v>128995173</v>
       </c>
       <c r="B43" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5137,21 +5137,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5161,10 +5161,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493144</v>
+        <v>493010</v>
       </c>
       <c r="R43" t="n">
-        <v>6761263</v>
+        <v>6761236</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5661,7 +5661,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128994503</v>
+        <v>128991653</v>
       </c>
       <c r="B48" t="n">
         <v>57724</v>
@@ -5692,19 +5692,19 @@
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493047</v>
+        <v>493295</v>
       </c>
       <c r="R48" t="n">
-        <v>6761263</v>
+        <v>6761257</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5773,7 +5773,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128991653</v>
+        <v>128994503</v>
       </c>
       <c r="B49" t="n">
         <v>57724</v>
@@ -5804,19 +5804,19 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493295</v>
+        <v>493047</v>
       </c>
       <c r="R49" t="n">
-        <v>6761257</v>
+        <v>6761263</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5992,10 +5992,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128994661</v>
+        <v>128999627</v>
       </c>
       <c r="B51" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6003,39 +6003,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493048</v>
+        <v>493222</v>
       </c>
       <c r="R51" t="n">
-        <v>6761242</v>
+        <v>6761162</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6067,7 +6062,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6077,7 +6072,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6104,10 +6099,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128999627</v>
+        <v>128994661</v>
       </c>
       <c r="B52" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6115,34 +6110,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493222</v>
+        <v>493048</v>
       </c>
       <c r="R52" t="n">
-        <v>6761162</v>
+        <v>6761242</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6649,53 +6649,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128990627</v>
+        <v>128995292</v>
       </c>
       <c r="B57" t="n">
-        <v>58097</v>
+        <v>79041</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>493483</v>
+        <v>492996</v>
       </c>
       <c r="R57" t="n">
-        <v>6761261</v>
+        <v>6761284</v>
       </c>
       <c r="S57" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6724,7 +6719,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6734,7 +6729,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6761,48 +6756,53 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128995292</v>
+        <v>128990627</v>
       </c>
       <c r="B58" t="n">
-        <v>79041</v>
+        <v>58097</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>492996</v>
+        <v>493483</v>
       </c>
       <c r="R58" t="n">
-        <v>6761284</v>
+        <v>6761261</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 41794-2025 artfynd.xlsx
+++ b/artfynd/A 41794-2025 artfynd.xlsx
@@ -2071,45 +2071,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128990939</v>
+        <v>128998263</v>
       </c>
       <c r="B15" t="n">
-        <v>97549</v>
+        <v>57724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493487</v>
+        <v>492885</v>
       </c>
       <c r="R15" t="n">
-        <v>6761281</v>
+        <v>6761180</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2146,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2151,12 +2156,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,7 +2183,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128998263</v>
+        <v>128999613</v>
       </c>
       <c r="B16" t="n">
         <v>57724</v>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492885</v>
+        <v>493205</v>
       </c>
       <c r="R16" t="n">
         <v>6761180</v>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,7 +2295,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128999613</v>
+        <v>128997799</v>
       </c>
       <c r="B17" t="n">
         <v>57724</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493205</v>
+        <v>492929</v>
       </c>
       <c r="R17" t="n">
-        <v>6761180</v>
+        <v>6761272</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,7 +2407,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128997799</v>
+        <v>128998274</v>
       </c>
       <c r="B18" t="n">
         <v>57724</v>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492929</v>
+        <v>492894</v>
       </c>
       <c r="R18" t="n">
-        <v>6761272</v>
+        <v>6761171</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2519,50 +2519,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128998274</v>
+        <v>128990939</v>
       </c>
       <c r="B19" t="n">
-        <v>57724</v>
+        <v>97549</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492894</v>
+        <v>493487</v>
       </c>
       <c r="R19" t="n">
-        <v>6761171</v>
+        <v>6761281</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2594,7 +2589,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2604,7 +2599,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3608,32 +3608,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128998878</v>
+        <v>128995396</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492993</v>
+        <v>492992</v>
       </c>
       <c r="R29" t="n">
-        <v>6761002</v>
+        <v>6761309</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3715,7 +3715,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128995396</v>
+        <v>128994343</v>
       </c>
       <c r="B30" t="n">
         <v>79041</v>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492992</v>
+        <v>493103</v>
       </c>
       <c r="R30" t="n">
-        <v>6761309</v>
+        <v>6761270</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3822,32 +3822,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128994343</v>
+        <v>128998878</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493103</v>
+        <v>492993</v>
       </c>
       <c r="R31" t="n">
-        <v>6761270</v>
+        <v>6761002</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4250,10 +4250,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128994864</v>
+        <v>128991491</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4261,34 +4261,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493021</v>
+        <v>493290</v>
       </c>
       <c r="R35" t="n">
-        <v>6761214</v>
+        <v>6761213</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4320,7 +4325,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4330,7 +4335,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4357,7 +4362,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128993887</v>
+        <v>128994864</v>
       </c>
       <c r="B36" t="n">
         <v>79041</v>
@@ -4392,10 +4397,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493167</v>
+        <v>493021</v>
       </c>
       <c r="R36" t="n">
-        <v>6761257</v>
+        <v>6761214</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4464,7 +4469,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128994367</v>
+        <v>128993887</v>
       </c>
       <c r="B37" t="n">
         <v>79041</v>
@@ -4499,10 +4504,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493118</v>
+        <v>493167</v>
       </c>
       <c r="R37" t="n">
-        <v>6761310</v>
+        <v>6761257</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4571,7 +4576,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128997967</v>
+        <v>128994367</v>
       </c>
       <c r="B38" t="n">
         <v>79041</v>
@@ -4606,10 +4611,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>492949</v>
+        <v>493118</v>
       </c>
       <c r="R38" t="n">
-        <v>6761266</v>
+        <v>6761310</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4652,11 +4657,6 @@
       <c r="AB38" t="inlineStr">
         <is>
           <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4683,10 +4683,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128991964</v>
+        <v>128997967</v>
       </c>
       <c r="B39" t="n">
-        <v>58157</v>
+        <v>79041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4694,42 +4694,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493252</v>
+        <v>492949</v>
       </c>
       <c r="R39" t="n">
-        <v>6761277</v>
+        <v>6761266</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4758,7 +4753,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4768,7 +4763,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4795,7 +4795,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128999032</v>
+        <v>128991964</v>
       </c>
       <c r="B40" t="n">
         <v>58157</v>
@@ -4831,17 +4831,17 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493048</v>
+        <v>493252</v>
       </c>
       <c r="R40" t="n">
-        <v>6761092</v>
+        <v>6761277</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4907,10 +4907,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128991491</v>
+        <v>128999032</v>
       </c>
       <c r="B41" t="n">
-        <v>57724</v>
+        <v>58157</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4918,39 +4918,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493290</v>
+        <v>493048</v>
       </c>
       <c r="R41" t="n">
-        <v>6761213</v>
+        <v>6761092</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6649,48 +6649,53 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128995292</v>
+        <v>128990627</v>
       </c>
       <c r="B57" t="n">
-        <v>79041</v>
+        <v>58097</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>492996</v>
+        <v>493483</v>
       </c>
       <c r="R57" t="n">
-        <v>6761284</v>
+        <v>6761261</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6719,7 +6724,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6729,7 +6734,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6756,53 +6761,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128990627</v>
+        <v>128995292</v>
       </c>
       <c r="B58" t="n">
-        <v>58097</v>
+        <v>79041</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>493483</v>
+        <v>492996</v>
       </c>
       <c r="R58" t="n">
-        <v>6761261</v>
+        <v>6761284</v>
       </c>
       <c r="S58" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 41794-2025 artfynd.xlsx
+++ b/artfynd/A 41794-2025 artfynd.xlsx
@@ -1750,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128998025</v>
+        <v>128998263</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,34 +1761,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492895</v>
+        <v>492885</v>
       </c>
       <c r="R12" t="n">
-        <v>6761212</v>
+        <v>6761180</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128991923</v>
+        <v>128999613</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,34 +1873,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493277</v>
+        <v>493205</v>
       </c>
       <c r="R13" t="n">
-        <v>6761265</v>
+        <v>6761180</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1937,7 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1964,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128991903</v>
+        <v>128997799</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1975,34 +1985,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493287</v>
+        <v>492929</v>
       </c>
       <c r="R14" t="n">
-        <v>6761277</v>
+        <v>6761272</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +2049,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2044,7 +2059,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,7 +2086,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128998263</v>
+        <v>128998274</v>
       </c>
       <c r="B15" t="n">
         <v>57724</v>
@@ -2111,10 +2126,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492885</v>
+        <v>492894</v>
       </c>
       <c r="R15" t="n">
-        <v>6761180</v>
+        <v>6761171</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128999613</v>
+        <v>128998025</v>
       </c>
       <c r="B16" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,39 +2209,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493205</v>
+        <v>492895</v>
       </c>
       <c r="R16" t="n">
-        <v>6761180</v>
+        <v>6761212</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,7 +2268,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2268,7 +2278,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128997799</v>
+        <v>128991923</v>
       </c>
       <c r="B17" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2306,39 +2316,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492929</v>
+        <v>493277</v>
       </c>
       <c r="R17" t="n">
-        <v>6761272</v>
+        <v>6761265</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2375,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2385,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,10 +2412,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128998274</v>
+        <v>128991903</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2418,39 +2423,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492894</v>
+        <v>493287</v>
       </c>
       <c r="R18" t="n">
-        <v>6761171</v>
+        <v>6761277</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2522,7 +2522,7 @@
         <v>128990939</v>
       </c>
       <c r="B19" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2952,10 +2952,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128998223</v>
+        <v>128991711</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2963,34 +2963,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492885</v>
+        <v>493310</v>
       </c>
       <c r="R23" t="n">
-        <v>6761180</v>
+        <v>6761241</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3022,7 +3027,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3032,7 +3037,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3059,7 +3064,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128998201</v>
+        <v>128998223</v>
       </c>
       <c r="B24" t="n">
         <v>79041</v>
@@ -3094,10 +3099,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492877</v>
+        <v>492885</v>
       </c>
       <c r="R24" t="n">
-        <v>6761211</v>
+        <v>6761180</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3166,10 +3171,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128991711</v>
+        <v>128998201</v>
       </c>
       <c r="B25" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3177,39 +3182,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493310</v>
+        <v>492877</v>
       </c>
       <c r="R25" t="n">
-        <v>6761241</v>
+        <v>6761211</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3278,45 +3278,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128990886</v>
+        <v>128994100</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493487</v>
+        <v>493167</v>
       </c>
       <c r="R26" t="n">
-        <v>6761281</v>
+        <v>6761257</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3358,12 +3358,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Sumpskogskaraktär i området här.</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3390,10 +3385,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128995392</v>
+        <v>128990886</v>
       </c>
       <c r="B27" t="n">
-        <v>91562</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3401,38 +3396,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492992</v>
+        <v>493487</v>
       </c>
       <c r="R27" t="n">
-        <v>6761309</v>
+        <v>6761281</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3464,7 +3455,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3474,7 +3465,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Sumpskogskaraktär i området här.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3501,45 +3497,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128994100</v>
+        <v>128995392</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>91560</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493167</v>
+        <v>492992</v>
       </c>
       <c r="R28" t="n">
-        <v>6761257</v>
+        <v>6761309</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4250,10 +4250,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128991491</v>
+        <v>128994864</v>
       </c>
       <c r="B35" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4261,39 +4261,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493290</v>
+        <v>493021</v>
       </c>
       <c r="R35" t="n">
-        <v>6761213</v>
+        <v>6761214</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4325,7 +4320,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4335,7 +4330,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4362,7 +4357,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128994864</v>
+        <v>128993887</v>
       </c>
       <c r="B36" t="n">
         <v>79041</v>
@@ -4397,10 +4392,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493021</v>
+        <v>493167</v>
       </c>
       <c r="R36" t="n">
-        <v>6761214</v>
+        <v>6761257</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4469,7 +4464,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128993887</v>
+        <v>128994367</v>
       </c>
       <c r="B37" t="n">
         <v>79041</v>
@@ -4504,10 +4499,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493167</v>
+        <v>493118</v>
       </c>
       <c r="R37" t="n">
-        <v>6761257</v>
+        <v>6761310</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4576,7 +4571,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128994367</v>
+        <v>128997967</v>
       </c>
       <c r="B38" t="n">
         <v>79041</v>
@@ -4611,10 +4606,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493118</v>
+        <v>492949</v>
       </c>
       <c r="R38" t="n">
-        <v>6761310</v>
+        <v>6761266</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4657,6 +4652,11 @@
       <c r="AB38" t="inlineStr">
         <is>
           <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4683,10 +4683,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128997967</v>
+        <v>128991964</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>58157</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4694,37 +4694,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492949</v>
+        <v>493252</v>
       </c>
       <c r="R39" t="n">
-        <v>6761266</v>
+        <v>6761277</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4753,7 +4758,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4763,12 +4768,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4795,7 +4795,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128991964</v>
+        <v>128999032</v>
       </c>
       <c r="B40" t="n">
         <v>58157</v>
@@ -4831,17 +4831,17 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493252</v>
+        <v>493048</v>
       </c>
       <c r="R40" t="n">
-        <v>6761277</v>
+        <v>6761092</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4907,10 +4907,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128999032</v>
+        <v>128991491</v>
       </c>
       <c r="B41" t="n">
-        <v>58157</v>
+        <v>57724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4918,39 +4918,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103001</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493048</v>
+        <v>493290</v>
       </c>
       <c r="R41" t="n">
-        <v>6761092</v>
+        <v>6761213</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5019,10 +5019,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128994294</v>
+        <v>128995173</v>
       </c>
       <c r="B42" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493144</v>
+        <v>493010</v>
       </c>
       <c r="R42" t="n">
-        <v>6761263</v>
+        <v>6761236</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5126,10 +5126,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128995173</v>
+        <v>128994294</v>
       </c>
       <c r="B43" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5137,21 +5137,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5161,10 +5161,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493010</v>
+        <v>493144</v>
       </c>
       <c r="R43" t="n">
-        <v>6761236</v>
+        <v>6761263</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5554,32 +5554,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128998610</v>
+        <v>128999673</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5589,10 +5589,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492993</v>
+        <v>493255</v>
       </c>
       <c r="R47" t="n">
-        <v>6761086</v>
+        <v>6761127</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5661,10 +5661,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128991653</v>
+        <v>128998610</v>
       </c>
       <c r="B48" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5672,39 +5672,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493295</v>
+        <v>492993</v>
       </c>
       <c r="R48" t="n">
-        <v>6761257</v>
+        <v>6761086</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5736,7 +5731,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5746,7 +5741,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5773,7 +5768,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128994503</v>
+        <v>128991653</v>
       </c>
       <c r="B49" t="n">
         <v>57724</v>
@@ -5804,19 +5799,19 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493047</v>
+        <v>493295</v>
       </c>
       <c r="R49" t="n">
-        <v>6761263</v>
+        <v>6761257</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5848,7 +5843,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5858,7 +5853,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5885,45 +5880,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128999673</v>
+        <v>128994503</v>
       </c>
       <c r="B50" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493255</v>
+        <v>493047</v>
       </c>
       <c r="R50" t="n">
-        <v>6761127</v>
+        <v>6761263</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6211,10 +6211,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128998638</v>
+        <v>128991818</v>
       </c>
       <c r="B53" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6222,39 +6222,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>492971</v>
+        <v>493312</v>
       </c>
       <c r="R53" t="n">
-        <v>6761075</v>
+        <v>6761262</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6286,7 +6281,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6296,7 +6291,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6323,7 +6318,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128991818</v>
+        <v>128998999</v>
       </c>
       <c r="B54" t="n">
         <v>79041</v>
@@ -6354,14 +6349,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493312</v>
+        <v>493048</v>
       </c>
       <c r="R54" t="n">
-        <v>6761262</v>
+        <v>6761092</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6393,7 +6388,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6403,7 +6398,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6430,10 +6425,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128998999</v>
+        <v>128998638</v>
       </c>
       <c r="B55" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6441,34 +6436,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>493048</v>
+        <v>492971</v>
       </c>
       <c r="R55" t="n">
-        <v>6761092</v>
+        <v>6761075</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6978,7 +6978,7 @@
         <v>129015883</v>
       </c>
       <c r="B60" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 41794-2025 artfynd.xlsx
+++ b/artfynd/A 41794-2025 artfynd.xlsx
@@ -2198,45 +2198,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128998025</v>
+        <v>128990939</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>97576</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492895</v>
+        <v>493487</v>
       </c>
       <c r="R16" t="n">
-        <v>6761212</v>
+        <v>6761281</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2278,7 +2278,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2305,7 +2310,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128991923</v>
+        <v>128998025</v>
       </c>
       <c r="B17" t="n">
         <v>79041</v>
@@ -2336,14 +2341,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493277</v>
+        <v>492895</v>
       </c>
       <c r="R17" t="n">
-        <v>6761265</v>
+        <v>6761212</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2375,7 +2380,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2385,7 +2390,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2412,7 +2417,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128991903</v>
+        <v>128991923</v>
       </c>
       <c r="B18" t="n">
         <v>79041</v>
@@ -2447,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493287</v>
+        <v>493277</v>
       </c>
       <c r="R18" t="n">
-        <v>6761277</v>
+        <v>6761265</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2519,32 +2524,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128990939</v>
+        <v>128991903</v>
       </c>
       <c r="B19" t="n">
-        <v>97575</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2554,10 +2559,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493487</v>
+        <v>493287</v>
       </c>
       <c r="R19" t="n">
-        <v>6761281</v>
+        <v>6761277</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2600,11 +2605,6 @@
       <c r="AB19" t="inlineStr">
         <is>
           <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2952,10 +2952,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128991711</v>
+        <v>128998223</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2963,39 +2963,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493310</v>
+        <v>492885</v>
       </c>
       <c r="R23" t="n">
-        <v>6761241</v>
+        <v>6761180</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3027,7 +3022,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3037,7 +3032,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3064,7 +3059,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128998223</v>
+        <v>128998201</v>
       </c>
       <c r="B24" t="n">
         <v>79041</v>
@@ -3099,10 +3094,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492885</v>
+        <v>492877</v>
       </c>
       <c r="R24" t="n">
-        <v>6761180</v>
+        <v>6761211</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3171,10 +3166,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128998201</v>
+        <v>128991711</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3182,34 +3177,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492877</v>
+        <v>493310</v>
       </c>
       <c r="R25" t="n">
-        <v>6761211</v>
+        <v>6761241</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3500,7 +3500,7 @@
         <v>128995392</v>
       </c>
       <c r="B28" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4683,10 +4683,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128991964</v>
+        <v>128991491</v>
       </c>
       <c r="B39" t="n">
-        <v>58157</v>
+        <v>57724</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4694,27 +4694,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103001</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4723,13 +4723,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493252</v>
+        <v>493290</v>
       </c>
       <c r="R39" t="n">
-        <v>6761277</v>
+        <v>6761213</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128999032</v>
+        <v>128991964</v>
       </c>
       <c r="B40" t="n">
         <v>58157</v>
@@ -4831,17 +4831,17 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493048</v>
+        <v>493252</v>
       </c>
       <c r="R40" t="n">
-        <v>6761092</v>
+        <v>6761277</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4907,10 +4907,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128991491</v>
+        <v>128999032</v>
       </c>
       <c r="B41" t="n">
-        <v>57724</v>
+        <v>58157</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4918,39 +4918,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493290</v>
+        <v>493048</v>
       </c>
       <c r="R41" t="n">
-        <v>6761213</v>
+        <v>6761092</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5554,32 +5554,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128999673</v>
+        <v>128998610</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5589,10 +5589,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493255</v>
+        <v>492993</v>
       </c>
       <c r="R47" t="n">
-        <v>6761127</v>
+        <v>6761086</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5661,32 +5661,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128998610</v>
+        <v>128999673</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5696,10 +5696,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492993</v>
+        <v>493255</v>
       </c>
       <c r="R48" t="n">
-        <v>6761086</v>
+        <v>6761127</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6211,10 +6211,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128991818</v>
+        <v>128998638</v>
       </c>
       <c r="B53" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6222,34 +6222,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>493312</v>
+        <v>492971</v>
       </c>
       <c r="R53" t="n">
-        <v>6761262</v>
+        <v>6761075</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6281,7 +6286,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6291,7 +6296,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6318,7 +6323,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128998999</v>
+        <v>128991818</v>
       </c>
       <c r="B54" t="n">
         <v>79041</v>
@@ -6349,14 +6354,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493048</v>
+        <v>493312</v>
       </c>
       <c r="R54" t="n">
-        <v>6761092</v>
+        <v>6761262</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6388,7 +6393,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6398,7 +6403,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6425,10 +6430,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128998638</v>
+        <v>128998999</v>
       </c>
       <c r="B55" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6436,39 +6441,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>492971</v>
+        <v>493048</v>
       </c>
       <c r="R55" t="n">
-        <v>6761075</v>
+        <v>6761092</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6649,53 +6649,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128990627</v>
+        <v>128995292</v>
       </c>
       <c r="B57" t="n">
-        <v>58097</v>
+        <v>79041</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>493483</v>
+        <v>492996</v>
       </c>
       <c r="R57" t="n">
-        <v>6761261</v>
+        <v>6761284</v>
       </c>
       <c r="S57" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6724,7 +6719,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6734,7 +6729,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6761,48 +6756,53 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128995292</v>
+        <v>128990627</v>
       </c>
       <c r="B58" t="n">
-        <v>79041</v>
+        <v>58097</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>492996</v>
+        <v>493483</v>
       </c>
       <c r="R58" t="n">
-        <v>6761284</v>
+        <v>6761261</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6978,7 +6978,7 @@
         <v>129015883</v>
       </c>
       <c r="B60" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 41794-2025 artfynd.xlsx
+++ b/artfynd/A 41794-2025 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128999532</v>
+        <v>128993314</v>
       </c>
       <c r="B4" t="n">
         <v>79041</v>
@@ -920,14 +920,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493157</v>
+        <v>493165</v>
       </c>
       <c r="R4" t="n">
-        <v>6761137</v>
+        <v>6761309</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128993314</v>
+        <v>128997543</v>
       </c>
       <c r="B5" t="n">
         <v>79041</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493165</v>
+        <v>492963</v>
       </c>
       <c r="R5" t="n">
-        <v>6761309</v>
+        <v>6761283</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128997543</v>
+        <v>128992649</v>
       </c>
       <c r="B6" t="n">
         <v>79041</v>
@@ -1139,14 +1134,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492963</v>
+        <v>493247</v>
       </c>
       <c r="R6" t="n">
-        <v>6761283</v>
+        <v>6761309</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128992649</v>
+        <v>128994822</v>
       </c>
       <c r="B7" t="n">
         <v>79041</v>
@@ -1246,14 +1241,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493247</v>
+        <v>493022</v>
       </c>
       <c r="R7" t="n">
-        <v>6761309</v>
+        <v>6761226</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128994822</v>
+        <v>128999532</v>
       </c>
       <c r="B8" t="n">
         <v>79041</v>
@@ -1353,14 +1348,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493022</v>
+        <v>493157</v>
       </c>
       <c r="R8" t="n">
-        <v>6761226</v>
+        <v>6761137</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,7 +1397,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,7 +1429,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128999256</v>
+        <v>128998367</v>
       </c>
       <c r="B9" t="n">
         <v>79041</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493048</v>
+        <v>492928</v>
       </c>
       <c r="R9" t="n">
-        <v>6761242</v>
+        <v>6761141</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128998367</v>
+        <v>128999256</v>
       </c>
       <c r="B10" t="n">
         <v>79041</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492928</v>
+        <v>493048</v>
       </c>
       <c r="R10" t="n">
-        <v>6761141</v>
+        <v>6761242</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1750,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128998263</v>
+        <v>128991903</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,39 +1761,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492885</v>
+        <v>493287</v>
       </c>
       <c r="R12" t="n">
-        <v>6761180</v>
+        <v>6761277</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1820,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1830,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,7 +1857,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128999613</v>
+        <v>128998263</v>
       </c>
       <c r="B13" t="n">
         <v>57724</v>
@@ -1902,7 +1897,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493205</v>
+        <v>492885</v>
       </c>
       <c r="R13" t="n">
         <v>6761180</v>
@@ -1937,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,7 +1969,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128997799</v>
+        <v>128999613</v>
       </c>
       <c r="B14" t="n">
         <v>57724</v>
@@ -2014,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492929</v>
+        <v>493205</v>
       </c>
       <c r="R14" t="n">
-        <v>6761272</v>
+        <v>6761180</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2059,7 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,7 +2081,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128998274</v>
+        <v>128997799</v>
       </c>
       <c r="B15" t="n">
         <v>57724</v>
@@ -2126,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492894</v>
+        <v>492929</v>
       </c>
       <c r="R15" t="n">
-        <v>6761171</v>
+        <v>6761272</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2198,45 +2193,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128990939</v>
+        <v>128998274</v>
       </c>
       <c r="B16" t="n">
-        <v>97576</v>
+        <v>57724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493487</v>
+        <v>492894</v>
       </c>
       <c r="R16" t="n">
-        <v>6761281</v>
+        <v>6761171</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2278,12 +2278,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,45 +2305,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128998025</v>
+        <v>128990939</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>97577</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492895</v>
+        <v>493487</v>
       </c>
       <c r="R17" t="n">
-        <v>6761212</v>
+        <v>6761281</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,7 +2375,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2390,7 +2385,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2417,7 +2417,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128991923</v>
+        <v>128998025</v>
       </c>
       <c r="B18" t="n">
         <v>79041</v>
@@ -2448,14 +2448,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493277</v>
+        <v>492895</v>
       </c>
       <c r="R18" t="n">
-        <v>6761265</v>
+        <v>6761212</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2524,7 +2524,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128991903</v>
+        <v>128991923</v>
       </c>
       <c r="B19" t="n">
         <v>79041</v>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493287</v>
+        <v>493277</v>
       </c>
       <c r="R19" t="n">
-        <v>6761277</v>
+        <v>6761265</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2631,7 +2631,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128994202</v>
+        <v>128991027</v>
       </c>
       <c r="B20" t="n">
         <v>79041</v>
@@ -2662,14 +2662,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493144</v>
+        <v>493464</v>
       </c>
       <c r="R20" t="n">
-        <v>6761263</v>
+        <v>6761291</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2845,7 +2845,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128991027</v>
+        <v>128994202</v>
       </c>
       <c r="B22" t="n">
         <v>79041</v>
@@ -2876,14 +2876,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493464</v>
+        <v>493144</v>
       </c>
       <c r="R22" t="n">
-        <v>6761291</v>
+        <v>6761263</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2952,10 +2952,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128998223</v>
+        <v>128991711</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2963,34 +2963,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492885</v>
+        <v>493310</v>
       </c>
       <c r="R23" t="n">
-        <v>6761180</v>
+        <v>6761241</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3022,7 +3027,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3032,7 +3037,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3059,7 +3064,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128998201</v>
+        <v>128998223</v>
       </c>
       <c r="B24" t="n">
         <v>79041</v>
@@ -3094,10 +3099,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492877</v>
+        <v>492885</v>
       </c>
       <c r="R24" t="n">
-        <v>6761211</v>
+        <v>6761180</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3166,10 +3171,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128991711</v>
+        <v>128998201</v>
       </c>
       <c r="B25" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3177,39 +3182,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493310</v>
+        <v>492877</v>
       </c>
       <c r="R25" t="n">
-        <v>6761241</v>
+        <v>6761211</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3278,45 +3278,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128994100</v>
+        <v>128995392</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>91561</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493167</v>
+        <v>492992</v>
       </c>
       <c r="R26" t="n">
-        <v>6761257</v>
+        <v>6761309</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3497,49 +3501,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128995392</v>
+        <v>128994100</v>
       </c>
       <c r="B28" t="n">
-        <v>91561</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492992</v>
+        <v>493167</v>
       </c>
       <c r="R28" t="n">
-        <v>6761309</v>
+        <v>6761257</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128995396</v>
+        <v>128994343</v>
       </c>
       <c r="B29" t="n">
         <v>79041</v>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492992</v>
+        <v>493103</v>
       </c>
       <c r="R29" t="n">
-        <v>6761309</v>
+        <v>6761270</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3715,7 +3715,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128994343</v>
+        <v>128995396</v>
       </c>
       <c r="B30" t="n">
         <v>79041</v>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493103</v>
+        <v>492992</v>
       </c>
       <c r="R30" t="n">
-        <v>6761270</v>
+        <v>6761309</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3929,45 +3929,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128994846</v>
+        <v>128991481</v>
       </c>
       <c r="B32" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493013</v>
+        <v>493300</v>
       </c>
       <c r="R32" t="n">
-        <v>6761220</v>
+        <v>6761215</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4036,45 +4036,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128991481</v>
+        <v>128994846</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493300</v>
+        <v>493013</v>
       </c>
       <c r="R33" t="n">
-        <v>6761215</v>
+        <v>6761220</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4250,7 +4250,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128994864</v>
+        <v>128993887</v>
       </c>
       <c r="B35" t="n">
         <v>79041</v>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493021</v>
+        <v>493167</v>
       </c>
       <c r="R35" t="n">
-        <v>6761214</v>
+        <v>6761257</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4357,7 +4357,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128993887</v>
+        <v>128997967</v>
       </c>
       <c r="B36" t="n">
         <v>79041</v>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493167</v>
+        <v>492949</v>
       </c>
       <c r="R36" t="n">
-        <v>6761257</v>
+        <v>6761266</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4438,6 +4438,11 @@
       <c r="AB36" t="inlineStr">
         <is>
           <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4571,7 +4576,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128997967</v>
+        <v>128994864</v>
       </c>
       <c r="B38" t="n">
         <v>79041</v>
@@ -4606,10 +4611,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>492949</v>
+        <v>493021</v>
       </c>
       <c r="R38" t="n">
-        <v>6761266</v>
+        <v>6761214</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4652,11 +4657,6 @@
       <c r="AB38" t="inlineStr">
         <is>
           <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4683,10 +4683,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128991491</v>
+        <v>128991964</v>
       </c>
       <c r="B39" t="n">
-        <v>57724</v>
+        <v>58157</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4694,27 +4694,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4723,13 +4723,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493290</v>
+        <v>493252</v>
       </c>
       <c r="R39" t="n">
-        <v>6761213</v>
+        <v>6761277</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128991964</v>
+        <v>128999032</v>
       </c>
       <c r="B40" t="n">
         <v>58157</v>
@@ -4831,17 +4831,17 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493252</v>
+        <v>493048</v>
       </c>
       <c r="R40" t="n">
-        <v>6761277</v>
+        <v>6761092</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4907,10 +4907,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128999032</v>
+        <v>128991491</v>
       </c>
       <c r="B41" t="n">
-        <v>58157</v>
+        <v>57724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4918,39 +4918,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103001</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493048</v>
+        <v>493290</v>
       </c>
       <c r="R41" t="n">
-        <v>6761092</v>
+        <v>6761213</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5126,10 +5126,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128994294</v>
+        <v>128994946</v>
       </c>
       <c r="B43" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5137,21 +5137,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5161,10 +5161,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493144</v>
+        <v>492986</v>
       </c>
       <c r="R43" t="n">
-        <v>6761263</v>
+        <v>6761194</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5233,7 +5233,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128999732</v>
+        <v>128991661</v>
       </c>
       <c r="B44" t="n">
         <v>79041</v>
@@ -5268,10 +5268,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>493327</v>
+        <v>493295</v>
       </c>
       <c r="R44" t="n">
-        <v>6761155</v>
+        <v>6761257</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5340,7 +5340,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128991661</v>
+        <v>128999732</v>
       </c>
       <c r="B45" t="n">
         <v>79041</v>
@@ -5375,10 +5375,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>493295</v>
+        <v>493327</v>
       </c>
       <c r="R45" t="n">
-        <v>6761257</v>
+        <v>6761155</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5447,10 +5447,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128994946</v>
+        <v>128994294</v>
       </c>
       <c r="B46" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5458,21 +5458,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5482,10 +5482,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492986</v>
+        <v>493144</v>
       </c>
       <c r="R46" t="n">
-        <v>6761194</v>
+        <v>6761263</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5554,32 +5554,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128998610</v>
+        <v>128999673</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5589,10 +5589,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492993</v>
+        <v>493255</v>
       </c>
       <c r="R47" t="n">
-        <v>6761086</v>
+        <v>6761127</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5661,32 +5661,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128999673</v>
+        <v>128998610</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5696,10 +5696,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493255</v>
+        <v>492993</v>
       </c>
       <c r="R48" t="n">
-        <v>6761127</v>
+        <v>6761086</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6211,10 +6211,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128998638</v>
+        <v>128998999</v>
       </c>
       <c r="B53" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6222,39 +6222,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>492971</v>
+        <v>493048</v>
       </c>
       <c r="R53" t="n">
-        <v>6761075</v>
+        <v>6761092</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6430,10 +6425,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128998999</v>
+        <v>128998638</v>
       </c>
       <c r="B55" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6441,34 +6436,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>493048</v>
+        <v>492971</v>
       </c>
       <c r="R55" t="n">
-        <v>6761092</v>
+        <v>6761075</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 41794-2025 artfynd.xlsx
+++ b/artfynd/A 41794-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128991347</v>
+        <v>128998779</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -706,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493372</v>
+        <v>492970</v>
       </c>
       <c r="R2" t="n">
-        <v>6761249</v>
+        <v>6761018</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128998779</v>
+        <v>128991347</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492970</v>
+        <v>493372</v>
       </c>
       <c r="R3" t="n">
-        <v>6761018</v>
+        <v>6761249</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>128993314</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128997543</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128992649</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128994822</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128999532</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>128998367</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>128999256</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>128999351</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>128991903</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1857,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128998263</v>
+        <v>128998025</v>
       </c>
       <c r="B13" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,39 +1868,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492885</v>
+        <v>492895</v>
       </c>
       <c r="R13" t="n">
-        <v>6761180</v>
+        <v>6761212</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1969,10 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128999613</v>
+        <v>128991923</v>
       </c>
       <c r="B14" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,39 +1975,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493205</v>
+        <v>493277</v>
       </c>
       <c r="R14" t="n">
-        <v>6761180</v>
+        <v>6761265</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,7 +2034,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2044,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,7 +2071,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128997799</v>
+        <v>128998263</v>
       </c>
       <c r="B15" t="n">
         <v>57724</v>
@@ -2121,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492929</v>
+        <v>492885</v>
       </c>
       <c r="R15" t="n">
-        <v>6761272</v>
+        <v>6761180</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2193,7 +2183,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128998274</v>
+        <v>128999613</v>
       </c>
       <c r="B16" t="n">
         <v>57724</v>
@@ -2233,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492894</v>
+        <v>493205</v>
       </c>
       <c r="R16" t="n">
-        <v>6761171</v>
+        <v>6761180</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2278,7 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2305,45 +2295,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128990939</v>
+        <v>128997799</v>
       </c>
       <c r="B17" t="n">
-        <v>97577</v>
+        <v>57724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493487</v>
+        <v>492929</v>
       </c>
       <c r="R17" t="n">
-        <v>6761281</v>
+        <v>6761272</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2375,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2385,12 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2417,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128998025</v>
+        <v>128998274</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,34 +2418,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492895</v>
+        <v>492894</v>
       </c>
       <c r="R18" t="n">
-        <v>6761212</v>
+        <v>6761171</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2524,32 +2519,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128991923</v>
+        <v>128990939</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>97581</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2559,10 +2554,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493277</v>
+        <v>493487</v>
       </c>
       <c r="R19" t="n">
-        <v>6761265</v>
+        <v>6761281</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2605,6 +2600,11 @@
       <c r="AB19" t="inlineStr">
         <is>
           <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2634,7 +2634,7 @@
         <v>128991027</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>128998438</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>128994202</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>128998223</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>128998201</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>128995392</v>
       </c>
       <c r="B26" t="n">
-        <v>91561</v>
+        <v>91564</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>128990886</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>128994343</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>128995396</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3929,45 +3929,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128991481</v>
+        <v>128994846</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493300</v>
+        <v>493013</v>
       </c>
       <c r="R32" t="n">
-        <v>6761215</v>
+        <v>6761220</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4036,45 +4036,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128994846</v>
+        <v>128991481</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493013</v>
+        <v>493300</v>
       </c>
       <c r="R33" t="n">
-        <v>6761220</v>
+        <v>6761215</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4146,7 +4146,7 @@
         <v>128994977</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>128993887</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>128997967</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4469,10 +4469,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128994367</v>
+        <v>128994864</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493118</v>
+        <v>493021</v>
       </c>
       <c r="R37" t="n">
-        <v>6761310</v>
+        <v>6761214</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4576,10 +4576,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128994864</v>
+        <v>128994367</v>
       </c>
       <c r="B38" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493021</v>
+        <v>493118</v>
       </c>
       <c r="R38" t="n">
-        <v>6761214</v>
+        <v>6761310</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4683,10 +4683,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128991964</v>
+        <v>128991491</v>
       </c>
       <c r="B39" t="n">
-        <v>58157</v>
+        <v>57724</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4694,27 +4694,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103001</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4723,13 +4723,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493252</v>
+        <v>493290</v>
       </c>
       <c r="R39" t="n">
-        <v>6761277</v>
+        <v>6761213</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128999032</v>
+        <v>128991964</v>
       </c>
       <c r="B40" t="n">
         <v>58157</v>
@@ -4831,17 +4831,17 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493048</v>
+        <v>493252</v>
       </c>
       <c r="R40" t="n">
-        <v>6761092</v>
+        <v>6761277</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4907,10 +4907,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128991491</v>
+        <v>128999032</v>
       </c>
       <c r="B41" t="n">
-        <v>57724</v>
+        <v>58157</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4918,39 +4918,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493290</v>
+        <v>493048</v>
       </c>
       <c r="R41" t="n">
-        <v>6761213</v>
+        <v>6761092</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5022,7 +5022,7 @@
         <v>128995173</v>
       </c>
       <c r="B42" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>128994946</v>
       </c>
       <c r="B43" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>128991661</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>128999732</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>128994294</v>
       </c>
       <c r="B46" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>128998610</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5992,10 +5992,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128999627</v>
+        <v>128994661</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6003,34 +6003,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493222</v>
+        <v>493048</v>
       </c>
       <c r="R51" t="n">
-        <v>6761162</v>
+        <v>6761242</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6062,7 +6067,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6072,7 +6077,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6099,10 +6104,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128994661</v>
+        <v>128999627</v>
       </c>
       <c r="B52" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6110,39 +6115,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493048</v>
+        <v>493222</v>
       </c>
       <c r="R52" t="n">
-        <v>6761242</v>
+        <v>6761162</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6214,7 +6214,7 @@
         <v>128998999</v>
       </c>
       <c r="B53" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>128991818</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6649,48 +6649,53 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128995292</v>
+        <v>128990627</v>
       </c>
       <c r="B57" t="n">
-        <v>79041</v>
+        <v>58097</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>492996</v>
+        <v>493483</v>
       </c>
       <c r="R57" t="n">
-        <v>6761284</v>
+        <v>6761261</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6719,7 +6724,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6729,7 +6734,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6756,53 +6761,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128990627</v>
+        <v>128995292</v>
       </c>
       <c r="B58" t="n">
-        <v>58097</v>
+        <v>79043</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>493483</v>
+        <v>492996</v>
       </c>
       <c r="R58" t="n">
-        <v>6761261</v>
+        <v>6761284</v>
       </c>
       <c r="S58" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6871,7 +6871,7 @@
         <v>128994922</v>
       </c>
       <c r="B59" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>129015883</v>
       </c>
       <c r="B60" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 41794-2025 artfynd.xlsx
+++ b/artfynd/A 41794-2025 artfynd.xlsx
@@ -2952,10 +2952,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128991711</v>
+        <v>128998223</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2963,39 +2963,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493310</v>
+        <v>492885</v>
       </c>
       <c r="R23" t="n">
-        <v>6761241</v>
+        <v>6761180</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3027,7 +3022,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3037,7 +3032,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3064,7 +3059,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128998223</v>
+        <v>128998201</v>
       </c>
       <c r="B24" t="n">
         <v>79043</v>
@@ -3099,10 +3094,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492885</v>
+        <v>492877</v>
       </c>
       <c r="R24" t="n">
-        <v>6761180</v>
+        <v>6761211</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3171,10 +3166,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128998201</v>
+        <v>128991711</v>
       </c>
       <c r="B25" t="n">
-        <v>79043</v>
+        <v>57724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3182,34 +3177,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492877</v>
+        <v>493310</v>
       </c>
       <c r="R25" t="n">
-        <v>6761211</v>
+        <v>6761241</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3278,49 +3278,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128995392</v>
+        <v>128994100</v>
       </c>
       <c r="B26" t="n">
-        <v>91564</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492992</v>
+        <v>493167</v>
       </c>
       <c r="R26" t="n">
-        <v>6761309</v>
+        <v>6761257</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3389,10 +3385,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128990886</v>
+        <v>128995392</v>
       </c>
       <c r="B27" t="n">
-        <v>79043</v>
+        <v>91564</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3400,34 +3396,38 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493487</v>
+        <v>492992</v>
       </c>
       <c r="R27" t="n">
-        <v>6761281</v>
+        <v>6761309</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3469,12 +3469,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Sumpskogskaraktär i området här.</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3501,45 +3496,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128994100</v>
+        <v>128990886</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493167</v>
+        <v>493487</v>
       </c>
       <c r="R28" t="n">
-        <v>6761257</v>
+        <v>6761281</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3571,7 +3566,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3581,7 +3576,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Sumpskogskaraktär i området här.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -6649,53 +6649,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128990627</v>
+        <v>128995292</v>
       </c>
       <c r="B57" t="n">
-        <v>58097</v>
+        <v>79043</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>493483</v>
+        <v>492996</v>
       </c>
       <c r="R57" t="n">
-        <v>6761261</v>
+        <v>6761284</v>
       </c>
       <c r="S57" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6724,7 +6719,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6734,7 +6729,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6761,48 +6756,53 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128995292</v>
+        <v>128990627</v>
       </c>
       <c r="B58" t="n">
-        <v>79043</v>
+        <v>58097</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>492996</v>
+        <v>493483</v>
       </c>
       <c r="R58" t="n">
-        <v>6761284</v>
+        <v>6761261</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 41794-2025 artfynd.xlsx
+++ b/artfynd/A 41794-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128998779</v>
+        <v>128991347</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -706,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492970</v>
+        <v>493372</v>
       </c>
       <c r="R2" t="n">
-        <v>6761018</v>
+        <v>6761249</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128991347</v>
+        <v>128998779</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493372</v>
+        <v>492970</v>
       </c>
       <c r="R3" t="n">
-        <v>6761249</v>
+        <v>6761018</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128993314</v>
+        <v>128999532</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,14 +920,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493165</v>
+        <v>493157</v>
       </c>
       <c r="R4" t="n">
-        <v>6761309</v>
+        <v>6761137</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128997543</v>
+        <v>128993314</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492963</v>
+        <v>493165</v>
       </c>
       <c r="R5" t="n">
-        <v>6761283</v>
+        <v>6761309</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128992649</v>
+        <v>128997543</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,14 +1139,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493247</v>
+        <v>492963</v>
       </c>
       <c r="R6" t="n">
-        <v>6761309</v>
+        <v>6761283</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128994822</v>
+        <v>128992649</v>
       </c>
       <c r="B7" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,14 +1246,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493022</v>
+        <v>493247</v>
       </c>
       <c r="R7" t="n">
-        <v>6761226</v>
+        <v>6761309</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128999532</v>
+        <v>128994822</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,14 +1353,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493157</v>
+        <v>493022</v>
       </c>
       <c r="R8" t="n">
-        <v>6761137</v>
+        <v>6761226</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,12 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128998367</v>
+        <v>128999256</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492928</v>
+        <v>493048</v>
       </c>
       <c r="R9" t="n">
-        <v>6761141</v>
+        <v>6761242</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128999256</v>
+        <v>128998367</v>
       </c>
       <c r="B10" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493048</v>
+        <v>492928</v>
       </c>
       <c r="R10" t="n">
-        <v>6761242</v>
+        <v>6761141</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,7 +1646,7 @@
         <v>128999351</v>
       </c>
       <c r="B11" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1750,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128991903</v>
+        <v>128990939</v>
       </c>
       <c r="B12" t="n">
-        <v>79043</v>
+        <v>97583</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493287</v>
+        <v>493487</v>
       </c>
       <c r="R12" t="n">
-        <v>6761277</v>
+        <v>6761281</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1831,6 +1831,11 @@
       <c r="AB12" t="inlineStr">
         <is>
           <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1857,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128998025</v>
+        <v>128998263</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>57724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,34 +1873,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492895</v>
+        <v>492885</v>
       </c>
       <c r="R13" t="n">
-        <v>6761212</v>
+        <v>6761180</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1964,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128991923</v>
+        <v>128999613</v>
       </c>
       <c r="B14" t="n">
-        <v>79043</v>
+        <v>57724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1975,34 +1985,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493277</v>
+        <v>493205</v>
       </c>
       <c r="R14" t="n">
-        <v>6761265</v>
+        <v>6761180</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +2049,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2044,7 +2059,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,7 +2086,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128998263</v>
+        <v>128997799</v>
       </c>
       <c r="B15" t="n">
         <v>57724</v>
@@ -2111,10 +2126,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492885</v>
+        <v>492929</v>
       </c>
       <c r="R15" t="n">
-        <v>6761180</v>
+        <v>6761272</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,7 +2198,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128999613</v>
+        <v>128998274</v>
       </c>
       <c r="B16" t="n">
         <v>57724</v>
@@ -2223,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493205</v>
+        <v>492894</v>
       </c>
       <c r="R16" t="n">
-        <v>6761180</v>
+        <v>6761171</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2268,7 +2283,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,10 +2310,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128997799</v>
+        <v>128998025</v>
       </c>
       <c r="B17" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2306,39 +2321,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492929</v>
+        <v>492895</v>
       </c>
       <c r="R17" t="n">
-        <v>6761272</v>
+        <v>6761212</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2407,10 +2417,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128998274</v>
+        <v>128991923</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2418,39 +2428,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492894</v>
+        <v>493277</v>
       </c>
       <c r="R18" t="n">
-        <v>6761171</v>
+        <v>6761265</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,7 +2487,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2492,7 +2497,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2519,32 +2524,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128990939</v>
+        <v>128991903</v>
       </c>
       <c r="B19" t="n">
-        <v>97581</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2554,10 +2559,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493487</v>
+        <v>493287</v>
       </c>
       <c r="R19" t="n">
-        <v>6761281</v>
+        <v>6761277</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2600,11 +2605,6 @@
       <c r="AB19" t="inlineStr">
         <is>
           <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2631,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128991027</v>
+        <v>128994202</v>
       </c>
       <c r="B20" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2662,14 +2662,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493464</v>
+        <v>493144</v>
       </c>
       <c r="R20" t="n">
-        <v>6761291</v>
+        <v>6761263</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2741,7 +2741,7 @@
         <v>128998438</v>
       </c>
       <c r="B21" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2845,10 +2845,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128994202</v>
+        <v>128991027</v>
       </c>
       <c r="B22" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2876,14 +2876,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493144</v>
+        <v>493464</v>
       </c>
       <c r="R22" t="n">
-        <v>6761263</v>
+        <v>6761291</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2955,7 +2955,7 @@
         <v>128998223</v>
       </c>
       <c r="B23" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3059,10 +3059,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128998201</v>
+        <v>128991711</v>
       </c>
       <c r="B24" t="n">
-        <v>79043</v>
+        <v>57724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3070,34 +3070,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492877</v>
+        <v>493310</v>
       </c>
       <c r="R24" t="n">
-        <v>6761211</v>
+        <v>6761241</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3129,7 +3134,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3139,7 +3144,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3166,10 +3171,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128991711</v>
+        <v>128998201</v>
       </c>
       <c r="B25" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3177,39 +3182,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493310</v>
+        <v>492877</v>
       </c>
       <c r="R25" t="n">
-        <v>6761241</v>
+        <v>6761211</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3388,7 +3388,7 @@
         <v>128995392</v>
       </c>
       <c r="B27" t="n">
-        <v>91564</v>
+        <v>91566</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>128990886</v>
       </c>
       <c r="B28" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>128994343</v>
       </c>
       <c r="B29" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>128995396</v>
       </c>
       <c r="B30" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>128994846</v>
       </c>
       <c r="B32" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>128994977</v>
       </c>
       <c r="B34" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4250,10 +4250,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128993887</v>
+        <v>128991491</v>
       </c>
       <c r="B35" t="n">
-        <v>79043</v>
+        <v>57724</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4261,34 +4261,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493167</v>
+        <v>493290</v>
       </c>
       <c r="R35" t="n">
-        <v>6761257</v>
+        <v>6761213</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4320,7 +4325,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4330,7 +4335,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4357,10 +4362,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128997967</v>
+        <v>128994864</v>
       </c>
       <c r="B36" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4392,10 +4397,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492949</v>
+        <v>493021</v>
       </c>
       <c r="R36" t="n">
-        <v>6761266</v>
+        <v>6761214</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4438,11 +4443,6 @@
       <c r="AB36" t="inlineStr">
         <is>
           <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4469,10 +4469,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128994864</v>
+        <v>128993887</v>
       </c>
       <c r="B37" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493021</v>
+        <v>493167</v>
       </c>
       <c r="R37" t="n">
-        <v>6761214</v>
+        <v>6761257</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4579,7 +4579,7 @@
         <v>128994367</v>
       </c>
       <c r="B38" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4683,10 +4683,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128991491</v>
+        <v>128997967</v>
       </c>
       <c r="B39" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4694,39 +4694,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493290</v>
+        <v>492949</v>
       </c>
       <c r="R39" t="n">
-        <v>6761213</v>
+        <v>6761266</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4758,7 +4753,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4768,7 +4763,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5019,10 +5019,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128995173</v>
+        <v>128994294</v>
       </c>
       <c r="B42" t="n">
-        <v>79043</v>
+        <v>79663</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493010</v>
+        <v>493144</v>
       </c>
       <c r="R42" t="n">
-        <v>6761236</v>
+        <v>6761263</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5126,10 +5126,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128994946</v>
+        <v>128999732</v>
       </c>
       <c r="B43" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5157,14 +5157,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492986</v>
+        <v>493327</v>
       </c>
       <c r="R43" t="n">
-        <v>6761194</v>
+        <v>6761155</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5233,10 +5233,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128991661</v>
+        <v>128994946</v>
       </c>
       <c r="B44" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5264,14 +5264,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>493295</v>
+        <v>492986</v>
       </c>
       <c r="R44" t="n">
-        <v>6761257</v>
+        <v>6761194</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5340,10 +5340,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128999732</v>
+        <v>128995173</v>
       </c>
       <c r="B45" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5371,14 +5371,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>493327</v>
+        <v>493010</v>
       </c>
       <c r="R45" t="n">
-        <v>6761155</v>
+        <v>6761236</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5447,10 +5447,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128994294</v>
+        <v>128991661</v>
       </c>
       <c r="B46" t="n">
-        <v>79662</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5458,34 +5458,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493144</v>
+        <v>493295</v>
       </c>
       <c r="R46" t="n">
-        <v>6761263</v>
+        <v>6761257</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5554,45 +5554,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128999673</v>
+        <v>128991653</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493255</v>
+        <v>493295</v>
       </c>
       <c r="R47" t="n">
-        <v>6761127</v>
+        <v>6761257</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5624,7 +5629,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5634,7 +5639,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5661,10 +5666,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128998610</v>
+        <v>128994503</v>
       </c>
       <c r="B48" t="n">
-        <v>79043</v>
+        <v>57724</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5672,34 +5677,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492993</v>
+        <v>493047</v>
       </c>
       <c r="R48" t="n">
-        <v>6761086</v>
+        <v>6761263</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5731,7 +5741,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5741,7 +5751,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5768,10 +5778,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128991653</v>
+        <v>128998610</v>
       </c>
       <c r="B49" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5779,39 +5789,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493295</v>
+        <v>492993</v>
       </c>
       <c r="R49" t="n">
-        <v>6761257</v>
+        <v>6761086</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5843,7 +5848,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5853,7 +5858,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5880,50 +5885,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128994503</v>
+        <v>128999673</v>
       </c>
       <c r="B50" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493047</v>
+        <v>493255</v>
       </c>
       <c r="R50" t="n">
-        <v>6761263</v>
+        <v>6761127</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5992,10 +5992,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128994661</v>
+        <v>128999627</v>
       </c>
       <c r="B51" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6003,39 +6003,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493048</v>
+        <v>493222</v>
       </c>
       <c r="R51" t="n">
-        <v>6761242</v>
+        <v>6761162</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6067,7 +6062,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6077,7 +6072,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6104,10 +6099,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128999627</v>
+        <v>128994661</v>
       </c>
       <c r="B52" t="n">
-        <v>79043</v>
+        <v>57724</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6115,34 +6110,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493222</v>
+        <v>493048</v>
       </c>
       <c r="R52" t="n">
-        <v>6761162</v>
+        <v>6761242</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6211,10 +6211,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128998999</v>
+        <v>128991818</v>
       </c>
       <c r="B53" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6242,14 +6242,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>493048</v>
+        <v>493312</v>
       </c>
       <c r="R53" t="n">
-        <v>6761092</v>
+        <v>6761262</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6318,10 +6318,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128991818</v>
+        <v>128998999</v>
       </c>
       <c r="B54" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6349,14 +6349,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493312</v>
+        <v>493048</v>
       </c>
       <c r="R54" t="n">
-        <v>6761262</v>
+        <v>6761092</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6652,7 +6652,7 @@
         <v>128995292</v>
       </c>
       <c r="B57" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>128994922</v>
       </c>
       <c r="B59" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>129015883</v>
       </c>
       <c r="B60" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 41794-2025 artfynd.xlsx
+++ b/artfynd/A 41794-2025 artfynd.xlsx
@@ -1750,45 +1750,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128990939</v>
+        <v>128998025</v>
       </c>
       <c r="B12" t="n">
-        <v>97583</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493487</v>
+        <v>492895</v>
       </c>
       <c r="R12" t="n">
-        <v>6761281</v>
+        <v>6761212</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1830,12 +1830,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128998263</v>
+        <v>128991923</v>
       </c>
       <c r="B13" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,39 +1868,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492885</v>
+        <v>493277</v>
       </c>
       <c r="R13" t="n">
-        <v>6761180</v>
+        <v>6761265</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,7 +1927,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1937,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,10 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128999613</v>
+        <v>128991903</v>
       </c>
       <c r="B14" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,39 +1975,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493205</v>
+        <v>493287</v>
       </c>
       <c r="R14" t="n">
-        <v>6761180</v>
+        <v>6761277</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,7 +2034,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2059,7 +2044,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,7 +2071,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128997799</v>
+        <v>128998263</v>
       </c>
       <c r="B15" t="n">
         <v>57724</v>
@@ -2126,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492929</v>
+        <v>492885</v>
       </c>
       <c r="R15" t="n">
-        <v>6761272</v>
+        <v>6761180</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2198,7 +2183,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128998274</v>
+        <v>128999613</v>
       </c>
       <c r="B16" t="n">
         <v>57724</v>
@@ -2238,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492894</v>
+        <v>493205</v>
       </c>
       <c r="R16" t="n">
-        <v>6761171</v>
+        <v>6761180</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2283,7 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128998025</v>
+        <v>128997799</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,34 +2306,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492895</v>
+        <v>492929</v>
       </c>
       <c r="R17" t="n">
-        <v>6761212</v>
+        <v>6761272</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2417,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128991923</v>
+        <v>128998274</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,34 +2418,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493277</v>
+        <v>492894</v>
       </c>
       <c r="R18" t="n">
-        <v>6761265</v>
+        <v>6761171</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2487,7 +2482,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2497,7 +2492,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2524,32 +2519,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128991903</v>
+        <v>128990939</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>97587</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2559,10 +2554,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493287</v>
+        <v>493487</v>
       </c>
       <c r="R19" t="n">
-        <v>6761277</v>
+        <v>6761281</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2605,6 +2600,11 @@
       <c r="AB19" t="inlineStr">
         <is>
           <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2952,10 +2952,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128998223</v>
+        <v>128991711</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2963,34 +2963,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492885</v>
+        <v>493310</v>
       </c>
       <c r="R23" t="n">
-        <v>6761180</v>
+        <v>6761241</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3022,7 +3027,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3032,7 +3037,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3059,10 +3064,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128991711</v>
+        <v>128998223</v>
       </c>
       <c r="B24" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3070,39 +3075,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493310</v>
+        <v>492885</v>
       </c>
       <c r="R24" t="n">
-        <v>6761241</v>
+        <v>6761180</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3278,45 +3278,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128994100</v>
+        <v>128990886</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493167</v>
+        <v>493487</v>
       </c>
       <c r="R26" t="n">
-        <v>6761257</v>
+        <v>6761281</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3358,7 +3358,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Sumpskogskaraktär i området här.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3388,7 +3393,7 @@
         <v>128995392</v>
       </c>
       <c r="B27" t="n">
-        <v>91566</v>
+        <v>91570</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3496,45 +3501,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128990886</v>
+        <v>128994100</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493487</v>
+        <v>493167</v>
       </c>
       <c r="R28" t="n">
-        <v>6761281</v>
+        <v>6761257</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3566,7 +3571,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3576,12 +3581,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Sumpskogskaraktär i området här.</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3608,7 +3608,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128994343</v>
+        <v>128995396</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493103</v>
+        <v>492992</v>
       </c>
       <c r="R29" t="n">
-        <v>6761270</v>
+        <v>6761309</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3715,7 +3715,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128995396</v>
+        <v>128994343</v>
       </c>
       <c r="B30" t="n">
         <v>79044</v>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492992</v>
+        <v>493103</v>
       </c>
       <c r="R30" t="n">
-        <v>6761309</v>
+        <v>6761270</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4250,10 +4250,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128991491</v>
+        <v>128994864</v>
       </c>
       <c r="B35" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4261,39 +4261,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493290</v>
+        <v>493021</v>
       </c>
       <c r="R35" t="n">
-        <v>6761213</v>
+        <v>6761214</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4325,7 +4320,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4335,7 +4330,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4362,7 +4357,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128994864</v>
+        <v>128993887</v>
       </c>
       <c r="B36" t="n">
         <v>79044</v>
@@ -4397,10 +4392,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493021</v>
+        <v>493167</v>
       </c>
       <c r="R36" t="n">
-        <v>6761214</v>
+        <v>6761257</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4469,7 +4464,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128993887</v>
+        <v>128994367</v>
       </c>
       <c r="B37" t="n">
         <v>79044</v>
@@ -4504,10 +4499,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493167</v>
+        <v>493118</v>
       </c>
       <c r="R37" t="n">
-        <v>6761257</v>
+        <v>6761310</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4576,7 +4571,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128994367</v>
+        <v>128997967</v>
       </c>
       <c r="B38" t="n">
         <v>79044</v>
@@ -4611,10 +4606,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493118</v>
+        <v>492949</v>
       </c>
       <c r="R38" t="n">
-        <v>6761310</v>
+        <v>6761266</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4657,6 +4652,11 @@
       <c r="AB38" t="inlineStr">
         <is>
           <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4683,10 +4683,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128997967</v>
+        <v>128991491</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4694,34 +4694,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492949</v>
+        <v>493290</v>
       </c>
       <c r="R39" t="n">
-        <v>6761266</v>
+        <v>6761213</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4753,7 +4758,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4763,12 +4768,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4795,7 +4795,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128991964</v>
+        <v>128999032</v>
       </c>
       <c r="B40" t="n">
         <v>58157</v>
@@ -4831,17 +4831,17 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493252</v>
+        <v>493048</v>
       </c>
       <c r="R40" t="n">
-        <v>6761277</v>
+        <v>6761092</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4907,7 +4907,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128999032</v>
+        <v>128991964</v>
       </c>
       <c r="B41" t="n">
         <v>58157</v>
@@ -4943,17 +4943,17 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493048</v>
+        <v>493252</v>
       </c>
       <c r="R41" t="n">
-        <v>6761092</v>
+        <v>6761277</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5019,10 +5019,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128994294</v>
+        <v>128995173</v>
       </c>
       <c r="B42" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493144</v>
+        <v>493010</v>
       </c>
       <c r="R42" t="n">
-        <v>6761263</v>
+        <v>6761236</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5233,7 +5233,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128994946</v>
+        <v>128991661</v>
       </c>
       <c r="B44" t="n">
         <v>79044</v>
@@ -5264,14 +5264,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492986</v>
+        <v>493295</v>
       </c>
       <c r="R44" t="n">
-        <v>6761194</v>
+        <v>6761257</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5340,7 +5340,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128995173</v>
+        <v>128994946</v>
       </c>
       <c r="B45" t="n">
         <v>79044</v>
@@ -5375,10 +5375,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>493010</v>
+        <v>492986</v>
       </c>
       <c r="R45" t="n">
-        <v>6761236</v>
+        <v>6761194</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5447,10 +5447,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128991661</v>
+        <v>128994294</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5458,34 +5458,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493295</v>
+        <v>493144</v>
       </c>
       <c r="R46" t="n">
-        <v>6761257</v>
+        <v>6761263</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5554,50 +5554,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128991653</v>
+        <v>128999673</v>
       </c>
       <c r="B47" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493295</v>
+        <v>493255</v>
       </c>
       <c r="R47" t="n">
-        <v>6761257</v>
+        <v>6761127</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5629,7 +5624,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5639,7 +5634,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5666,10 +5661,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128994503</v>
+        <v>128998610</v>
       </c>
       <c r="B48" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5677,39 +5672,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493047</v>
+        <v>492993</v>
       </c>
       <c r="R48" t="n">
-        <v>6761263</v>
+        <v>6761086</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5741,7 +5731,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5751,7 +5741,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5778,10 +5768,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128998610</v>
+        <v>128991653</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5789,34 +5779,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492993</v>
+        <v>493295</v>
       </c>
       <c r="R49" t="n">
-        <v>6761086</v>
+        <v>6761257</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5848,7 +5843,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5858,7 +5853,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5885,45 +5880,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128999673</v>
+        <v>128994503</v>
       </c>
       <c r="B50" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493255</v>
+        <v>493047</v>
       </c>
       <c r="R50" t="n">
-        <v>6761127</v>
+        <v>6761263</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5992,10 +5992,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128999627</v>
+        <v>128994661</v>
       </c>
       <c r="B51" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6003,34 +6003,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493222</v>
+        <v>493048</v>
       </c>
       <c r="R51" t="n">
-        <v>6761162</v>
+        <v>6761242</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6062,7 +6067,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6072,7 +6077,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6099,10 +6104,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128994661</v>
+        <v>128999627</v>
       </c>
       <c r="B52" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6110,39 +6115,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493048</v>
+        <v>493222</v>
       </c>
       <c r="R52" t="n">
-        <v>6761242</v>
+        <v>6761162</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6978,7 +6978,7 @@
         <v>129015883</v>
       </c>
       <c r="B60" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 41794-2025 artfynd.xlsx
+++ b/artfynd/A 41794-2025 artfynd.xlsx
@@ -1750,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128998025</v>
+        <v>128998263</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,34 +1761,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492895</v>
+        <v>492885</v>
       </c>
       <c r="R12" t="n">
-        <v>6761212</v>
+        <v>6761180</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128991923</v>
+        <v>128999613</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,34 +1873,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493277</v>
+        <v>493205</v>
       </c>
       <c r="R13" t="n">
-        <v>6761265</v>
+        <v>6761180</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1937,7 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1964,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128991903</v>
+        <v>128997799</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1975,34 +1985,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493287</v>
+        <v>492929</v>
       </c>
       <c r="R14" t="n">
-        <v>6761277</v>
+        <v>6761272</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +2049,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2044,7 +2059,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,7 +2086,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128998263</v>
+        <v>128998274</v>
       </c>
       <c r="B15" t="n">
         <v>57724</v>
@@ -2111,10 +2126,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492885</v>
+        <v>492894</v>
       </c>
       <c r="R15" t="n">
-        <v>6761180</v>
+        <v>6761171</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128999613</v>
+        <v>128998025</v>
       </c>
       <c r="B16" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,39 +2209,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493205</v>
+        <v>492895</v>
       </c>
       <c r="R16" t="n">
-        <v>6761180</v>
+        <v>6761212</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,7 +2268,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2268,7 +2278,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128997799</v>
+        <v>128991923</v>
       </c>
       <c r="B17" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2306,39 +2316,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492929</v>
+        <v>493277</v>
       </c>
       <c r="R17" t="n">
-        <v>6761272</v>
+        <v>6761265</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2375,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2385,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,10 +2412,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128998274</v>
+        <v>128991903</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2418,39 +2423,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492894</v>
+        <v>493287</v>
       </c>
       <c r="R18" t="n">
-        <v>6761171</v>
+        <v>6761277</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2522,7 +2522,7 @@
         <v>128990939</v>
       </c>
       <c r="B19" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3390,49 +3390,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128995392</v>
+        <v>128994100</v>
       </c>
       <c r="B27" t="n">
-        <v>91570</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492992</v>
+        <v>493167</v>
       </c>
       <c r="R27" t="n">
-        <v>6761309</v>
+        <v>6761257</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3501,45 +3497,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128994100</v>
+        <v>128995392</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>91571</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493167</v>
+        <v>492992</v>
       </c>
       <c r="R28" t="n">
-        <v>6761257</v>
+        <v>6761309</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3929,45 +3929,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128994846</v>
+        <v>128991481</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493013</v>
+        <v>493300</v>
       </c>
       <c r="R32" t="n">
-        <v>6761220</v>
+        <v>6761215</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4036,45 +4036,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128991481</v>
+        <v>128994846</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493300</v>
+        <v>493013</v>
       </c>
       <c r="R33" t="n">
-        <v>6761215</v>
+        <v>6761220</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4250,10 +4250,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128994864</v>
+        <v>128991491</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4261,34 +4261,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493021</v>
+        <v>493290</v>
       </c>
       <c r="R35" t="n">
-        <v>6761214</v>
+        <v>6761213</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4320,7 +4325,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4330,7 +4335,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4357,7 +4362,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128993887</v>
+        <v>128994864</v>
       </c>
       <c r="B36" t="n">
         <v>79044</v>
@@ -4392,10 +4397,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493167</v>
+        <v>493021</v>
       </c>
       <c r="R36" t="n">
-        <v>6761257</v>
+        <v>6761214</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4464,7 +4469,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128994367</v>
+        <v>128993887</v>
       </c>
       <c r="B37" t="n">
         <v>79044</v>
@@ -4499,10 +4504,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493118</v>
+        <v>493167</v>
       </c>
       <c r="R37" t="n">
-        <v>6761310</v>
+        <v>6761257</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4571,7 +4576,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128997967</v>
+        <v>128994367</v>
       </c>
       <c r="B38" t="n">
         <v>79044</v>
@@ -4606,10 +4611,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>492949</v>
+        <v>493118</v>
       </c>
       <c r="R38" t="n">
-        <v>6761266</v>
+        <v>6761310</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4652,11 +4657,6 @@
       <c r="AB38" t="inlineStr">
         <is>
           <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4683,10 +4683,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128991491</v>
+        <v>128991964</v>
       </c>
       <c r="B39" t="n">
-        <v>57724</v>
+        <v>58157</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4694,27 +4694,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4723,13 +4723,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493290</v>
+        <v>493252</v>
       </c>
       <c r="R39" t="n">
-        <v>6761213</v>
+        <v>6761277</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4907,10 +4907,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128991964</v>
+        <v>128997967</v>
       </c>
       <c r="B41" t="n">
-        <v>58157</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4918,42 +4918,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493252</v>
+        <v>492949</v>
       </c>
       <c r="R41" t="n">
-        <v>6761277</v>
+        <v>6761266</v>
       </c>
       <c r="S41" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4982,7 +4977,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4992,7 +4987,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5019,7 +5019,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128995173</v>
+        <v>128991661</v>
       </c>
       <c r="B42" t="n">
         <v>79044</v>
@@ -5050,14 +5050,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493010</v>
+        <v>493295</v>
       </c>
       <c r="R42" t="n">
-        <v>6761236</v>
+        <v>6761257</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5126,7 +5126,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128999732</v>
+        <v>128994946</v>
       </c>
       <c r="B43" t="n">
         <v>79044</v>
@@ -5157,14 +5157,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493327</v>
+        <v>492986</v>
       </c>
       <c r="R43" t="n">
-        <v>6761155</v>
+        <v>6761194</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5233,7 +5233,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128991661</v>
+        <v>128995173</v>
       </c>
       <c r="B44" t="n">
         <v>79044</v>
@@ -5264,14 +5264,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>493295</v>
+        <v>493010</v>
       </c>
       <c r="R44" t="n">
-        <v>6761257</v>
+        <v>6761236</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5340,10 +5340,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128994946</v>
+        <v>128994294</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5351,21 +5351,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5375,10 +5375,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>492986</v>
+        <v>493144</v>
       </c>
       <c r="R45" t="n">
-        <v>6761194</v>
+        <v>6761263</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5447,10 +5447,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128994294</v>
+        <v>128999732</v>
       </c>
       <c r="B46" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5458,34 +5458,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493144</v>
+        <v>493327</v>
       </c>
       <c r="R46" t="n">
-        <v>6761263</v>
+        <v>6761155</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5554,45 +5554,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128999673</v>
+        <v>128991653</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493255</v>
+        <v>493295</v>
       </c>
       <c r="R47" t="n">
-        <v>6761127</v>
+        <v>6761257</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5624,7 +5629,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5634,7 +5639,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5661,10 +5666,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128998610</v>
+        <v>128994503</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5672,34 +5677,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492993</v>
+        <v>493047</v>
       </c>
       <c r="R48" t="n">
-        <v>6761086</v>
+        <v>6761263</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5731,7 +5741,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5741,7 +5751,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5768,10 +5778,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128991653</v>
+        <v>128998610</v>
       </c>
       <c r="B49" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5779,39 +5789,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493295</v>
+        <v>492993</v>
       </c>
       <c r="R49" t="n">
-        <v>6761257</v>
+        <v>6761086</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5843,7 +5848,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5853,7 +5858,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5880,50 +5885,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128994503</v>
+        <v>128999673</v>
       </c>
       <c r="B50" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493047</v>
+        <v>493255</v>
       </c>
       <c r="R50" t="n">
-        <v>6761263</v>
+        <v>6761127</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6211,10 +6211,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128991818</v>
+        <v>128998638</v>
       </c>
       <c r="B53" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6222,34 +6222,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>493312</v>
+        <v>492971</v>
       </c>
       <c r="R53" t="n">
-        <v>6761262</v>
+        <v>6761075</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6281,7 +6286,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6291,7 +6296,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6318,7 +6323,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128998999</v>
+        <v>128991818</v>
       </c>
       <c r="B54" t="n">
         <v>79044</v>
@@ -6349,14 +6354,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493048</v>
+        <v>493312</v>
       </c>
       <c r="R54" t="n">
-        <v>6761092</v>
+        <v>6761262</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6388,7 +6393,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6398,7 +6403,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6425,10 +6430,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128998638</v>
+        <v>128998999</v>
       </c>
       <c r="B55" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6436,39 +6441,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>492971</v>
+        <v>493048</v>
       </c>
       <c r="R55" t="n">
-        <v>6761075</v>
+        <v>6761092</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6978,7 +6978,7 @@
         <v>129015883</v>
       </c>
       <c r="B60" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 41794-2025 artfynd.xlsx
+++ b/artfynd/A 41794-2025 artfynd.xlsx
@@ -1429,7 +1429,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128999256</v>
+        <v>128999351</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493048</v>
+        <v>493087</v>
       </c>
       <c r="R9" t="n">
-        <v>6761242</v>
+        <v>6761166</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128998367</v>
+        <v>128999256</v>
       </c>
       <c r="B10" t="n">
         <v>79044</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492928</v>
+        <v>493048</v>
       </c>
       <c r="R10" t="n">
-        <v>6761141</v>
+        <v>6761242</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128999351</v>
+        <v>128998367</v>
       </c>
       <c r="B11" t="n">
         <v>79044</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493087</v>
+        <v>492928</v>
       </c>
       <c r="R11" t="n">
-        <v>6761166</v>
+        <v>6761141</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128998263</v>
+        <v>128998025</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,39 +1761,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492885</v>
+        <v>492895</v>
       </c>
       <c r="R12" t="n">
-        <v>6761180</v>
+        <v>6761212</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1862,50 +1857,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128999613</v>
+        <v>128990939</v>
       </c>
       <c r="B13" t="n">
-        <v>57724</v>
+        <v>97595</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493205</v>
+        <v>493487</v>
       </c>
       <c r="R13" t="n">
-        <v>6761180</v>
+        <v>6761281</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,7 +1927,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1937,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128997799</v>
+        <v>128991923</v>
       </c>
       <c r="B14" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,39 +1980,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492929</v>
+        <v>493277</v>
       </c>
       <c r="R14" t="n">
-        <v>6761272</v>
+        <v>6761265</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2059,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128998274</v>
+        <v>128991903</v>
       </c>
       <c r="B15" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,39 +2087,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492894</v>
+        <v>493287</v>
       </c>
       <c r="R15" t="n">
-        <v>6761171</v>
+        <v>6761277</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,7 +2146,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2171,7 +2156,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2198,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128998025</v>
+        <v>128998263</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,34 +2194,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492895</v>
+        <v>492885</v>
       </c>
       <c r="R16" t="n">
-        <v>6761212</v>
+        <v>6761180</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2305,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128991923</v>
+        <v>128999613</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2316,34 +2306,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493277</v>
+        <v>493205</v>
       </c>
       <c r="R17" t="n">
-        <v>6761265</v>
+        <v>6761180</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2375,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2385,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2412,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128991903</v>
+        <v>128997799</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,34 +2418,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493287</v>
+        <v>492929</v>
       </c>
       <c r="R18" t="n">
-        <v>6761277</v>
+        <v>6761272</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2519,45 +2519,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128990939</v>
+        <v>128998274</v>
       </c>
       <c r="B19" t="n">
-        <v>97595</v>
+        <v>57724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493487</v>
+        <v>492894</v>
       </c>
       <c r="R19" t="n">
-        <v>6761281</v>
+        <v>6761171</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,7 +2594,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2599,12 +2604,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2738,7 +2738,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128998438</v>
+        <v>128991027</v>
       </c>
       <c r="B21" t="n">
         <v>79044</v>
@@ -2769,14 +2769,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492969</v>
+        <v>493464</v>
       </c>
       <c r="R21" t="n">
-        <v>6761101</v>
+        <v>6761291</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2845,7 +2845,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128991027</v>
+        <v>128998438</v>
       </c>
       <c r="B22" t="n">
         <v>79044</v>
@@ -2876,14 +2876,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493464</v>
+        <v>492969</v>
       </c>
       <c r="R22" t="n">
-        <v>6761291</v>
+        <v>6761101</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2952,10 +2952,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128991711</v>
+        <v>128998223</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2963,39 +2963,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493310</v>
+        <v>492885</v>
       </c>
       <c r="R23" t="n">
-        <v>6761241</v>
+        <v>6761180</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3027,7 +3022,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3037,7 +3032,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3064,7 +3059,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128998223</v>
+        <v>128998201</v>
       </c>
       <c r="B24" t="n">
         <v>79044</v>
@@ -3099,10 +3094,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492885</v>
+        <v>492877</v>
       </c>
       <c r="R24" t="n">
-        <v>6761180</v>
+        <v>6761211</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3171,10 +3166,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128998201</v>
+        <v>128991711</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3182,34 +3177,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492877</v>
+        <v>493310</v>
       </c>
       <c r="R25" t="n">
-        <v>6761211</v>
+        <v>6761241</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3608,7 +3608,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128995396</v>
+        <v>128994343</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492992</v>
+        <v>493103</v>
       </c>
       <c r="R29" t="n">
-        <v>6761309</v>
+        <v>6761270</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3715,7 +3715,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128994343</v>
+        <v>128995396</v>
       </c>
       <c r="B30" t="n">
         <v>79044</v>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493103</v>
+        <v>492992</v>
       </c>
       <c r="R30" t="n">
-        <v>6761270</v>
+        <v>6761309</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3929,45 +3929,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128991481</v>
+        <v>128994846</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493300</v>
+        <v>493013</v>
       </c>
       <c r="R32" t="n">
-        <v>6761215</v>
+        <v>6761220</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4036,45 +4036,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128994846</v>
+        <v>128991481</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493013</v>
+        <v>493300</v>
       </c>
       <c r="R33" t="n">
-        <v>6761220</v>
+        <v>6761215</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4362,7 +4362,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128994864</v>
+        <v>128994367</v>
       </c>
       <c r="B36" t="n">
         <v>79044</v>
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493021</v>
+        <v>493118</v>
       </c>
       <c r="R36" t="n">
-        <v>6761214</v>
+        <v>6761310</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4469,7 +4469,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128993887</v>
+        <v>128997967</v>
       </c>
       <c r="B37" t="n">
         <v>79044</v>
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493167</v>
+        <v>492949</v>
       </c>
       <c r="R37" t="n">
-        <v>6761257</v>
+        <v>6761266</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4550,6 +4550,11 @@
       <c r="AB37" t="inlineStr">
         <is>
           <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4576,10 +4581,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128994367</v>
+        <v>128991964</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>58157</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4587,37 +4592,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493118</v>
+        <v>493252</v>
       </c>
       <c r="R38" t="n">
-        <v>6761310</v>
+        <v>6761277</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4646,7 +4656,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4656,7 +4666,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4683,7 +4693,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128991964</v>
+        <v>128999032</v>
       </c>
       <c r="B39" t="n">
         <v>58157</v>
@@ -4719,17 +4729,17 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493252</v>
+        <v>493048</v>
       </c>
       <c r="R39" t="n">
-        <v>6761277</v>
+        <v>6761092</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4758,7 +4768,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4768,7 +4778,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4795,10 +4805,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128999032</v>
+        <v>128994864</v>
       </c>
       <c r="B40" t="n">
-        <v>58157</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4806,39 +4816,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493048</v>
+        <v>493021</v>
       </c>
       <c r="R40" t="n">
-        <v>6761092</v>
+        <v>6761214</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4870,7 +4875,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4880,7 +4885,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4907,7 +4912,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128997967</v>
+        <v>128993887</v>
       </c>
       <c r="B41" t="n">
         <v>79044</v>
@@ -4942,10 +4947,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492949</v>
+        <v>493167</v>
       </c>
       <c r="R41" t="n">
-        <v>6761266</v>
+        <v>6761257</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4988,11 +4993,6 @@
       <c r="AB41" t="inlineStr">
         <is>
           <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5019,7 +5019,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128991661</v>
+        <v>128995173</v>
       </c>
       <c r="B42" t="n">
         <v>79044</v>
@@ -5050,14 +5050,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493295</v>
+        <v>493010</v>
       </c>
       <c r="R42" t="n">
-        <v>6761257</v>
+        <v>6761236</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5126,7 +5126,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128994946</v>
+        <v>128991661</v>
       </c>
       <c r="B43" t="n">
         <v>79044</v>
@@ -5157,14 +5157,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492986</v>
+        <v>493295</v>
       </c>
       <c r="R43" t="n">
-        <v>6761194</v>
+        <v>6761257</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5233,7 +5233,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128995173</v>
+        <v>128994946</v>
       </c>
       <c r="B44" t="n">
         <v>79044</v>
@@ -5268,10 +5268,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>493010</v>
+        <v>492986</v>
       </c>
       <c r="R44" t="n">
-        <v>6761236</v>
+        <v>6761194</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5554,10 +5554,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128991653</v>
+        <v>128998610</v>
       </c>
       <c r="B47" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5565,39 +5565,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493295</v>
+        <v>492993</v>
       </c>
       <c r="R47" t="n">
-        <v>6761257</v>
+        <v>6761086</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5629,7 +5624,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5639,7 +5634,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5666,7 +5661,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128994503</v>
+        <v>128991653</v>
       </c>
       <c r="B48" t="n">
         <v>57724</v>
@@ -5697,19 +5692,19 @@
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493047</v>
+        <v>493295</v>
       </c>
       <c r="R48" t="n">
-        <v>6761263</v>
+        <v>6761257</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5741,7 +5736,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5751,7 +5746,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5778,10 +5773,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128998610</v>
+        <v>128994503</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5789,34 +5784,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492993</v>
+        <v>493047</v>
       </c>
       <c r="R49" t="n">
-        <v>6761086</v>
+        <v>6761263</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5992,10 +5992,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128994661</v>
+        <v>128999627</v>
       </c>
       <c r="B51" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6003,39 +6003,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493048</v>
+        <v>493222</v>
       </c>
       <c r="R51" t="n">
-        <v>6761242</v>
+        <v>6761162</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6067,7 +6062,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6077,7 +6072,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6104,10 +6099,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128999627</v>
+        <v>128994661</v>
       </c>
       <c r="B52" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6115,34 +6110,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493222</v>
+        <v>493048</v>
       </c>
       <c r="R52" t="n">
-        <v>6761162</v>
+        <v>6761242</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 41794-2025 artfynd.xlsx
+++ b/artfynd/A 41794-2025 artfynd.xlsx
@@ -1750,45 +1750,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128998025</v>
+        <v>128990939</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>97595</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492895</v>
+        <v>493487</v>
       </c>
       <c r="R12" t="n">
-        <v>6761212</v>
+        <v>6761281</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1830,7 +1830,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1857,45 +1862,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128990939</v>
+        <v>128998025</v>
       </c>
       <c r="B13" t="n">
-        <v>97595</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493487</v>
+        <v>492895</v>
       </c>
       <c r="R13" t="n">
-        <v>6761281</v>
+        <v>6761212</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1937,12 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3278,10 +3278,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128990886</v>
+        <v>128995392</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>91571</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3289,34 +3289,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493487</v>
+        <v>492992</v>
       </c>
       <c r="R26" t="n">
-        <v>6761281</v>
+        <v>6761309</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3348,7 +3352,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3358,12 +3362,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Sumpskogskaraktär i området här.</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3390,45 +3389,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128994100</v>
+        <v>128990886</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493167</v>
+        <v>493487</v>
       </c>
       <c r="R27" t="n">
-        <v>6761257</v>
+        <v>6761281</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3460,7 +3459,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3470,7 +3469,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Sumpskogskaraktär i området här.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3497,49 +3501,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128995392</v>
+        <v>128994100</v>
       </c>
       <c r="B28" t="n">
-        <v>91571</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492992</v>
+        <v>493167</v>
       </c>
       <c r="R28" t="n">
-        <v>6761309</v>
+        <v>6761257</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4250,10 +4250,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128991491</v>
+        <v>128994864</v>
       </c>
       <c r="B35" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4261,39 +4261,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493290</v>
+        <v>493021</v>
       </c>
       <c r="R35" t="n">
-        <v>6761213</v>
+        <v>6761214</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4325,7 +4320,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4335,7 +4330,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4362,7 +4357,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128994367</v>
+        <v>128993887</v>
       </c>
       <c r="B36" t="n">
         <v>79044</v>
@@ -4397,10 +4392,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493118</v>
+        <v>493167</v>
       </c>
       <c r="R36" t="n">
-        <v>6761310</v>
+        <v>6761257</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4469,7 +4464,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128997967</v>
+        <v>128994367</v>
       </c>
       <c r="B37" t="n">
         <v>79044</v>
@@ -4504,10 +4499,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>492949</v>
+        <v>493118</v>
       </c>
       <c r="R37" t="n">
-        <v>6761266</v>
+        <v>6761310</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4550,11 +4545,6 @@
       <c r="AB37" t="inlineStr">
         <is>
           <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4581,10 +4571,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128991964</v>
+        <v>128997967</v>
       </c>
       <c r="B38" t="n">
-        <v>58157</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4592,42 +4582,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493252</v>
+        <v>492949</v>
       </c>
       <c r="R38" t="n">
-        <v>6761277</v>
+        <v>6761266</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4656,7 +4641,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4666,7 +4651,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4693,10 +4683,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128999032</v>
+        <v>128991491</v>
       </c>
       <c r="B39" t="n">
-        <v>58157</v>
+        <v>57724</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4704,39 +4694,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103001</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493048</v>
+        <v>493290</v>
       </c>
       <c r="R39" t="n">
-        <v>6761092</v>
+        <v>6761213</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4768,7 +4758,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4778,7 +4768,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4805,10 +4795,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128994864</v>
+        <v>128991964</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>58157</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4816,37 +4806,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493021</v>
+        <v>493252</v>
       </c>
       <c r="R40" t="n">
-        <v>6761214</v>
+        <v>6761277</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4875,7 +4870,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4885,7 +4880,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4912,10 +4907,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128993887</v>
+        <v>128999032</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>58157</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4923,34 +4918,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493167</v>
+        <v>493048</v>
       </c>
       <c r="R41" t="n">
-        <v>6761257</v>
+        <v>6761092</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5554,32 +5554,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128998610</v>
+        <v>128999673</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5589,10 +5589,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492993</v>
+        <v>493255</v>
       </c>
       <c r="R47" t="n">
-        <v>6761086</v>
+        <v>6761127</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5661,10 +5661,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128991653</v>
+        <v>128998610</v>
       </c>
       <c r="B48" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5672,39 +5672,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493295</v>
+        <v>492993</v>
       </c>
       <c r="R48" t="n">
-        <v>6761257</v>
+        <v>6761086</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5736,7 +5731,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5746,7 +5741,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5773,7 +5768,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128994503</v>
+        <v>128991653</v>
       </c>
       <c r="B49" t="n">
         <v>57724</v>
@@ -5804,19 +5799,19 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493047</v>
+        <v>493295</v>
       </c>
       <c r="R49" t="n">
-        <v>6761263</v>
+        <v>6761257</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5848,7 +5843,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5858,7 +5853,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5885,45 +5880,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128999673</v>
+        <v>128994503</v>
       </c>
       <c r="B50" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493255</v>
+        <v>493047</v>
       </c>
       <c r="R50" t="n">
-        <v>6761127</v>
+        <v>6761263</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6211,10 +6211,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128998638</v>
+        <v>128991818</v>
       </c>
       <c r="B53" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6222,39 +6222,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>492971</v>
+        <v>493312</v>
       </c>
       <c r="R53" t="n">
-        <v>6761075</v>
+        <v>6761262</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6286,7 +6281,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6296,7 +6291,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6323,7 +6318,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128991818</v>
+        <v>128998999</v>
       </c>
       <c r="B54" t="n">
         <v>79044</v>
@@ -6354,14 +6349,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493312</v>
+        <v>493048</v>
       </c>
       <c r="R54" t="n">
-        <v>6761262</v>
+        <v>6761092</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6393,7 +6388,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6403,7 +6398,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6430,10 +6425,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128998999</v>
+        <v>128998638</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6441,34 +6436,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>493048</v>
+        <v>492971</v>
       </c>
       <c r="R55" t="n">
-        <v>6761092</v>
+        <v>6761075</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 41794-2025 artfynd.xlsx
+++ b/artfynd/A 41794-2025 artfynd.xlsx
@@ -1429,7 +1429,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128999351</v>
+        <v>128999256</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493087</v>
+        <v>493048</v>
       </c>
       <c r="R9" t="n">
-        <v>6761166</v>
+        <v>6761242</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128999256</v>
+        <v>128998367</v>
       </c>
       <c r="B10" t="n">
         <v>79044</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493048</v>
+        <v>492928</v>
       </c>
       <c r="R10" t="n">
-        <v>6761242</v>
+        <v>6761141</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128998367</v>
+        <v>128999351</v>
       </c>
       <c r="B11" t="n">
         <v>79044</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492928</v>
+        <v>493087</v>
       </c>
       <c r="R11" t="n">
-        <v>6761141</v>
+        <v>6761166</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,45 +1750,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128990939</v>
+        <v>128998263</v>
       </c>
       <c r="B12" t="n">
-        <v>97595</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493487</v>
+        <v>492885</v>
       </c>
       <c r="R12" t="n">
-        <v>6761281</v>
+        <v>6761180</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1830,12 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128998025</v>
+        <v>128999613</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,34 +1873,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492895</v>
+        <v>493205</v>
       </c>
       <c r="R13" t="n">
-        <v>6761212</v>
+        <v>6761180</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128991923</v>
+        <v>128997799</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,34 +1985,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493277</v>
+        <v>492929</v>
       </c>
       <c r="R14" t="n">
-        <v>6761265</v>
+        <v>6761272</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2049,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2059,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128991903</v>
+        <v>128998274</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2087,34 +2097,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493287</v>
+        <v>492894</v>
       </c>
       <c r="R15" t="n">
-        <v>6761277</v>
+        <v>6761171</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2161,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2156,7 +2171,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128998263</v>
+        <v>128998025</v>
       </c>
       <c r="B16" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,39 +2209,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492885</v>
+        <v>492895</v>
       </c>
       <c r="R16" t="n">
-        <v>6761180</v>
+        <v>6761212</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2295,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128999613</v>
+        <v>128991923</v>
       </c>
       <c r="B17" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2306,39 +2316,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493205</v>
+        <v>493277</v>
       </c>
       <c r="R17" t="n">
-        <v>6761180</v>
+        <v>6761265</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2375,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2385,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,10 +2412,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128997799</v>
+        <v>128991903</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2418,39 +2423,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492929</v>
+        <v>493287</v>
       </c>
       <c r="R18" t="n">
-        <v>6761272</v>
+        <v>6761277</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2519,50 +2519,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128998274</v>
+        <v>128990939</v>
       </c>
       <c r="B19" t="n">
-        <v>57724</v>
+        <v>97598</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492894</v>
+        <v>493487</v>
       </c>
       <c r="R19" t="n">
-        <v>6761171</v>
+        <v>6761281</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2594,7 +2589,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2604,7 +2599,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2738,7 +2738,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128991027</v>
+        <v>128998438</v>
       </c>
       <c r="B21" t="n">
         <v>79044</v>
@@ -2769,14 +2769,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493464</v>
+        <v>492969</v>
       </c>
       <c r="R21" t="n">
-        <v>6761291</v>
+        <v>6761101</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2845,7 +2845,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128998438</v>
+        <v>128991027</v>
       </c>
       <c r="B22" t="n">
         <v>79044</v>
@@ -2876,14 +2876,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492969</v>
+        <v>493464</v>
       </c>
       <c r="R22" t="n">
-        <v>6761101</v>
+        <v>6761291</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3278,10 +3278,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128995392</v>
+        <v>128990886</v>
       </c>
       <c r="B26" t="n">
-        <v>91571</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3289,38 +3289,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492992</v>
+        <v>493487</v>
       </c>
       <c r="R26" t="n">
-        <v>6761309</v>
+        <v>6761281</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3352,7 +3348,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3362,7 +3358,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Sumpskogskaraktär i området här.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3389,45 +3390,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128990886</v>
+        <v>128994100</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493487</v>
+        <v>493167</v>
       </c>
       <c r="R27" t="n">
-        <v>6761281</v>
+        <v>6761257</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3459,7 +3460,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3469,12 +3470,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Sumpskogskaraktär i området här.</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3501,45 +3497,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128994100</v>
+        <v>128995392</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>91574</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493167</v>
+        <v>492992</v>
       </c>
       <c r="R28" t="n">
-        <v>6761257</v>
+        <v>6761309</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128994343</v>
+        <v>128995396</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493103</v>
+        <v>492992</v>
       </c>
       <c r="R29" t="n">
-        <v>6761270</v>
+        <v>6761309</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3715,7 +3715,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128995396</v>
+        <v>128994343</v>
       </c>
       <c r="B30" t="n">
         <v>79044</v>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492992</v>
+        <v>493103</v>
       </c>
       <c r="R30" t="n">
-        <v>6761309</v>
+        <v>6761270</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3929,45 +3929,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128994846</v>
+        <v>128991481</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493013</v>
+        <v>493300</v>
       </c>
       <c r="R32" t="n">
-        <v>6761220</v>
+        <v>6761215</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4036,45 +4036,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128991481</v>
+        <v>128994846</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493300</v>
+        <v>493013</v>
       </c>
       <c r="R33" t="n">
-        <v>6761215</v>
+        <v>6761220</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5126,7 +5126,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128991661</v>
+        <v>128999732</v>
       </c>
       <c r="B43" t="n">
         <v>79044</v>
@@ -5161,10 +5161,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493295</v>
+        <v>493327</v>
       </c>
       <c r="R43" t="n">
-        <v>6761257</v>
+        <v>6761155</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5233,7 +5233,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128994946</v>
+        <v>128991661</v>
       </c>
       <c r="B44" t="n">
         <v>79044</v>
@@ -5264,14 +5264,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492986</v>
+        <v>493295</v>
       </c>
       <c r="R44" t="n">
-        <v>6761194</v>
+        <v>6761257</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5340,10 +5340,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128994294</v>
+        <v>128994946</v>
       </c>
       <c r="B45" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5351,21 +5351,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5375,10 +5375,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>493144</v>
+        <v>492986</v>
       </c>
       <c r="R45" t="n">
-        <v>6761263</v>
+        <v>6761194</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5447,10 +5447,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128999732</v>
+        <v>128994294</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5458,34 +5458,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493327</v>
+        <v>493144</v>
       </c>
       <c r="R46" t="n">
-        <v>6761155</v>
+        <v>6761263</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5554,32 +5554,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128999673</v>
+        <v>128998610</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5589,10 +5589,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493255</v>
+        <v>492993</v>
       </c>
       <c r="R47" t="n">
-        <v>6761127</v>
+        <v>6761086</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5661,10 +5661,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128998610</v>
+        <v>128991653</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5672,34 +5672,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492993</v>
+        <v>493295</v>
       </c>
       <c r="R48" t="n">
-        <v>6761086</v>
+        <v>6761257</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5731,7 +5736,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5741,7 +5746,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5768,7 +5773,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128991653</v>
+        <v>128994503</v>
       </c>
       <c r="B49" t="n">
         <v>57724</v>
@@ -5799,19 +5804,19 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493295</v>
+        <v>493047</v>
       </c>
       <c r="R49" t="n">
-        <v>6761257</v>
+        <v>6761263</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5843,7 +5848,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5853,7 +5858,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5880,50 +5885,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128994503</v>
+        <v>128999673</v>
       </c>
       <c r="B50" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493047</v>
+        <v>493255</v>
       </c>
       <c r="R50" t="n">
-        <v>6761263</v>
+        <v>6761127</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6978,7 +6978,7 @@
         <v>129015883</v>
       </c>
       <c r="B60" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 41794-2025 artfynd.xlsx
+++ b/artfynd/A 41794-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128991347</v>
+        <v>128995392</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493372</v>
+        <v>492992</v>
       </c>
       <c r="R2" t="n">
-        <v>6761249</v>
+        <v>6761309</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128998779</v>
+        <v>129015883</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +797,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492970</v>
+        <v>493474</v>
       </c>
       <c r="R3" t="n">
-        <v>6761018</v>
+        <v>6761277</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,27 +861,18 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,14 +891,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128999532</v>
+        <v>128990886</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -924,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493157</v>
+        <v>493487</v>
       </c>
       <c r="R4" t="n">
-        <v>6761137</v>
+        <v>6761281</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +961,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,12 +971,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Sumpskogskaraktär i området här.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,14 +1003,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128993314</v>
+        <v>128991005</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1032,14 +1034,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493165</v>
+        <v>493464</v>
       </c>
       <c r="R5" t="n">
-        <v>6761309</v>
+        <v>6761291</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,14 +1110,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128997543</v>
+        <v>128991220</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1139,14 +1141,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492963</v>
+        <v>493446</v>
       </c>
       <c r="R6" t="n">
-        <v>6761283</v>
+        <v>6761310</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1180,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1190,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,14 +1217,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128992649</v>
+        <v>128991347</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1250,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493247</v>
+        <v>493372</v>
       </c>
       <c r="R7" t="n">
-        <v>6761309</v>
+        <v>6761249</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,14 +1324,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128994822</v>
+        <v>128991661</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1353,14 +1355,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493022</v>
+        <v>493295</v>
       </c>
       <c r="R8" t="n">
-        <v>6761226</v>
+        <v>6761257</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1394,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,7 +1404,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,14 +1431,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128999256</v>
+        <v>128991818</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1460,14 +1462,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493048</v>
+        <v>493312</v>
       </c>
       <c r="R9" t="n">
-        <v>6761242</v>
+        <v>6761262</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1501,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1511,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,14 +1538,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128998367</v>
+        <v>128991903</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1567,14 +1569,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492928</v>
+        <v>493287</v>
       </c>
       <c r="R10" t="n">
-        <v>6761141</v>
+        <v>6761277</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1608,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,7 +1618,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1643,14 +1645,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128999351</v>
+        <v>128991923</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1674,14 +1676,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493087</v>
+        <v>493277</v>
       </c>
       <c r="R11" t="n">
-        <v>6761166</v>
+        <v>6761265</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1715,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1723,7 +1725,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,50 +1752,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128998263</v>
+        <v>128992535</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492885</v>
+        <v>493247</v>
       </c>
       <c r="R12" t="n">
-        <v>6761180</v>
+        <v>6761309</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1822,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1832,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,50 +1859,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128999613</v>
+        <v>128993230</v>
       </c>
       <c r="B13" t="n">
-        <v>57724</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
         <v>493205</v>
       </c>
       <c r="R13" t="n">
-        <v>6761180</v>
+        <v>6761315</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,7 +1929,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1939,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,50 +1966,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128997799</v>
+        <v>128993314</v>
       </c>
       <c r="B14" t="n">
-        <v>57724</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492929</v>
+        <v>493165</v>
       </c>
       <c r="R14" t="n">
-        <v>6761272</v>
+        <v>6761309</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,7 +2036,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2059,7 +2046,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,50 +2073,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128998274</v>
+        <v>128993887</v>
       </c>
       <c r="B15" t="n">
-        <v>57724</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492894</v>
+        <v>493167</v>
       </c>
       <c r="R15" t="n">
-        <v>6761171</v>
+        <v>6761257</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2198,14 +2180,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128998025</v>
+        <v>128994202</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2233,10 +2215,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492895</v>
+        <v>493144</v>
       </c>
       <c r="R16" t="n">
-        <v>6761212</v>
+        <v>6761263</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2305,14 +2287,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128991923</v>
+        <v>128994343</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2336,14 +2318,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493277</v>
+        <v>493103</v>
       </c>
       <c r="R17" t="n">
-        <v>6761265</v>
+        <v>6761270</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2375,7 +2357,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2385,7 +2367,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2412,14 +2394,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128991903</v>
+        <v>128994367</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2443,14 +2425,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493287</v>
+        <v>493118</v>
       </c>
       <c r="R18" t="n">
-        <v>6761277</v>
+        <v>6761310</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,7 +2464,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2492,7 +2474,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2519,45 +2501,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128990939</v>
+        <v>128994769</v>
       </c>
       <c r="B19" t="n">
-        <v>97598</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493487</v>
+        <v>493022</v>
       </c>
       <c r="R19" t="n">
-        <v>6761281</v>
+        <v>6761226</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,7 +2571,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2599,12 +2581,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2631,14 +2608,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128994202</v>
+        <v>128994846</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2666,10 +2643,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493144</v>
+        <v>493013</v>
       </c>
       <c r="R20" t="n">
-        <v>6761263</v>
+        <v>6761220</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2738,14 +2715,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128998438</v>
+        <v>128994864</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2773,10 +2750,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492969</v>
+        <v>493021</v>
       </c>
       <c r="R21" t="n">
-        <v>6761101</v>
+        <v>6761214</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2808,7 +2785,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2818,7 +2795,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2845,14 +2822,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128991027</v>
+        <v>128994922</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2876,14 +2853,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493464</v>
+        <v>493011</v>
       </c>
       <c r="R22" t="n">
-        <v>6761291</v>
+        <v>6761188</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2915,7 +2892,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2925,7 +2902,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2952,14 +2929,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128998223</v>
+        <v>128994946</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2987,10 +2964,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492885</v>
+        <v>492986</v>
       </c>
       <c r="R23" t="n">
-        <v>6761180</v>
+        <v>6761194</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3059,14 +3036,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128998201</v>
+        <v>128994977</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3094,10 +3071,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492877</v>
+        <v>492979</v>
       </c>
       <c r="R24" t="n">
-        <v>6761211</v>
+        <v>6761210</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3166,50 +3143,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128991711</v>
+        <v>128995173</v>
       </c>
       <c r="B25" t="n">
-        <v>57724</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493310</v>
+        <v>493010</v>
       </c>
       <c r="R25" t="n">
-        <v>6761241</v>
+        <v>6761236</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3241,7 +3213,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3251,7 +3223,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3278,14 +3250,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128990886</v>
+        <v>128995292</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3309,14 +3281,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493487</v>
+        <v>492996</v>
       </c>
       <c r="R26" t="n">
-        <v>6761281</v>
+        <v>6761284</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3348,7 +3320,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3358,12 +3330,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Sumpskogskaraktär i området här.</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3390,32 +3357,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128994100</v>
+        <v>128995320</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3425,10 +3392,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493167</v>
+        <v>492992</v>
       </c>
       <c r="R27" t="n">
-        <v>6761257</v>
+        <v>6761309</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3497,49 +3464,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128995392</v>
+        <v>128995447</v>
       </c>
       <c r="B28" t="n">
-        <v>91574</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492992</v>
+        <v>492963</v>
       </c>
       <c r="R28" t="n">
-        <v>6761309</v>
+        <v>6761283</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3608,14 +3571,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128995396</v>
+        <v>128997930</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3643,10 +3606,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492992</v>
+        <v>492949</v>
       </c>
       <c r="R29" t="n">
-        <v>6761309</v>
+        <v>6761266</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3715,14 +3678,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128994343</v>
+        <v>128998025</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3750,10 +3713,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493103</v>
+        <v>492895</v>
       </c>
       <c r="R30" t="n">
-        <v>6761270</v>
+        <v>6761212</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3822,32 +3785,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128998878</v>
+        <v>128998201</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3857,10 +3820,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492993</v>
+        <v>492877</v>
       </c>
       <c r="R31" t="n">
-        <v>6761002</v>
+        <v>6761211</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3892,7 +3855,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3902,7 +3865,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3929,45 +3892,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128991481</v>
+        <v>128998223</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493300</v>
+        <v>492885</v>
       </c>
       <c r="R32" t="n">
-        <v>6761215</v>
+        <v>6761180</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3999,7 +3962,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4009,7 +3972,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4036,14 +3999,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128994846</v>
+        <v>128998367</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4071,10 +4034,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493013</v>
+        <v>492928</v>
       </c>
       <c r="R33" t="n">
-        <v>6761220</v>
+        <v>6761141</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4106,7 +4069,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4116,7 +4079,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4143,14 +4106,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128994977</v>
+        <v>128998438</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4178,10 +4141,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492979</v>
+        <v>492969</v>
       </c>
       <c r="R34" t="n">
-        <v>6761210</v>
+        <v>6761101</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4213,7 +4176,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4223,7 +4186,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4250,14 +4213,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128994864</v>
+        <v>128998610</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4285,10 +4248,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493021</v>
+        <v>492993</v>
       </c>
       <c r="R35" t="n">
-        <v>6761214</v>
+        <v>6761086</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4320,7 +4283,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4330,7 +4293,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4357,14 +4320,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128993887</v>
+        <v>128998766</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4392,10 +4355,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493167</v>
+        <v>492970</v>
       </c>
       <c r="R36" t="n">
-        <v>6761257</v>
+        <v>6761018</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4427,7 +4390,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4437,7 +4400,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4464,14 +4427,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128994367</v>
+        <v>128998999</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4499,10 +4462,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493118</v>
+        <v>493048</v>
       </c>
       <c r="R37" t="n">
-        <v>6761310</v>
+        <v>6761092</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4534,7 +4497,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4544,7 +4507,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4571,14 +4534,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128997967</v>
+        <v>128999256</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4606,10 +4569,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>492949</v>
+        <v>493048</v>
       </c>
       <c r="R38" t="n">
-        <v>6761266</v>
+        <v>6761242</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4641,7 +4604,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4651,12 +4614,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4683,50 +4641,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128991491</v>
+        <v>128999312</v>
       </c>
       <c r="B39" t="n">
-        <v>57724</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493290</v>
+        <v>493087</v>
       </c>
       <c r="R39" t="n">
-        <v>6761213</v>
+        <v>6761166</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4758,7 +4711,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4768,7 +4721,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4795,53 +4748,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128991964</v>
+        <v>128999532</v>
       </c>
       <c r="B40" t="n">
-        <v>58157</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493252</v>
+        <v>493157</v>
       </c>
       <c r="R40" t="n">
-        <v>6761277</v>
+        <v>6761137</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4870,7 +4818,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4880,7 +4828,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4907,50 +4860,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128999032</v>
+        <v>128999627</v>
       </c>
       <c r="B41" t="n">
-        <v>58157</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493048</v>
+        <v>493222</v>
       </c>
       <c r="R41" t="n">
-        <v>6761092</v>
+        <v>6761162</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5019,14 +4967,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128995173</v>
+        <v>128999732</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -5050,14 +4998,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493010</v>
+        <v>493327</v>
       </c>
       <c r="R42" t="n">
-        <v>6761236</v>
+        <v>6761155</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5089,7 +5037,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5099,7 +5047,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5126,10 +5074,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128999732</v>
+        <v>128994294</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>79946</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5137,34 +5085,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493327</v>
+        <v>493144</v>
       </c>
       <c r="R43" t="n">
-        <v>6761155</v>
+        <v>6761263</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5196,7 +5144,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5206,7 +5154,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5233,45 +5181,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128991661</v>
+        <v>128991154</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>57950</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>493295</v>
+        <v>493446</v>
       </c>
       <c r="R44" t="n">
-        <v>6761257</v>
+        <v>6761310</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5340,45 +5293,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128994946</v>
+        <v>128991463</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>57950</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>492986</v>
+        <v>493300</v>
       </c>
       <c r="R45" t="n">
-        <v>6761194</v>
+        <v>6761215</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5410,7 +5368,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5420,7 +5378,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5447,45 +5405,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128994294</v>
+        <v>128991491</v>
       </c>
       <c r="B46" t="n">
-        <v>79663</v>
+        <v>57950</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493144</v>
+        <v>493290</v>
       </c>
       <c r="R46" t="n">
-        <v>6761263</v>
+        <v>6761213</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5517,7 +5480,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5527,7 +5490,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5554,45 +5517,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128998610</v>
+        <v>128991653</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>57950</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492993</v>
+        <v>493295</v>
       </c>
       <c r="R47" t="n">
-        <v>6761086</v>
+        <v>6761257</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5624,7 +5592,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5634,7 +5602,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5661,14 +5629,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128991653</v>
+        <v>128991711</v>
       </c>
       <c r="B48" t="n">
-        <v>57724</v>
+        <v>57950</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5692,7 +5660,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5701,10 +5669,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493295</v>
+        <v>493310</v>
       </c>
       <c r="R48" t="n">
-        <v>6761257</v>
+        <v>6761241</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5773,14 +5741,14 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128994503</v>
+        <v>128993205</v>
       </c>
       <c r="B49" t="n">
-        <v>57724</v>
+        <v>57950</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -5804,19 +5772,19 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493047</v>
+        <v>493205</v>
       </c>
       <c r="R49" t="n">
-        <v>6761263</v>
+        <v>6761315</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5848,7 +5816,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5858,7 +5826,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5885,10 +5853,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128999673</v>
+        <v>128994503</v>
       </c>
       <c r="B50" t="n">
-        <v>8450</v>
+        <v>57950</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5896,34 +5864,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493255</v>
+        <v>493047</v>
       </c>
       <c r="R50" t="n">
-        <v>6761127</v>
+        <v>6761263</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5955,7 +5928,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5965,7 +5938,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5992,45 +5965,50 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128999627</v>
+        <v>128994661</v>
       </c>
       <c r="B51" t="n">
-        <v>79044</v>
+        <v>57950</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493222</v>
+        <v>493048</v>
       </c>
       <c r="R51" t="n">
-        <v>6761162</v>
+        <v>6761242</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6062,7 +6040,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6072,7 +6050,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6099,14 +6077,14 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128994661</v>
+        <v>128997799</v>
       </c>
       <c r="B52" t="n">
-        <v>57724</v>
+        <v>57950</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -6130,7 +6108,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6139,10 +6117,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493048</v>
+        <v>492929</v>
       </c>
       <c r="R52" t="n">
-        <v>6761242</v>
+        <v>6761272</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6211,45 +6189,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128991818</v>
+        <v>128998263</v>
       </c>
       <c r="B53" t="n">
-        <v>79044</v>
+        <v>57950</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>493312</v>
+        <v>492885</v>
       </c>
       <c r="R53" t="n">
-        <v>6761262</v>
+        <v>6761180</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6281,7 +6264,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6291,7 +6274,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6318,45 +6301,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128998999</v>
+        <v>128998274</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>57950</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493048</v>
+        <v>492894</v>
       </c>
       <c r="R54" t="n">
-        <v>6761092</v>
+        <v>6761171</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6388,7 +6376,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6398,7 +6386,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6428,11 +6416,11 @@
         <v>128998638</v>
       </c>
       <c r="B55" t="n">
-        <v>57724</v>
+        <v>57950</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -6537,14 +6525,14 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128991463</v>
+        <v>128999613</v>
       </c>
       <c r="B56" t="n">
-        <v>57724</v>
+        <v>57950</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -6568,19 +6556,19 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>493300</v>
+        <v>493205</v>
       </c>
       <c r="R56" t="n">
-        <v>6761215</v>
+        <v>6761180</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6612,7 +6600,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6622,7 +6610,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6649,10 +6637,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128995292</v>
+        <v>128991964</v>
       </c>
       <c r="B57" t="n">
-        <v>79044</v>
+        <v>58388</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6660,37 +6648,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>492996</v>
+        <v>493252</v>
       </c>
       <c r="R57" t="n">
-        <v>6761284</v>
+        <v>6761277</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6719,7 +6712,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6729,7 +6722,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6756,32 +6749,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128990627</v>
+        <v>128999032</v>
       </c>
       <c r="B58" t="n">
-        <v>58097</v>
+        <v>58388</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103015</v>
+        <v>103001</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6792,17 +6785,17 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stikå-Persänget, Dlr</t>
+          <t>Ingärdningsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>493483</v>
+        <v>493048</v>
       </c>
       <c r="R58" t="n">
-        <v>6761261</v>
+        <v>6761092</v>
       </c>
       <c r="S58" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6831,7 +6824,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6841,7 +6834,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6868,48 +6861,53 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128994922</v>
+        <v>128990627</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>58327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Ingärdningsbodarna, Dlr</t>
+          <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>493011</v>
+        <v>493483</v>
       </c>
       <c r="R59" t="n">
-        <v>6761188</v>
+        <v>6761261</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6938,7 +6936,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6948,7 +6946,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6975,52 +6973,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129015883</v>
+        <v>128991481</v>
       </c>
       <c r="B60" t="n">
-        <v>92873</v>
+        <v>8455</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stikå-Persänget, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>493474</v>
+        <v>493300</v>
       </c>
       <c r="R60" t="n">
-        <v>6761277</v>
+        <v>6761215</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7050,18 +7041,27 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7077,6 +7077,439 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128994100</v>
+      </c>
+      <c r="B61" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Ingärdningsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>493167</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6761257</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128998878</v>
+      </c>
+      <c r="B62" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Ingärdningsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>492993</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6761002</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128999673</v>
+      </c>
+      <c r="B63" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Ingärdningsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>493255</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6761127</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128990939</v>
+      </c>
+      <c r="B64" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Stikå-Persänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>493487</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6761281</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41794-2025 artfynd.xlsx
+++ b/artfynd/A 41794-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AZ64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128995392</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129015883</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128990886</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128991005</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1214,6 +1239,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128991220</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1321,6 +1351,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128991347</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1428,6 +1463,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128991661</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1535,6 +1575,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128991818</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1642,6 +1687,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128991903</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1749,6 +1799,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128991923</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1856,6 +1911,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128992535</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1963,6 +2023,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128993230</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2070,6 +2135,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128993314</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2177,6 +2247,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128993887</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2284,6 +2359,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128994202</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2391,6 +2471,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128994343</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2498,6 +2583,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128994367</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2605,6 +2695,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128994769</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2712,6 +2807,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128994846</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2819,6 +2919,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128994864</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2926,6 +3031,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128994922</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3033,6 +3143,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128994946</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3140,6 +3255,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128994977</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3247,6 +3367,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128995173</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3354,6 +3479,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128995292</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3461,6 +3591,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128995320</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3568,6 +3703,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128995447</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3675,6 +3815,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128997930</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3782,6 +3927,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128998025</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3889,6 +4039,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128998201</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3996,6 +4151,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128998223</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4103,6 +4263,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128998367</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4210,6 +4375,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128998438</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4317,6 +4487,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128998610</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4424,6 +4599,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128998766</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4531,6 +4711,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128998999</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4638,6 +4823,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999256</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4745,6 +4935,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999312</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4857,6 +5052,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999532</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4964,6 +5164,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999627</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5071,6 +5276,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999732</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5178,6 +5388,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128994294</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5290,6 +5505,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128991154</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5402,6 +5622,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128991463</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5514,6 +5739,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128991491</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5626,6 +5856,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128991653</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5738,6 +5973,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128991711</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5850,6 +6090,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128993205</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5962,6 +6207,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128994503</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6074,6 +6324,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128994661</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6186,6 +6441,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128997799</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6298,6 +6558,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128998263</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6410,6 +6675,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128998274</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6522,6 +6792,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128998638</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6634,6 +6909,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999613</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6746,6 +7026,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128991964</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6858,6 +7143,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999032</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6970,6 +7260,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128990627</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7077,6 +7372,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128991481</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7184,6 +7484,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128994100</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7291,6 +7596,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128998878</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7398,6 +7708,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999673</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7510,8 +7825,78 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128990939</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>